--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12T19:16:45</t>
+          <t>2026-09-13T19:26:27</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13T19:26:27</t>
+          <t>2026-09-14T20:56:35</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14T20:56:35</t>
+          <t>2026-09-15T20:13:13</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -1135,7 +1135,7 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 89% 11%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 88% 12%</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Trimmel 75 RB PAC 61 SHO 65 PAS 74 DRI 68 DEF 74 PHY 79 RM R 3 ★ 3 RB 63.4 Trimmel 79 RB PAC 80 SHO 65 PAS 77 DRI 79 DEF 76 PHY 81 RM R 3 ★ 3 RB 76.7 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 92% 8%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Trimmel 75 RB PAC 61 SHO 65 PAS 74 DRI 68 DEF 74 PHY 79 RM R 3 ★ 3 RB 63.4 Trimmel 79 RB PAC 80 SHO 65 PAS 77 DRI 79 DEF 76 PHY 81 RM R 3 ★ 3 RB 76.7 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 93% 8%</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Antônia Silva 80 RB PAC 81 SHO 50 PAS 71 DRI 79 DEF 79 PHY 79 RM R 4 ★ 3 RB 75.5 Antônia Silva 80 RB PAC 81 SHO 50 PAS 71 DRI 79 DEF 79 PHY 79 RM R 4 ★ 3 RB 78.4 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       <c r="CV6" t="inlineStr"/>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 88% of GG users upvoted this Evolution. Vote Now! 88% 12% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades 4 Level 1 Fofana 80 CM PAC 75 SHO 69 PAS 76 DRI 79 DEF 78 PHY 74 CAM R 3 ★ 3 Fofana 80 CM PAC 75 SHO 69 PAS 76 DRI 79 DEF 78 PHY 74 CAM R 3 ★ 3 UPGRADE PATHS Pick one Option A 76.8 GGR 4 Option B Best GG Rating 77.0 GGR 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 89% of GG users upvoted this Evolution. Vote Now! 89% 11% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades 4 Level 1 Fofana 80 CM PAC 75 SHO 69 PAS 76 DRI 79 DEF 78 PHY 74 CAM R 3 ★ 3 Fofana 80 CM PAC 75 SHO 69 PAS 76 DRI 79 DEF 78 PHY 74 CAM R 3 ★ 3 UPGRADE PATHS Pick one Option A 77.0 GGR 4 Option B Best GG Rating 77.2 GGR 4</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES 4 in 1 year in 1 year 88% 12%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES 4 in 1 year in 1 year 89% 11%</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>Pinged Pass NEW</t>
+          <t>Pinged Pass</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Pinged Pass NEW Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>Believe NEW</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Believe NEW Unlocked by completing the Ted Lasso's Masterclass objective Olaru 73 CM PAC 84 SHO 75 PAS 73 DRI 75 DEF 66 PHY 77 CDM CAM ST R 3 ★ 5 CM 81.7 Olaru 74 CM PAC 84 SHO 75 PAS 74 DRI 75 DEF 66 PHY 77 CDM CAM ST R 3 ★ 5 CM 82.2 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 25% 75%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Olaru 73 CM PAC 84 SHO 75 PAS 73 DRI 75 DEF 66 PHY 77 CDM CAM ST R 3 ★ 5 CM 81.7 Olaru 74 CM PAC 84 SHO 75 PAS 74 DRI 75 DEF 66 PHY 77 CDM CAM ST R 3 ★ 5 CM 82.2 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 27% 73%</t>
         </is>
       </c>
     </row>
@@ -2375,12 +2375,12 @@
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] NEW</t>
+          <t>Shooting Practice [SP+ 28]</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] NEW Unlocked by reaching level 28 in the Premium Season Pass. Rahimi 78 ST PAC 87 SHO 78 PAS 71 DRI 79 DEF 38 PHY 68 RM LM RW LW R 4 ★ 4 LM 79.5 Rahimi 78 ST PAC 87 SHO 78 PAS 71 DRI 79 DEF 38 PHY 68 RM LM RW LW R 4 ★ 4 ST 81.3 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES 4 in 1 month in 1 month 83% 17%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Rahimi 78 ST PAC 87 SHO 78 PAS 71 DRI 79 DEF 38 PHY 68 RM LM RW LW R 4 ★ 4 LM 79.5 Rahimi 78 ST PAC 87 SHO 78 PAS 71 DRI 79 DEF 38 PHY 68 RM LM RW LW R 4 ★ 4 ST 81.3 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES 4 in 1 month in 1 month 83% 17%</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] NEW</t>
+          <t>Creative or Composed? [SP 27]</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] NEW Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] NEW</t>
+          <t>Winger Glow Up [SP+ 26]</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] NEW Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 83% 17%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 92% 8%</t>
         </is>
       </c>
     </row>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] NEW</t>
+          <t>Tactical Ascent [SP+ 14]</t>
         </is>
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] NEW Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 80% 20%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] NEW</t>
+          <t>Relentless [SP 11]</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] NEW Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 33% 67%</t>
         </is>
       </c>
     </row>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] NEW</t>
+          <t>Striker Glow Up [SP 7]</t>
         </is>
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] NEW Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 100% 0%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 91% 9%</t>
         </is>
       </c>
     </row>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] NEW</t>
+          <t>Midfield Polish [SP+ 1]</t>
         </is>
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] NEW Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 43% 57%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 89% 11%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 88% 12%</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Trimmel 75 RB PAC 61 SHO 65 PAS 74 DRI 68 DEF 74 PHY 79 RM R 3 ★ 3 RB 63.4 Trimmel 79 RB PAC 80 SHO 65 PAS 77 DRI 79 DEF 76 PHY 81 RM R 3 ★ 3 RB 76.7 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 92% 8%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Trimmel 75 RB PAC 61 SHO 65 PAS 74 DRI 68 DEF 74 PHY 79 RM R 3 ★ 3 RB 63.4 Trimmel 79 RB PAC 80 SHO 65 PAS 77 DRI 79 DEF 76 PHY 81 RM R 3 ★ 3 RB 76.7 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 93% 8%</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Antônia Silva 80 RB PAC 81 SHO 50 PAS 71 DRI 79 DEF 79 PHY 79 RM R 4 ★ 3 RB 75.5 Antônia Silva 80 RB PAC 81 SHO 50 PAS 71 DRI 79 DEF 79 PHY 79 RM R 4 ★ 3 RB 78.4 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES 4 in 1 year in 1 year 88% 12%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES 4 in 1 year in 1 year 89% 11%</t>
         </is>
       </c>
     </row>
@@ -10227,12 +10227,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pinged Pass NEW</t>
+          <t>Pinged Pass</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pinged Pass NEW Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
         </is>
       </c>
     </row>
@@ -10254,12 +10254,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Believe NEW</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Believe NEW Unlocked by completing the Ted Lasso's Masterclass objective Olaru 73 CM PAC 84 SHO 75 PAS 73 DRI 75 DEF 66 PHY 77 CDM CAM ST R 3 ★ 5 CM 81.7 Olaru 74 CM PAC 84 SHO 75 PAS 74 DRI 75 DEF 66 PHY 77 CDM CAM ST R 3 ★ 5 CM 82.2 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 25% 75%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Olaru 73 CM PAC 84 SHO 75 PAS 73 DRI 75 DEF 66 PHY 77 CDM CAM ST R 3 ★ 5 CM 81.7 Olaru 74 CM PAC 84 SHO 75 PAS 74 DRI 75 DEF 66 PHY 77 CDM CAM ST R 3 ★ 5 CM 82.2 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 27% 73%</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] NEW</t>
+          <t>Shooting Practice [SP+ 28]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] NEW Unlocked by reaching level 28 in the Premium Season Pass. Rahimi 78 ST PAC 87 SHO 78 PAS 71 DRI 79 DEF 38 PHY 68 RM LM RW LW R 4 ★ 4 LM 79.5 Rahimi 78 ST PAC 87 SHO 78 PAS 71 DRI 79 DEF 38 PHY 68 RM LM RW LW R 4 ★ 4 ST 81.3 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES 4 in 1 month in 1 month 83% 17%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Rahimi 78 ST PAC 87 SHO 78 PAS 71 DRI 79 DEF 38 PHY 68 RM LM RW LW R 4 ★ 4 LM 79.5 Rahimi 78 ST PAC 87 SHO 78 PAS 71 DRI 79 DEF 38 PHY 68 RM LM RW LW R 4 ★ 4 ST 81.3 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES 4 in 1 month in 1 month 83% 17%</t>
         </is>
       </c>
     </row>
@@ -10308,12 +10308,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] NEW</t>
+          <t>Creative or Composed? [SP 27]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] NEW Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
         </is>
       </c>
     </row>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] NEW</t>
+          <t>Winger Glow Up [SP+ 26]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] NEW Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 83% 17%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 92% 8%</t>
         </is>
       </c>
     </row>
@@ -10362,12 +10362,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] NEW</t>
+          <t>Tactical Ascent [SP+ 14]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] NEW Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 80% 20%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -10389,12 +10389,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] NEW</t>
+          <t>Relentless [SP 11]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] NEW Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 33% 67%</t>
         </is>
       </c>
     </row>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] NEW</t>
+          <t>Striker Glow Up [SP 7]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] NEW Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 100% 0%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 91% 9%</t>
         </is>
       </c>
     </row>
@@ -10443,12 +10443,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] NEW</t>
+          <t>Midfield Polish [SP+ 1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] NEW Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 43% 57%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16T20:06:04</t>
+          <t>2026-09-17T20:18:50</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA16"/>
+  <dimension ref="A1:DA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,59 +961,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 20 - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>LB, RB</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CB, CM</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>80</v>
-      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
@@ -1026,18 +1002,10 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>82</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
@@ -1074,60 +1042,24 @@
       <c r="BW2" t="inlineStr"/>
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>78</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>75</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>79</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>80</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>75</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>76</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>77</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>76</v>
-      </c>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
       <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="inlineStr"/>
@@ -1135,27 +1067,27 @@
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 Level 1 Bradley 79 RB PAC 79 SHO 62 PAS 71 DRI 75 DEF 76 PHY 73 RM R 3 ★ 3 Bradley 80 RB PAC 81 SHO 62 PAS 71 DRI 75 DEF 77 PHY 73 RM R 3 ★ 3 UPGRADES +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80</t>
+          <t>No upgrades Level 1 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Fullback Fork NEW</t>
+          <t>Ones to Watch Retro 20 NEW 25,000 200</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Fullback Fork NEW Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 10 days in 17 days 91% 9%</t>
+          <t>Ones to Watch Retro 20 NEW 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 19% 81%</t>
         </is>
       </c>
     </row>
@@ -1172,35 +1104,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 19 - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -1211,12 +1131,8 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>80</v>
-      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
@@ -1237,68 +1153,36 @@
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>78</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>77</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>78</v>
-      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>79</v>
-      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>78</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>77</v>
-      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>80</v>
-      </c>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>80</v>
-      </c>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="inlineStr"/>
@@ -1326,27 +1210,27 @@
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 Amanda Gutierres 79 ST PAC 73 SHO 78 PAS 62 DRI 74 DEF 37 PHY 77 R 3 ★ 4 Amanda Gutierres 80 ST PAC 73 SHO 78 PAS 63 DRI 74 DEF 37 PHY 77 R 3 ★ 4 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
+          <t>No upgrades Level 1 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2</t>
+          <t>Ones to Watch Retro 19 NEW 25,000 200</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 87% 13%</t>
+          <t>Ones to Watch Retro 19 NEW 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 12% 88%</t>
         </is>
       </c>
     </row>
@@ -1363,63 +1247,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Intro to Evolutions - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 18 - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>79</v>
-      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
@@ -1432,18 +1288,10 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>80</v>
-      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
@@ -1456,96 +1304,44 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>78</v>
-      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>76</v>
-      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>80</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>77</v>
-      </c>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>80</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>80</v>
-      </c>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>76</v>
-      </c>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
       <c r="CB4" t="inlineStr"/>
       <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>77</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>78</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>75</v>
-      </c>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
       <c r="CJ4" t="inlineStr"/>
       <c r="CK4" t="inlineStr"/>
-      <c r="CL4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>80</v>
-      </c>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
       <c r="CN4" t="inlineStr"/>
       <c r="CO4" t="inlineStr"/>
       <c r="CP4" t="inlineStr"/>
@@ -1554,34 +1350,30 @@
       <c r="CS4" t="inlineStr"/>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>RB Wingback +</t>
-        </is>
-      </c>
+      <c r="CV4" t="inlineStr"/>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Wolter 75 RB PAC 78 SHO 72 PAS 70 DRI 76 DEF 72 PHY 74 RM R 3 ★ 3 Wolter 79 RB PAC 79 SHO 72 PAS 71 DRI 76 DEF 74 PHY 74 RM R 3 ★ 3 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
+          <t>No upgrades Level 1 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>Intro to Evolutions</t>
+          <t>Ones to Watch Retro 18 NEW 25,000 200</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 92% 8%</t>
+          <t>Ones to Watch Retro 18 NEW 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 16% 84%</t>
         </is>
       </c>
     </row>
@@ -1598,43 +1390,59 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs - EA SPORTS FC 27</t>
+          <t>Fullback Fork - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
+          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>LB, RB</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CB, CM</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>80</v>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
@@ -1647,10 +1455,18 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>82</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>82</v>
+      </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
@@ -1687,56 +1503,88 @@
       <c r="BW5" t="inlineStr"/>
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
-      <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="inlineStr"/>
-      <c r="CK5" t="inlineStr"/>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
+      <c r="BZ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>78</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>75</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>79</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>80</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>80</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>75</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>76</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>77</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>76</v>
+      </c>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>RB Fullback +</t>
-        </is>
-      </c>
+      <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 90% of GG users upvoted this Evolution. Vote Now! 90% 10% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 UPGRADES RB Fullback +</t>
+          <t>B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 Level 1 Bradley 79 RB PAC 79 SHO 62 PAS 71 DRI 75 DEF 76 PHY 73 RM R 3 ★ 3 Bradley 80 RB PAC 81 SHO 62 PAS 71 DRI 75 DEF 77 PHY 73 RM R 3 ★ 3 UPGRADES +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs</t>
+          <t>Fullback Fork</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 77.6 Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 79.4 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 90% 10%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 9 days in 16 days 88% 12%</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1601,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LM, RM</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>LB, RB</t>
-        </is>
-      </c>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1791,20 +1635,16 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1818,98 +1658,78 @@
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>80</v>
-      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>78</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>78</v>
+      </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="BC6" t="n">
-        <v>84</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>78</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="BI6" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BK6" t="n">
-        <v>76</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>78</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>75</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BS6" t="n">
-        <v>73</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>74</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BW6" t="n">
-        <v>74</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>75</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
       <c r="CB6" t="inlineStr"/>
@@ -1922,52 +1742,40 @@
       <c r="CI6" t="inlineStr"/>
       <c r="CJ6" t="inlineStr"/>
       <c r="CK6" t="inlineStr"/>
-      <c r="CL6" t="n">
-        <v>15</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>78</v>
-      </c>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
       <c r="CN6" t="inlineStr"/>
       <c r="CO6" t="inlineStr"/>
       <c r="CP6" t="inlineStr"/>
       <c r="CQ6" t="inlineStr"/>
-      <c r="CR6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>3</v>
-      </c>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
       <c r="CV6" t="inlineStr"/>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Guiagon 74 LM PAC 71 SHO 70 PAS 70 DRI 78 DEF 26 PHY 59 CDM CM LW R 4 ★ 3 Guiagon 78 LM PAC 74 SHO 70 PAS 71 DRI 79 DEF 26 PHY 59 CDM CM LW R 4 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
+          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 Amanda Gutierres 79 ST PAC 73 SHO 78 PAS 62 DRI 74 DEF 37 PHY 77 R 3 ★ 4 Amanda Gutierres 80 ST PAC 73 SHO 78 PAS 63 DRI 74 DEF 37 PHY 77 R 3 ★ 4 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2</t>
+          <t>Intro to Repeatable Evolutions 2</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 1 month in 1 month 96% 4%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 85% 15%</t>
         </is>
       </c>
     </row>
@@ -1984,27 +1792,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
+          <t>Intro to Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2012,15 +1832,23 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>79</v>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
@@ -2033,10 +1861,18 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>80</v>
+      </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
@@ -2049,44 +1885,96 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>78</v>
+      </c>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
+      <c r="BH7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>76</v>
+      </c>
       <c r="BJ7" t="inlineStr"/>
       <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
+      <c r="BL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>80</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>77</v>
+      </c>
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
+      <c r="BT7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>80</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>80</v>
+      </c>
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr"/>
-      <c r="CA7" t="inlineStr"/>
+      <c r="BZ7" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>76</v>
+      </c>
       <c r="CB7" t="inlineStr"/>
       <c r="CC7" t="inlineStr"/>
-      <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr"/>
-      <c r="CH7" t="inlineStr"/>
-      <c r="CI7" t="inlineStr"/>
+      <c r="CD7" t="n">
+        <v>40</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>77</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>40</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>78</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>75</v>
+      </c>
       <c r="CJ7" t="inlineStr"/>
       <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" t="inlineStr"/>
+      <c r="CL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>80</v>
+      </c>
       <c r="CN7" t="inlineStr"/>
       <c r="CO7" t="inlineStr"/>
       <c r="CP7" t="inlineStr"/>
@@ -2095,63 +1983,71 @@
       <c r="CS7" t="inlineStr"/>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>RB Wingback +</t>
+        </is>
+      </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 90% of GG users upvoted this Evolution. Vote Now! 90% 10% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Mastantuono 80 RM PAC 80 SHO 78 PAS 79 DRI 83 DEF 53 PHY 70 CAM RW L 3 ★ 3 Mastantuono 80 RM PAC 80 SHO 78 PAS 79 DRI 83 DEF 53 PHY 70 CAM RW L 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Wolter 75 RB PAC 78 SHO 72 PAS 70 DRI 76 DEF 72 PHY 74 RM R 3 ★ 3 Wolter 79 RB PAC 79 SHO 72 PAS 71 DRI 76 DEF 74 PHY 74 RM R 3 ★ 3 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions</t>
+          <t>Intro to Evolutions</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pinged Pass - EA SPORTS FC 27</t>
+          <t>Intro to Training Camp EVOs - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -2161,11 +2057,7 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -2246,86 +2138,102 @@
       <c r="CS8" t="inlineStr"/>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>RB Fullback +</t>
+        </is>
+      </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES 3</t>
+          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 91% of GG users upvoted this Evolution. Vote Now! 91% 9% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 UPGRADES RB Fullback +</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>Pinged Pass</t>
+          <t>Intro to Training Camp EVOs</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 89% 11%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 77.6 Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 79.4 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>LM, RM</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>LB, RB</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -2339,10 +2247,18 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>80</v>
+      </c>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
@@ -2355,37 +2271,73 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>84</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>78</v>
+      </c>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BI9" t="n">
-        <v>83</v>
-      </c>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
-      <c r="BT9" t="inlineStr"/>
-      <c r="BU9" t="inlineStr"/>
-      <c r="BV9" t="inlineStr"/>
-      <c r="BW9" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>76</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>78</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>75</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>73</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>74</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>74</v>
+      </c>
       <c r="BX9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BY9" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="BZ9" t="inlineStr"/>
       <c r="CA9" t="inlineStr"/>
@@ -2399,77 +2351,85 @@
       <c r="CI9" t="inlineStr"/>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="inlineStr"/>
-      <c r="CL9" t="inlineStr"/>
-      <c r="CM9" t="inlineStr"/>
+      <c r="CL9" t="n">
+        <v>15</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>78</v>
+      </c>
       <c r="CN9" t="inlineStr"/>
       <c r="CO9" t="inlineStr"/>
       <c r="CP9" t="inlineStr"/>
       <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="inlineStr"/>
-      <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
+      <c r="CR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>3</v>
+      </c>
       <c r="CV9" t="inlineStr"/>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Marmoush 82 LW PAC 87 SHO 83 PAS 76 DRI 83 DEF 34 PHY 69 LM CAM ST R 4 ★ 3 Marmoush 83 LW PAC 87 SHO 83 PAS 77 DRI 83 DEF 34 PHY 69 LM CAM ST R 4 ★ 3 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
+          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Guiagon 74 LM PAC 71 SHO 70 PAS 70 DRI 78 DEF 26 PHY 59 CDM CM LW R 4 ★ 3 Guiagon 78 LM PAC 74 SHO 70 PAS 71 DRI 79 DEF 26 PHY 59 CDM CM LW R 4 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>Overall Max. 82 Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>Overall Max. 82 Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Repeat Delivery 2</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 30% 70%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 1 month in 1 month 96% 4%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
+          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>LW, RW, ST</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -2484,11 +2444,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -2571,27 +2527,27 @@
       <c r="CV10" t="inlineStr"/>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>A · B 4 Level 1 Dudinha 81 LM PAC 71 SHO 73 PAS 78 DRI 81 DEF 41 PHY 52 LW L 4 ★ 3 Dudinha 81 LM PAC 71 SHO 73 PAS 78 DRI 81 DEF 41 PHY 52 LW L 4 ★ 3 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 91% of GG users upvoted this Evolution. Vote Now! 91% 9% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Mastantuono 80 RM PAC 80 SHO 78 PAS 79 DRI 83 DEF 53 PHY 70 CAM RW L 3 ★ 3 Mastantuono 80 RM PAC 80 SHO 78 PAS 79 DRI 83 DEF 53 PHY 70 CAM RW L 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28]</t>
+          <t>Intro to Pathway Evolutions</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 71% 29%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2559,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
+          <t>Pinged Pass - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -2722,27 +2678,27 @@
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>A · B 3 Level 1 Mayulu 79 CM PAC 75 SHO 75 PAS 75 DRI 79 DEF 64 PHY 62 CDM CAM ST L 3 ★ 5 Mayulu 79 CM PAC 75 SHO 75 PAS 75 DRI 79 DEF 64 PHY 62 CDM CAM ST L 3 ★ 5 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27]</t>
+          <t>Pinged Pass</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 78% 22%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -2754,68 +2710,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LW</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>LB, ST</t>
-        </is>
-      </c>
+          <t>ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>83</v>
@@ -2832,121 +2768,53 @@
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>78</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>77</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>74</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>74</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>81</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>82</v>
-      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BI12" t="n">
-        <v>76</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>80</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>78</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>86</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>85</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>78</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>85</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW12" t="n">
+        <v>83</v>
+      </c>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY12" t="n">
         <v>84</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>80</v>
       </c>
       <c r="BZ12" t="inlineStr"/>
       <c r="CA12" t="inlineStr"/>
@@ -2960,48 +2828,40 @@
       <c r="CI12" t="inlineStr"/>
       <c r="CJ12" t="inlineStr"/>
       <c r="CK12" t="inlineStr"/>
-      <c r="CL12" t="n">
-        <v>10</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>72</v>
-      </c>
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
       <c r="CN12" t="inlineStr"/>
       <c r="CO12" t="inlineStr"/>
       <c r="CP12" t="inlineStr"/>
       <c r="CQ12" t="inlineStr"/>
-      <c r="CR12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>3</v>
-      </c>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Lang 79 LM PAC 80 SHO 77 PAS 73 DRI 84 DEF 50 PHY 68 LW R 5 ★ 3 Lang 83 LM PAC 80 SHO 78 PAS 73 DRI 84 DEF 50 PHY 68 LW R 5 ★ 3 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
+          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Marmoush 82 LW PAC 87 SHO 83 PAS 76 DRI 83 DEF 34 PHY 69 LM CAM ST R 4 ★ 3 Marmoush 83 LW PAC 87 SHO 83 PAS 77 DRI 83 DEF 34 PHY 69 LM CAM ST R 4 ★ 3 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 82 Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 82 Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26]</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 86% 14%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 27% 73%</t>
         </is>
       </c>
     </row>
@@ -3018,23 +2878,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
+          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LW, RW, ST</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -3046,10 +2910,14 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -3132,27 +3000,27 @@
       <c r="CV13" t="inlineStr"/>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>A · B 4 Level 1 Dudinha 81 LM PAC 71 SHO 73 PAS 78 DRI 81 DEF 41 PHY 52 LW L 4 ★ 3 Dudinha 81 LM PAC 71 SHO 73 PAS 78 DRI 81 DEF 41 PHY 52 LW L 4 ★ 3 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
         </is>
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14]</t>
+          <t>Shooting Practice [SP+ 28]</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 76% 24%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 80% 20%</t>
         </is>
       </c>
     </row>
@@ -3169,12 +3037,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
+          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -3283,27 +3151,27 @@
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="inlineStr">
         <is>
-          <t>3 Level 1 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 UPGRADES 3</t>
+          <t>A · B 3 Level 1 Mayulu 79 CM PAC 75 SHO 75 PAS 75 DRI 79 DEF 64 PHY 62 CDM CAM ST L 3 ★ 5 Mayulu 79 CM PAC 75 SHO 75 PAS 75 DRI 79 DEF 64 PHY 62 CDM CAM ST L 3 ★ 5 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
-          <t>Relentless [SP 11]</t>
+          <t>Creative or Composed? [SP 27]</t>
         </is>
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 25% 75%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 78% 22%</t>
         </is>
       </c>
     </row>
@@ -3315,42 +3183,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>CAM, CM</t>
+          <t>LB, ST</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -3363,7 +3231,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>3</t>
@@ -3375,7 +3247,7 @@
         <v>10</v>
       </c>
       <c r="Y15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -3390,113 +3262,117 @@
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP15" t="n">
         <v>10</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AQ15" t="n">
         <v>80</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AR15" t="n">
         <v>10</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AS15" t="n">
         <v>78</v>
       </c>
-      <c r="AP15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>82</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>83</v>
-      </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AZ15" t="n">
         <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
-        <v>70</v>
-      </c>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>82</v>
+      </c>
       <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="BJ15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BK15" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="BL15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BM15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BN15" t="n">
         <v>15</v>
       </c>
       <c r="BO15" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="BP15" t="n">
         <v>15</v>
       </c>
       <c r="BQ15" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="BR15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BS15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="BT15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BU15" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BW15" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BX15" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BY15" t="n">
         <v>80</v>
@@ -3511,50 +3387,50 @@
       <c r="CG15" t="inlineStr"/>
       <c r="CH15" t="inlineStr"/>
       <c r="CI15" t="inlineStr"/>
-      <c r="CJ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>78</v>
-      </c>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr"/>
       <c r="CL15" t="n">
         <v>10</v>
       </c>
       <c r="CM15" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="CN15" t="inlineStr"/>
       <c r="CO15" t="inlineStr"/>
       <c r="CP15" t="inlineStr"/>
       <c r="CQ15" t="inlineStr"/>
-      <c r="CR15" t="inlineStr"/>
-      <c r="CS15" t="inlineStr"/>
+      <c r="CR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>3</v>
+      </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="inlineStr"/>
       <c r="CW15" t="inlineStr">
         <is>
-          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 80 ST PAC 75 SHO 80 PAS 66 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
+          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Lang 79 LM PAC 80 SHO 77 PAS 73 DRI 84 DEF 50 PHY 68 LW R 5 ★ 3 Lang 83 LM PAC 80 SHO 78 PAS 73 DRI 84 DEF 50 PHY 68 LW R 5 ★ 3 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
         </is>
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7]</t>
+          <t>Winger Glow Up [SP+ 26]</t>
         </is>
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 81% 19%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3447,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -3587,16 +3463,8 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CM, CDM</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -3605,35 +3473,27 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>80</v>
-      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>79</v>
-      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>79</v>
-      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -3701,27 +3561,596 @@
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="inlineStr">
         <is>
+          <t>A · A 3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+        </is>
+      </c>
+      <c r="CX16" t="inlineStr">
+        <is>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CZ16" t="inlineStr">
+        <is>
+          <t>Tactical Ascent [SP+ 14]</t>
+        </is>
+      </c>
+      <c r="DA16" t="inlineStr">
+        <is>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 81% 19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="inlineStr"/>
+      <c r="CI17" t="inlineStr"/>
+      <c r="CJ17" t="inlineStr"/>
+      <c r="CK17" t="inlineStr"/>
+      <c r="CL17" t="inlineStr"/>
+      <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr">
+        <is>
+          <t>3 Level 1 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 UPGRADES 3</t>
+        </is>
+      </c>
+      <c r="CX17" t="inlineStr">
+        <is>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CZ17" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11]</t>
+        </is>
+      </c>
+      <c r="DA17" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 17% 83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CAM, CM</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>78</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>82</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>83</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>82</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>78</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>78</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>70</v>
+      </c>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>72</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>62</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>77</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>77</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>76</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>76</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>76</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr"/>
+      <c r="CH18" t="inlineStr"/>
+      <c r="CI18" t="inlineStr"/>
+      <c r="CJ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>78</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>10</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>67</v>
+      </c>
+      <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="inlineStr"/>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr"/>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 80 ST PAC 75 SHO 80 PAS 66 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
+        </is>
+      </c>
+      <c r="CX18" t="inlineStr">
+        <is>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CZ18" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7]</t>
+        </is>
+      </c>
+      <c r="DA18" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 81% 19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Premium Season Pass</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CM, CDM</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>79</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>79</v>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
+      <c r="CH19" t="inlineStr"/>
+      <c r="CI19" t="inlineStr"/>
+      <c r="CJ19" t="inlineStr"/>
+      <c r="CK19" t="inlineStr"/>
+      <c r="CL19" t="inlineStr"/>
+      <c r="CM19" t="inlineStr"/>
+      <c r="CN19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="inlineStr"/>
+      <c r="CQ19" t="inlineStr"/>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr"/>
+      <c r="CW19" t="inlineStr">
+        <is>
           <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Nildén 79 LB PAC 83 SHO 52 PAS 73 DRI 72 DEF 74 PHY 75 CDM L 3 ★ 3 Nildén 80 LB PAC 83 SHO 52 PAS 74 DRI 72 DEF 75 PHY 75 CDM L 3 ★ 3 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
         </is>
       </c>
-      <c r="CX16" t="inlineStr">
+      <c r="CX19" t="inlineStr">
         <is>
           <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CY16" t="inlineStr">
+      <c r="CY19" t="inlineStr">
         <is>
           <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
         </is>
       </c>
-      <c r="CZ16" t="inlineStr">
+      <c r="CZ19" t="inlineStr">
         <is>
           <t>Midfield Polish [SP+ 1]</t>
         </is>
       </c>
-      <c r="DA16" t="inlineStr">
-        <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 23% 77%</t>
+      <c r="DA19" t="inlineStr">
+        <is>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 22% 78%</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11061,17 +11490,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fullback Fork NEW</t>
+          <t>Ones to Watch Retro 20 NEW 25,000 200</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fullback Fork NEW Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 10 days in 17 days 91% 9%</t>
+          <t>Ones to Watch Retro 20 NEW 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 19% 81%</t>
         </is>
       </c>
     </row>
@@ -11088,17 +11517,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2</t>
+          <t>Ones to Watch Retro 19 NEW 25,000 200</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 87% 13%</t>
+          <t>Ones to Watch Retro 19 NEW 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 12% 88%</t>
         </is>
       </c>
     </row>
@@ -11115,17 +11544,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Intro to Evolutions</t>
+          <t>Ones to Watch Retro 18 NEW 25,000 200</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 92% 8%</t>
+          <t>Ones to Watch Retro 18 NEW 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 16% 84%</t>
         </is>
       </c>
     </row>
@@ -11142,17 +11571,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
+          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs</t>
+          <t>Fullback Fork</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 77.6 Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 79.4 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 90% 10%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 9 days in 16 days 88% 12%</t>
         </is>
       </c>
     </row>
@@ -11169,17 +11598,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2</t>
+          <t>Intro to Repeatable Evolutions 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 1 month in 1 month 96% 4%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 85% 15%</t>
         </is>
       </c>
     </row>
@@ -11196,98 +11625,98 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions</t>
+          <t>Intro to Evolutions</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pinged Pass</t>
+          <t>Intro to Training Camp EVOs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 89% 11%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 77.6 Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 79.4 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Repeat Delivery 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 30% 70%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 1 month in 1 month 96% 4%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28]</t>
+          <t>Intro to Pathway Evolutions</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 71% 29%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
@@ -11299,22 +11728,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27]</t>
+          <t>Pinged Pass</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 78% 22%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -11326,22 +11755,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26]</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 86% 14%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 27% 73%</t>
         </is>
       </c>
     </row>
@@ -11358,17 +11787,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14]</t>
+          <t>Shooting Practice [SP+ 28]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 76% 24%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 80% 20%</t>
         </is>
       </c>
     </row>
@@ -11385,17 +11814,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Relentless [SP 11]</t>
+          <t>Creative or Composed? [SP 27]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 25% 75%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 78% 22%</t>
         </is>
       </c>
     </row>
@@ -11407,22 +11836,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7]</t>
+          <t>Winger Glow Up [SP+ 26]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 81% 19%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -11439,17 +11868,98 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tactical Ascent [SP+ 14]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 81% 19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 17% 83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 81% 19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Premium Season Pass</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Midfield Polish [SP+ 1]</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 23% 77%</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 22% 78%</t>
         </is>
       </c>
     </row>
@@ -11495,7 +12005,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Reward_Count</t>
+          <t>Current_Count</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -11505,11 +12015,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Current_Count</t>
+          <t>Reward_Count</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -11520,7 +12030,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T19:35:04</t>
+          <t>2026-09-19T19:19:01</t>
         </is>
       </c>
     </row>
@@ -11543,7 +12053,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -1147,27 +1147,27 @@
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>A +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Vision 80 +7 Long Pass 78 +7 Reactions 80 +7 Ball Control 79 CAM Classic 10 + 3 Level 1 Tavernier 79 LM PAC 80 SHO 78 PAS 77 DRI 79 DEF 60 PHY 67 RM CM CAM RW LW L 3 ★ 3 Tavernier 81 LM PAC 82 SHO 78 PAS 77 DRI 79 DEF 60 PHY 67 RM CM CAM RW LW L 3 ★ 3 UPGRADES +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82</t>
+          <t>A +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Vision 80 +7 Long Pass 78 +7 Reactions 80 +7 Ball Control 79 CAM Classic 10 + 3 Level 1 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 Tanikawa 81 CAM PAC 76 SHO 77 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 UPGRADES +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Creative Crossroads NEW 15,000 150</t>
+          <t>Creative Crossroads 15,000 150</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Creative Crossroads NEW 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 10 days in 17 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 9 days in 16 days 51% 49%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 30 days Expiry in 30 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 30 days Expiry in 30 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 90.4 Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 91.0 REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 20% 80%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 30 days in 30 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
       <c r="CV4" t="inlineStr"/>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Hamm 93 ST PAC 92 SHO 93 PAS 86 DRI 92 DEF 54 PHY 81 CAM RW R 5 ★ 5 Hamm 93 ST PAC 92 SHO 93 PAS 86 DRI 92 DEF 54 PHY 81 CAM RW R 5 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 30 days Expiry in 30 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 30 days Expiry in 30 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 90.4 Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 91.0 REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 18% 82%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 30 days in 30 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -1576,17 +1576,17 @@
       <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Garrincha 93 RW PAC 90 SHO 87 PAS 92 DRI 95 DEF 40 PHY 66 RM R 5 ★ 4 Garrincha 93 RW PAC 90 SHO 87 PAS 92 DRI 95 DEF 40 PHY 66 RM R 5 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Pelé 95 CAM PAC 93 SHO 94 PAS 91 DRI 94 DEF 58 PHY 74 ST R 5 ★ 4 Pelé 95 CAM PAC 93 SHO 94 PAS 91 DRI 94 DEF 58 PHY 74 ST R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 30 days Expiry in 30 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 1 month Expiry in 1 month Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 30 days Expiry in 30 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 90.4 Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 91.0 REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 19% 81%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 30 days in 30 days 20% 80%</t>
         </is>
       </c>
     </row>
@@ -1787,17 +1787,17 @@
       <c r="CV6" t="inlineStr"/>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 Level 1 Rodriguez 79 LB PAC 70 SHO 54 PAS 75 DRI 67 DEF 79 PHY 63 LM L 3 ★ 3 Rodriguez 80 LB PAC 72 SHO 54 PAS 75 DRI 67 DEF 80 PHY 63 LM L 3 ★ 3 UPGRADES +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80</t>
+          <t>B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 Level 1 Svensson 79 LB PAC 75 SHO 60 PAS 76 DRI 77 DEF 75 PHY 75 LM LW L 3 ★ 4 Svensson 80 LB PAC 78 SHO 60 PAS 76 DRI 77 DEF 75 PHY 75 LM LW L 3 ★ 4 UPGRADES +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 8 days in 15 days 88% 12%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 7 days in 14 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       <c r="CV7" t="inlineStr"/>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 Clara Serrajordi 79 CM PAC 75 SHO 68 PAS 75 DRI 75 DEF 56 PHY 77 CAM ST R 3 ★ 3 Clara Serrajordi 80 CM PAC 75 SHO 68 PAS 75 DRI 75 DEF 56 PHY 77 CAM ST R 3 ★ 3 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
+          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 80 ST PAC 75 SHO 80 PAS 67 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 85% 15%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 84% 16%</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Smolčić 75 RB PAC 64 SHO 56 PAS 66 DRI 71 DEF 77 PHY 73 RM R 2 ★ 4 Smolčić 79 RB PAC 73 SHO 56 PAS 68 DRI 71 DEF 77 PHY 73 RM R 2 ★ 4 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
+          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Kumbedi 75 RB PAC 77 SHO 45 PAS 68 DRI 76 DEF 70 PHY 62 RM R 3 ★ 3 Kumbedi 79 RB PAC 79 SHO 45 PAS 69 DRI 76 DEF 72 PHY 62 RM R 3 ★ 3 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 92% of GG users upvoted this Evolution. Vote Now! 92% 8% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 De Almeida 80 CB PAC 74 SHO 34 PAS 64 DRI 61 DEF 81 PHY 82 RB CM R 2 ★ 2 De Almeida 80 CB PAC 74 SHO 34 PAS 64 DRI 61 DEF 81 PHY 82 RB CM R 2 ★ 2 UPGRADES RB Fullback +</t>
+          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 91% of GG users upvoted this Evolution. Vote Now! 91% 9% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 UPGRADES RB Fullback +</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 77.6 Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 79.4 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 92% 8%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 77.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.0 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       <c r="CV10" t="inlineStr"/>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Stanić 74 CAM PAC 71 SHO 70 PAS 74 DRI 75 DEF 49 PHY 70 CM LM LW R 4 ★ 4 Stanić 78 CAM PAC 74 SHO 70 PAS 74 DRI 75 DEF 49 PHY 70 CM LM LW R 4 ★ 4 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
+          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Guiagon 74 LM PAC 71 SHO 70 PAS 70 DRI 78 DEF 26 PHY 59 CDM CM LW R 4 ★ 3 Guiagon 78 LM PAC 74 SHO 70 PAS 71 DRI 79 DEF 26 PHY 59 CDM CM LW R 4 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
@@ -2750,7 +2750,7 @@
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 91% of GG users upvoted this Evolution. Vote Now! 91% 9% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 91% of GG users upvoted this Evolution. Vote Now! 91% 9% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades A 4 Level 1 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
         </is>
       </c>
       <c r="CX11" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 93% 7%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       <c r="CV13" t="inlineStr"/>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Bethune 82 CAM PAC 72 SHO 72 PAS 79 DRI 82 DEF 55 PHY 56 CDM CM ST L 4 ★ 4 Bethune 83 CAM PAC 72 SHO 72 PAS 79 DRI 82 DEF 55 PHY 56 CDM CM ST L 4 ★ 4 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
+          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Kofane 82 ST PAC 85 SHO 81 PAS 70 DRI 78 DEF 38 PHY 80 R 3 ★ 3 Kofane 83 ST PAC 85 SHO 81 PAS 71 DRI 78 DEF 38 PHY 80 R 3 ★ 3 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
         </is>
       </c>
       <c r="CX13" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 23% 77%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 32% 68%</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 82% 18%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 86% 14%</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 82% 18%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 87% 13%</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="inlineStr">
         <is>
-          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Ornella Vignola 78 LM PAC 82 SHO 70 PAS 74 DRI 77 DEF 58 PHY 77 RM LW R 4 ★ 3 Ornella Vignola 83 LM PAC 82 SHO 71 PAS 75 DRI 80 DEF 58 PHY 77 RM LW R 4 ★ 3 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
+          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Godts 78 LW PAC 83 SHO 72 PAS 71 DRI 84 DEF 42 PHY 65 LM R 4 ★ 3 Godts 83 LW PAC 83 SHO 72 PAS 72 DRI 84 DEF 42 PHY 65 LM R 4 ★ 3 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
         </is>
       </c>
       <c r="CX16" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 89% 11%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 86% 14%</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       <c r="CV17" t="inlineStr"/>
       <c r="CW17" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>A · A 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX17" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 83% 17%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 82% 18%</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       <c r="CV18" t="inlineStr"/>
       <c r="CW18" t="inlineStr">
         <is>
-          <t>3 Level 1 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 UPGRADES 3</t>
+          <t>3 Level 1 Sarr 79 CM PAC 66 SHO 66 PAS 77 DRI 79 DEF 78 PHY 74 CDM R 2 ★ 3 Sarr 79 CM PAC 66 SHO 66 PAS 77 DRI 79 DEF 78 PHY 74 CDM R 2 ★ 3 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX18" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 25% 75%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 38% 62%</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       <c r="CV19" t="inlineStr"/>
       <c r="CW19" t="inlineStr">
         <is>
-          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 80 ST PAC 75 SHO 80 PAS 66 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
+          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 Jackson 80 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
         </is>
       </c>
       <c r="CX19" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 86% 14%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 89% 11%</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       <c r="CV20" t="inlineStr"/>
       <c r="CW20" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Amrabat 79 CDM PAC 73 SHO 70 PAS 74 DRI 76 DEF 76 PHY 84 CM R 3 ★ 2 Amrabat 80 CDM PAC 73 SHO 70 PAS 75 DRI 76 DEF 77 PHY 84 CM R 3 ★ 2 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
+          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Jauregizar 79 CM PAC 75 SHO 72 PAS 76 DRI 77 DEF 78 PHY 80 CDM R 3 ★ 4 Jauregizar 80 CM PAC 75 SHO 72 PAS 77 DRI 77 DEF 79 PHY 80 CDM R 3 ★ 4 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
         </is>
       </c>
       <c r="CX20" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 25% 75%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 23% 77%</t>
         </is>
       </c>
     </row>
@@ -12657,12 +12657,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Creative Crossroads NEW 15,000 150</t>
+          <t>Creative Crossroads 15,000 150</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Creative Crossroads NEW 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 10 days in 17 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 9 days in 16 days 51% 49%</t>
         </is>
       </c>
     </row>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 90.4 Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 91.0 REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 20% 80%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 30 days in 30 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 90.4 Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 91.0 REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 18% 82%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 30 days in 30 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -12743,7 +12743,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 90.4 Patri Guijarro 88 CDM PAC 78 SHO 82 PAS 83 DRI 88 DEF 84 PHY 88 CM R 4 ★ 4 CM 91.0 REQUIREMENTS No requirements UPGRADES No upgrades in 1 month in 1 month 19% 81%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 30 days in 30 days 20% 80%</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 8 days in 15 days 88% 12%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 7 days in 14 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 85% 15%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 84% 16%</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 77.6 Johnston 78 RB PAC 82 SHO 59 PAS 73 DRI 72 DEF 73 PHY 80 RM R 2 ★ 3 RB 79.4 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 92% 8%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 77.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.0 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 93% 7%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 100% 0%</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 23% 77%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 32% 68%</t>
         </is>
       </c>
     </row>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 82% 18%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 86% 14%</t>
         </is>
       </c>
     </row>
@@ -13013,7 +13013,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 82% 18%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 87% 13%</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 89% 11%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 86% 14%</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 83% 17%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 82% 18%</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 25% 75%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 38% 62%</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 86% 14%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 89% 11%</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 25% 75%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 23% 77%</t>
         </is>
       </c>
     </row>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20T19:26:28</t>
+          <t>2026-09-21T21:02:38</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Midfield Glow Up NEW</t>
+          <t>Midfield Glow Up</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Midfield Glow Up NEW Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 30 days in 30 days 83% 17%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 29 days in 29 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 8 days in 15 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 7 days in 14 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 21% 79%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 19% 82%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 18% 82%</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 21% 79%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 6 days in 13 days 89% 11%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 5 days in 12 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 91% 9%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 90% 10%</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 91% of GG users upvoted this Evolution. Vote Now! 91% 9% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Di Guglielmo 80 RB PAC 90 SHO 41 PAS 71 DRI 71 DEF 75 PHY 65 LB R 2 ★ 3 Di Guglielmo 80 RB PAC 90 SHO 41 PAS 71 DRI 71 DEF 75 PHY 65 LB R 2 ★ 3 UPGRADES RB Fullback +</t>
+          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 90% of GG users upvoted this Evolution. Vote Now! 90% 10% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Di Guglielmo 80 RB PAC 90 SHO 41 PAS 71 DRI 71 DEF 75 PHY 65 LB R 2 ★ 3 Di Guglielmo 80 RB PAC 90 SHO 41 PAS 71 DRI 71 DEF 75 PHY 65 LB R 2 ★ 3 UPGRADES RB Fullback +</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 77.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.0 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 77.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.0 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 90% 10%</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 29 days in 29 days 94% 6%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 28 days in 28 days 94% 6%</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 90% of GG users upvoted this Evolution. Vote Now! 90% 10% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades A 4 Level 1 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 89% of GG users upvoted this Evolution. Vote Now! 89% 11% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 89% 11%</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 31% 69%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 33% 67%</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       <c r="CV15" t="inlineStr"/>
       <c r="CW15" t="inlineStr">
         <is>
-          <t>A · B 4 Level 1 England 81 ST PAC 61 SHO 83 PAS 72 DRI 78 DEF 42 PHY 72 CM CAM R 3 ★ 4 England 81 ST PAC 61 SHO 83 PAS 72 DRI 78 DEF 42 PHY 72 CM CAM R 3 ★ 4 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
+          <t>A · A 4 Level 1 England 81 ST PAC 61 SHO 83 PAS 72 DRI 78 DEF 42 PHY 72 CM CAM R 3 ★ 4 England 81 ST PAC 61 SHO 83 PAS 72 DRI 78 DEF 42 PHY 72 CM CAM R 3 ★ 4 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
         </is>
       </c>
       <c r="CX15" t="inlineStr">
@@ -3609,7 +3609,7 @@
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="inlineStr">
         <is>
-          <t>B · A 3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADE PATHS Pick one Option A 3 Option B Recommended 3</t>
+          <t>A · A 3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX16" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 88% 12%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 83% 17%</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 87% 13%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 89% 11%</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 84% 16%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 86% 14%</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 33% 67%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 38% 63%</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 88% 12%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 85% 15%</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 26% 74%</t>
         </is>
       </c>
     </row>
@@ -13875,12 +13875,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Midfield Glow Up NEW</t>
+          <t>Midfield Glow Up</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Midfield Glow Up NEW Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 30 days in 30 days 83% 17%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 29 days in 29 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 8 days in 15 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 7 days in 14 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 21% 79%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 19% 82%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 18% 82%</t>
         </is>
       </c>
     </row>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 21% 79%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 6 days in 13 days 89% 11%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 5 days in 12 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -14069,7 +14069,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 91% 9%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 90% 10%</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 77.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.0 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 91% 9%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 77.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.0 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 90% 10%</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14123,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 29 days in 29 days 94% 6%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 28 days in 28 days 94% 6%</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 89% 11%</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 31% 69%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 33% 67%</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 88% 12%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 83% 17%</t>
         </is>
       </c>
     </row>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 87% 13%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 89% 11%</t>
         </is>
       </c>
     </row>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 84% 16%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 86% 14%</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 33% 67%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 38% 63%</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 88% 12%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 85% 15%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 26% 74%</t>
         </is>
       </c>
     </row>
@@ -14464,7 +14464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22T20:11:14</t>
+          <t>2026-09-23T20:19:04</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -1160,12 +1160,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 29 days in 29 days 84% 16%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 28 days in 28 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 7 days in 14 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 6 days in 13 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 21% 79%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 20% 80%</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 18% 82%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 18% 82%</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 28 days Expiry in 28 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 21% 79%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 5 days in 12 days 89% 11%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 4 days in 11 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 28 days in 28 days 94% 6%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 27 days in 27 days 94% 6%</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 89% of GG users upvoted this Evolution. Vote Now! 89% 11% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 90% of GG users upvoted this Evolution. Vote Now! 90% 10% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 Damiani 80 ST PAC 78 SHO 80 PAS 70 DRI 78 DEF 43 PHY 87 CAM L 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 89% 11%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 90% 10%</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 95% 5%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 96% 4%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 86% 14%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 83% 17%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 85% 15%</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 89% 11%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 86% 14%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 87% 13%</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 38% 63%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 35% 65%</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 85% 15%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 26% 74%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 28% 72%</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 29 days in 29 days 84% 16%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 28 days in 28 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 7 days in 14 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 6 days in 13 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 21% 79%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 20% 80%</t>
         </is>
       </c>
     </row>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 18% 82%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 18% 82%</t>
         </is>
       </c>
     </row>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 28 days in 28 days 21% 79%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 5 days in 12 days 89% 11%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 4 days in 11 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14123,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 28 days in 28 days 94% 6%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 27 days in 27 days 94% 6%</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 89% 11%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 90% 10%</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 95% 5%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 96% 4%</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14231,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 86% 14%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 83% 17%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 85% 15%</t>
         </is>
       </c>
     </row>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 89% 11%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 90% 10%</t>
         </is>
       </c>
     </row>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 86% 14%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 87% 13%</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 38% 63%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 35% 65%</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 85% 15%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 26% 74%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 28% 72%</t>
         </is>
       </c>
     </row>
@@ -14464,7 +14464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23T20:19:04</t>
+          <t>2026-09-24T20:28:47</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -1040,24 +1040,12 @@
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>77</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>79</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>78</v>
-      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
@@ -1106,40 +1094,52 @@
       <c r="BQ2" t="n">
         <v>75</v>
       </c>
-      <c r="BR2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>78</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>78</v>
-      </c>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="inlineStr"/>
       <c r="BW2" t="inlineStr"/>
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr"/>
-      <c r="CA2" t="inlineStr"/>
+      <c r="BZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>78</v>
+      </c>
       <c r="CB2" t="inlineStr"/>
       <c r="CC2" t="inlineStr"/>
       <c r="CD2" t="inlineStr"/>
       <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="inlineStr"/>
-      <c r="CH2" t="inlineStr"/>
-      <c r="CI2" t="inlineStr"/>
+      <c r="CF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>78</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>77</v>
+      </c>
       <c r="CJ2" t="inlineStr"/>
       <c r="CK2" t="inlineStr"/>
       <c r="CL2" t="inlineStr"/>
       <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="inlineStr"/>
-      <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
+      <c r="CN2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>78</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>76</v>
+      </c>
       <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="inlineStr"/>
@@ -1147,27 +1147,27 @@
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>A +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Finishing 77 +5 Shot Power 79 +5 Long Shots 78 +5 Reactions 78 +5 Ball Control 78 3 Level 1 Angelina 79 CM PAC 72 SHO 70 PAS 78 DRI 79 DEF 65 PHY 68 CDM LM LW R 4 ★ 4 Angelina 80 CM PAC 74 SHO 70 PAS 79 DRI 79 DEF 65 PHY 68 CDM LM LW R 4 ★ 4 UPGRADES +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75</t>
+          <t>B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 Level 1 Ounahi 79 CM PAC 77 SHO 73 PAS 78 DRI 82 DEF 68 PHY 72 R 4 ★ 3 Ounahi 80 CM PAC 77 SHO 73 PAS 79 DRI 82 DEF 68 PHY 72 R 4 ★ 3 UPGRADES +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Pivot Shift NEW</t>
+          <t>Pivot Shift</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Pivot Shift NEW Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Cásseres Jr 76 CDM PAC 77 SHO 64 PAS 69 DRI 73 DEF 76 PHY 77 CM R 3 ★ 4 CDM 77.5 Cásseres Jr 80 CDM PAC 77 SHO 68 PAS 73 DRI 74 DEF 76 PHY 77 CM R 3 ★ 4 CDM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES A +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Finishing 77 +5 Shot Power 79 +5 Long Shots 78 +5 Reactions 78 +5 Ball Control 78 3 in 10 days in 17 days 24% 76%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Avdullahu 79 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 72 PHY 75 CM R 2 ★ 4 CDM 77.5 Avdullahu 80 CDM PAC 72 SHO 61 PAS 79 DRI 79 DEF 74 PHY 79 CM R 2 ★ 4 CDM 80.0 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 9 days in 16 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1370,17 @@
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 81 ST PAC 78 SHO 81 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES +5 OVR 81 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82</t>
+          <t>A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 Level 1 Amanda Gutierres 79 ST PAC 73 SHO 78 PAS 62 DRI 74 DEF 37 PHY 77 R 3 ★ 4 Amanda Gutierres 81 ST PAC 76 SHO 79 PAS 62 DRI 74 DEF 37 PHY 77 R 3 ★ 4 UPGRADES +5 OVR 81 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 79.0 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 9 days in 16 days 74% 26%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Paulinho 70 ST PAC 82 SHO 70 PAS 68 DRI 75 DEF 44 PHY 66 CAM RW L 4 ★ 3 ST 74.7 Paulinho 75 ST PAC 84 SHO 75 PAS 68 DRI 75 DEF 44 PHY 70 CAM RW L 4 ★ 3 ST 78.4 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 8 days in 15 days 73% 27%</t>
         </is>
       </c>
     </row>
@@ -1601,17 +1601,17 @@
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>+40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 Level 1 Louza 74 CM PAC 59 SHO 69 PAS 73 DRI 74 DEF 65 PHY 67 CDM L 4 ★ 3 Louza 79 CM PAC 59 SHO 69 PAS 74 DRI 74 DEF 68 PHY 75 CDM L 4 ★ 3 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77</t>
+          <t>+40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 Level 1 Guiagon 74 LM PAC 71 SHO 70 PAS 70 DRI 78 DEF 26 PHY 59 CDM CM LW R 4 ★ 3 Guiagon 79 LM PAC 71 SHO 70 PAS 73 DRI 78 DEF 38 PHY 66 CDM CM LW R 4 ★ 3 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 26 days in 26 days 84% 16%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 25 days in 25 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 Level 1 Berenguer 79 RW PAC 81 SHO 78 PAS 77 DRI 80 DEF 67 PHY 68 RM LM CAM LW R 3 ★ 4 Berenguer 81 RW PAC 82 SHO 78 PAS 77 DRI 80 DEF 67 PHY 68 RM LM CAM LW R 3 ★ 4 UPGRADES +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82</t>
+          <t>B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 Level 1 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 Tanikawa 81 CAM PAC 76 SHO 77 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 UPGRADES +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 3 days Expiry in 10 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 3 days Expiry in 10 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 4 days in 11 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 3 days in 10 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -1971,17 +1971,17 @@
       <c r="CV6" t="inlineStr"/>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Maradona 95 CAM PAC 90 SHO 91 PAS 91 DRI 96 DEF 40 PHY 77 ST L 5 ★ 3 Maradona 95 CAM PAC 90 SHO 91 PAS 91 DRI 96 DEF 40 PHY 77 ST L 5 ★ 3 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Cruyff 93 CAM PAC 90 SHO 91 PAS 90 DRI 94 DEF 42 PHY 73 ST R 5 ★ 5 Cruyff 93 CAM PAC 90 SHO 91 PAS 90 DRI 94 DEF 42 PHY 73 ST R 5 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 20% 80%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 20% 80%</t>
         </is>
       </c>
     </row>
@@ -2114,17 +2114,17 @@
       <c r="CV7" t="inlineStr"/>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Beckenbauer 93 CB PAC 82 SHO 73 PAS 88 DRI 84 DEF 93 PHY 83 CDM CM R 3 ★ 4 Beckenbauer 93 CB PAC 82 SHO 73 PAS 88 DRI 84 DEF 93 PHY 83 CDM CM R 3 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Pelé 95 CAM PAC 93 SHO 94 PAS 91 DRI 94 DEF 58 PHY 74 ST R 5 ★ 4 Pelé 95 CAM PAC 93 SHO 94 PAS 91 DRI 94 DEF 58 PHY 74 ST R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 17% 83%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -2257,17 +2257,17 @@
       <c r="CV8" t="inlineStr"/>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Garrincha 93 RW PAC 90 SHO 87 PAS 92 DRI 95 DEF 40 PHY 66 RM R 5 ★ 4 Garrincha 93 RW PAC 90 SHO 87 PAS 92 DRI 95 DEF 40 PHY 66 RM R 5 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 22% 78%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 22% 78%</t>
         </is>
       </c>
     </row>
@@ -2468,17 +2468,17 @@
       <c r="CV9" t="inlineStr"/>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 Level 1 Pickett 79 LB PAC 81 SHO 57 PAS 74 DRI 73 DEF 75 PHY 77 LM LW L 3 ★ 4 Pickett 80 LB PAC 82 SHO 57 PAS 74 DRI 73 DEF 76 PHY 77 LM LW L 3 ★ 4 UPGRADES +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80</t>
+          <t>B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 Level 1 Amad 79 RM PAC 83 SHO 75 PAS 74 DRI 83 DEF 54 PHY 53 RB RW L 4 ★ 4 Amad 80 RM PAC 85 SHO 75 PAS 74 DRI 83 DEF 56 PHY 53 RB RW L 4 ★ 4 UPGRADES +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 21 hours Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 21 hours Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 2 days in 9 days 89% 11%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.6 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 79.5 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 21 hours in 8 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       <c r="CV10" t="inlineStr"/>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 DeMelo 79 CM PAC 64 SHO 76 PAS 80 DRI 80 DEF 62 PHY 70 CAM ST R 4 ★ 3 DeMelo 80 CM PAC 64 SHO 76 PAS 80 DRI 80 DEF 62 PHY 70 CAM ST R 4 ★ 3 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
+          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 80 ST PAC 75 SHO 80 PAS 67 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 85% 16%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Esposito 76 ST PAC 78 SHO 78 PAS 78 DRI 77 DEF 50 PHY 72 CAM R 4 ★ 5 CAM 76.6 Esposito 77 ST PAC 78 SHO 78 PAS 78 DRI 79 DEF 50 PHY 72 CAM R 4 ★ 5 CAM 77.3 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 84% 16%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Endo 75 RB PAC 62 SHO 33 PAS 66 DRI 62 DEF 74 PHY 51 RM R 2 ★ 3 Endo 79 RB PAC 72 SHO 33 PAS 66 DRI 62 DEF 74 PHY 51 RM R 2 ★ 3 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
+          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Purtscheller 75 RM PAC 79 SHO 70 PAS 69 DRI 73 DEF 39 PHY 65 RB R 3 ★ 2 Purtscheller 79 RM PAC 79 SHO 70 PAS 70 DRI 74 DEF 51 PHY 65 RB R 3 ★ 2 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
         </is>
       </c>
       <c r="CX11" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 90% 10%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 88% of GG users upvoted this Evolution. Vote Now! 88% 12% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 UPGRADES RB Fullback +</t>
+          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 87% of GG users upvoted this Evolution. Vote Now! 87% 13% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Williams 80 RB PAC 79 SHO 50 PAS 72 DRI 72 DEF 78 PHY 65 RM RW R 3 ★ 3 Williams 80 RB PAC 79 SHO 50 PAS 72 DRI 72 DEF 78 PHY 65 RM RW R 3 ★ 3 UPGRADES RB Fullback +</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 77.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.0 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 88% 12%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Álex Jiménez 79 RB PAC 85 SHO 55 PAS 71 DRI 78 DEF 76 PHY 64 RM R 2 ★ 4 RB 76.9 Álex Jiménez 79 RB PAC 85 SHO 55 PAS 71 DRI 78 DEF 76 PHY 64 RM R 2 ★ 4 RB 78.3 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 87% 13%</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 25 days in 25 days 93% 7%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 24 days in 24 days 93% 7%</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Must Do 90% of GG users upvoted this Evolution. Vote Now! 90% 10% Completion Difficulty Easy Number of Games 1 Recommended Position RW Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Sears 80 RM PAC 89 SHO 72 PAS 75 DRI 78 DEF 44 PHY 68 RW R 3 ★ 3 Sears 80 RM PAC 89 SHO 72 PAS 75 DRI 78 DEF 44 PHY 68 RW R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 88% of GG users upvoted this Evolution. Vote Now! 88% 12% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX14" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.8 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 82.5 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       <c r="CV15" t="inlineStr"/>
       <c r="CW15" t="inlineStr">
         <is>
-          <t>3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES 3</t>
+          <t>3 Level 1 Mayulu 79 CM PAC 75 SHO 75 PAS 75 DRI 79 DEF 64 PHY 62 CDM CAM ST L 3 ★ 5 Mayulu 79 CM PAC 75 SHO 75 PAS 75 DRI 79 DEF 64 PHY 62 CDM CAM ST L 3 ★ 5 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX15" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 94% 6%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Vargas 78 LW PAC 87 SHO 72 PAS 73 DRI 80 DEF 56 PHY 67 LM CAM RW R 4 ★ 4 LM 80.0 Vargas 78 LW PAC 87 SHO 72 PAS 73 DRI 80 DEF 56 PHY 67 LM CAM RW R 4 ★ 4 LM 80.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 97% 3%</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="inlineStr">
         <is>
-          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Hugo Duro 82 ST PAC 78 SHO 83 PAS 74 DRI 79 DEF 55 PHY 81 L 3 ★ 4 Hugo Duro 83 ST PAC 78 SHO 83 PAS 75 DRI 79 DEF 55 PHY 81 L 3 ★ 4 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
+          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Igor Thiago 82 ST PAC 74 SHO 83 PAS 67 DRI 75 DEF 44 PHY 85 R 2 ★ 4 Igor Thiago 83 ST PAC 74 SHO 83 PAS 69 DRI 75 DEF 44 PHY 85 R 2 ★ 4 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
         </is>
       </c>
       <c r="CX16" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Rashford 82 LW PAC 92 SHO 83 PAS 78 DRI 81 DEF 33 PHY 68 LM ST R 5 ★ 3 ST 85.2 Rashford 83 LW PAC 92 SHO 83 PAS 80 DRI 81 DEF 33 PHY 68 LM ST R 5 ★ 3 ST 85.5 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       <c r="CV17" t="inlineStr"/>
       <c r="CW17" t="inlineStr">
         <is>
-          <t>A · A 4 Level 1 Svensson 81 LB PAC 77 SHO 62 PAS 78 DRI 81 DEF 77 PHY 77 LM LW L 3 ★ 4 Svensson 81 LB PAC 77 SHO 62 PAS 78 DRI 81 DEF 77 PHY 77 LM LW L 3 ★ 4 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
+          <t>B · A 4 Level 1 Lewis-Potter 81 LB PAC 81 SHO 74 PAS 78 DRI 82 DEF 76 PHY 70 RM LM RW LW R 3 ★ 4 Lewis-Potter 81 LB PAC 81 SHO 74 PAS 78 DRI 82 DEF 76 PHY 70 RM LM RW LW R 3 ★ 4 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX17" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 89% 11%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.8 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 82.7 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       <c r="CV18" t="inlineStr"/>
       <c r="CW18" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>A · A 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX18" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 75% 25%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 79.5 Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 81.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 76% 24%</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       <c r="CV19" t="inlineStr"/>
       <c r="CW19" t="inlineStr">
         <is>
-          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Schjelderup 80 LW PAC 81 SHO 75 PAS 75 DRI 82 DEF 42 PHY 59 LM R 3 ★ 4 Schjelderup 83 LW PAC 81 SHO 75 PAS 75 DRI 83 DEF 42 PHY 59 LM R 3 ★ 4 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
+          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Godts 78 LW PAC 83 SHO 72 PAS 71 DRI 84 DEF 42 PHY 65 LM R 4 ★ 3 Godts 83 LW PAC 83 SHO 72 PAS 72 DRI 84 DEF 42 PHY 65 LM R 4 ★ 3 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
         </is>
       </c>
       <c r="CX19" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 91% 9%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LM 71.7 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 82.0 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 91% 9%</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       <c r="CV20" t="inlineStr"/>
       <c r="CW20" t="inlineStr">
         <is>
-          <t>B · A 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADE PATHS Pick one Option A 3 Option B Recommended 3</t>
+          <t>A · A 3 Level 1 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX20" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 88% 12%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       <c r="CV21" t="inlineStr"/>
       <c r="CW21" t="inlineStr">
         <is>
-          <t>3 Level 1 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 UPGRADES 3</t>
+          <t>3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX21" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 30% 70%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Bertaccini 75 ST PAC 90 SHO 75 PAS 62 DRI 77 DEF 29 PHY 73 RM LM CAM RW LW R 2 ★ 4 ST 79.3 Bertaccini 75 ST PAC 90 SHO 75 PAS 62 DRI 77 DEF 29 PHY 73 RM LM CAM RW LW R 2 ★ 4 ST 79.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 36% 64%</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       <c r="CV22" t="inlineStr"/>
       <c r="CW22" t="inlineStr">
         <is>
-          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 Jackson 80 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
+          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Hoffmann 79 ST PAC 79 SHO 79 PAS 71 DRI 77 DEF 47 PHY 75 R 3 ★ 2 Hoffmann 80 ST PAC 79 SHO 79 PAS 71 DRI 77 DEF 47 PHY 75 R 3 ★ 2 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
         </is>
       </c>
       <c r="CX22" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="DA22" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 90% 10%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 89% 11%</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       <c r="CV23" t="inlineStr"/>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Sarr 79 CM PAC 66 SHO 66 PAS 77 DRI 79 DEF 78 PHY 74 CDM R 2 ★ 3 Sarr 80 CM PAC 66 SHO 66 PAS 78 DRI 79 DEF 79 PHY 74 CDM R 2 ★ 3 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
+          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Lucas Beraldo 79 CDM PAC 64 SHO 45 PAS 71 DRI 68 DEF 80 PHY 75 CB CM L 2 ★ 2 Lucas Beraldo 80 CDM PAC 64 SHO 45 PAS 72 DRI 68 DEF 80 PHY 75 CB CM L 2 ★ 2 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
         </is>
       </c>
       <c r="CX23" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="DA23" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Diks 77 CB PAC 79 SHO 67 PAS 70 DRI 72 DEF 77 PHY 78 RB LB CM R 3 ★ 4 CM 77.7 Diks 78 CB PAC 79 SHO 67 PAS 71 DRI 72 DEF 78 PHY 78 RB LB CM R 3 ★ 4 CM 78.3 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 28% 72%</t>
         </is>
       </c>
     </row>
@@ -5573,18 +5573,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Interceptions</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5 Finishing 77</t>
+          <t>+5 Interceptions 78</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5617,18 +5617,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shot Power</t>
+          <t>Standing Tackle</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+5 Shot Power 79</t>
+          <t>+5 Standing Tackle 78</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5661,18 +5661,18 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Long Shots</t>
+          <t>Sliding Tackle</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5 Long Shots 78</t>
+          <t>+5 Sliding Tackle 77</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5 Reactions 78</t>
+          <t>+5 Strength 78</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5749,18 +5749,18 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>Aggression</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5 Ball Control 78</t>
+          <t>+5 Aggression 76</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pivot Shift NEW</t>
+          <t>Pivot Shift</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pivot Shift NEW Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Cásseres Jr 76 CDM PAC 77 SHO 64 PAS 69 DRI 73 DEF 76 PHY 77 CM R 3 ★ 4 CDM 77.5 Cásseres Jr 80 CDM PAC 77 SHO 68 PAS 73 DRI 74 DEF 76 PHY 77 CM R 3 ★ 4 CDM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES A +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Finishing 77 +5 Shot Power 79 +5 Long Shots 78 +5 Reactions 78 +5 Ball Control 78 3 in 10 days in 17 days 24% 76%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Avdullahu 79 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 72 PHY 75 CM R 2 ★ 4 CDM 77.5 Avdullahu 80 CDM PAC 72 SHO 61 PAS 79 DRI 79 DEF 74 PHY 79 CM R 2 ★ 4 CDM 80.0 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 9 days in 16 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -16099,7 +16099,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 79.0 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 9 days in 16 days 74% 26%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Paulinho 70 ST PAC 82 SHO 70 PAS 68 DRI 75 DEF 44 PHY 66 CAM RW L 4 ★ 3 ST 74.7 Paulinho 75 ST PAC 84 SHO 75 PAS 68 DRI 75 DEF 44 PHY 70 CAM RW L 4 ★ 3 ST 78.4 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 8 days in 15 days 73% 27%</t>
         </is>
       </c>
     </row>
@@ -16126,7 +16126,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 65.7 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 80.6 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 26 days in 26 days 84% 16%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 25 days in 25 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Nebel 77 CAM PAC 75 SHO 74 PAS 72 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 76.7 Nebel 81 CAM PAC 80 SHO 78 PAS 73 DRI 81 DEF 49 PHY 60 CM R 4 ★ 4 CAM 80.9 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 4 days in 11 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 3 days in 10 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 20% 80%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 20% 80%</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16207,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 17% 83%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 Dumornay 89 LW PAC 93 SHO 86 PAS 81 DRI 91 DEF 62 PHY 75 LM CAM ST R 4 ★ 5 ST 93.3 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 22% 78%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 22% 78%</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.3 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 78.7 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 2 days in 9 days 89% 11%</t>
+          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.6 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 79.5 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 21 hours in 8 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Ioannidis 76 ST PAC 77 SHO 75 PAS 62 DRI 77 DEF 35 PHY 77 R 3 ★ 4 ST 76.3 Ioannidis 77 ST PAC 77 SHO 77 PAS 65 DRI 78 DEF 35 PHY 77 R 3 ★ 4 ST 77.1 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 85% 16%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Esposito 76 ST PAC 78 SHO 78 PAS 78 DRI 77 DEF 50 PHY 72 CAM R 4 ★ 5 CAM 76.6 Esposito 77 ST PAC 78 SHO 78 PAS 78 DRI 79 DEF 50 PHY 72 CAM R 4 ★ 5 CAM 77.3 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 84% 16%</t>
         </is>
       </c>
     </row>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 57.4 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 90% 10%</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 77.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.0 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 88% 12%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Álex Jiménez 79 RB PAC 85 SHO 55 PAS 71 DRI 78 DEF 76 PHY 64 RM R 2 ★ 4 RB 76.9 Álex Jiménez 79 RB PAC 85 SHO 55 PAS 71 DRI 78 DEF 76 PHY 64 RM R 2 ★ 4 RB 78.3 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 87% 13%</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 73.4 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 78.4 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 25 days in 25 days 93% 7%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 24 days in 24 days 93% 7%</t>
         </is>
       </c>
     </row>
@@ -16396,7 +16396,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 82.1 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.8 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 82.5 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
         </is>
       </c>
     </row>
@@ -16423,7 +16423,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 78.2 Javi Guerra 77 CM PAC 74 SHO 73 PAS 75 DRI 76 DEF 74 PHY 75 CDM CAM R 3 ★ 4 CM 79.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 94% 6%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Vargas 78 LW PAC 87 SHO 72 PAS 73 DRI 80 DEF 56 PHY 67 LM CAM RW R 4 ★ 4 LM 80.0 Vargas 78 LW PAC 87 SHO 72 PAS 73 DRI 80 DEF 56 PHY 67 LM CAM RW R 4 ★ 4 LM 80.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 97% 3%</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Kundananji 81 LM PAC 94 SHO 80 PAS 73 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.2 Kundananji 82 LM PAC 94 SHO 80 PAS 75 DRI 82 DEF 59 PHY 88 CAM ST LW R 4 ★ 5 LM 85.6 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Rashford 82 LW PAC 92 SHO 83 PAS 78 DRI 81 DEF 33 PHY 68 LM ST R 5 ★ 3 ST 85.2 Rashford 83 LW PAC 92 SHO 83 PAS 80 DRI 81 DEF 33 PHY 68 LM ST R 5 ★ 3 ST 85.5 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 80.1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.5 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES A · A 4 in 1 month in 1 month 89% 11%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.8 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 82.7 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16504,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 78.2 Sow 76 CM PAC 76 SHO 73 PAS 73 DRI 75 DEF 74 PHY 78 CDM R 3 ★ 4 CM 79.6 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 75% 25%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 79.5 Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 81.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 76% 24%</t>
         </is>
       </c>
     </row>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LW 70.5 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 81.5 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 91% 9%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LM 71.7 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 82.0 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 91% 9%</t>
         </is>
       </c>
     </row>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 77.3 Gorden 76 CB PAC 85 SHO 54 PAS 55 DRI 67 DEF 77 PHY 77 R 2 ★ 3 CB 80.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES B · A 3 in 1 month in 1 month 88% 12%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 88% 12%</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.3 Taylor 78 CM PAC 69 SHO 77 PAS 78 DRI 80 DEF 67 PHY 69 CDM L 3 ★ 5 CM 78.9 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 30% 70%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Bertaccini 75 ST PAC 90 SHO 75 PAS 62 DRI 77 DEF 29 PHY 73 RM LM CAM RW LW R 2 ★ 4 ST 79.3 Bertaccini 75 ST PAC 90 SHO 75 PAS 62 DRI 77 DEF 29 PHY 73 RM LM CAM RW LW R 2 ★ 4 ST 79.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 36% 64%</t>
         </is>
       </c>
     </row>
@@ -16612,7 +16612,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Mugoša 74 ST PAC 71 SHO 75 PAS 56 DRI 67 DEF 26 PHY 81 R 3 ★ 4 ST 69.8 Mugoša 80 ST PAC 78 SHO 81 PAS 62 DRI 75 DEF 26 PHY 81 R 3 ★ 4 ST 77.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 90% 10%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 89% 11%</t>
         </is>
       </c>
     </row>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Moreno 78 CDM PAC 81 SHO 68 PAS 73 DRI 76 DEF 76 PHY 77 CM R 4 ★ 3 CDM 78.9 Moreno 79 CDM PAC 81 SHO 68 PAS 74 DRI 76 DEF 77 PHY 77 CM R 4 ★ 3 CDM 79.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Diks 77 CB PAC 79 SHO 67 PAS 70 DRI 72 DEF 77 PHY 78 RB LB CM R 3 ★ 4 CM 77.7 Diks 78 CB PAC 79 SHO 67 PAS 71 DRI 72 DEF 78 PHY 78 RB LB CM R 3 ★ 4 CM 78.3 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 28% 72%</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26T19:49:46</t>
+          <t>2026-09-27T20:08:42</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -961,12 +961,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -979,19 +979,19 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CDM, CM</t>
+          <t>LM, LW</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ST, CAM, CB</t>
+          <t>ST, CDM, LB</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -1027,23 +1027,35 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AN2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>79</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>79</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>78</v>
+      </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -1054,92 +1066,84 @@
         <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="BD2" t="n">
         <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>78</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>80</v>
-      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
         <v>5</v>
       </c>
       <c r="BM2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="BN2" t="n">
         <v>5</v>
       </c>
       <c r="BO2" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="BP2" t="n">
         <v>5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>75</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BR2" t="n">
         <v>5</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="BS2" t="n">
         <v>78</v>
       </c>
+      <c r="BT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>79</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
       <c r="CB2" t="inlineStr"/>
       <c r="CC2" t="inlineStr"/>
       <c r="CD2" t="inlineStr"/>
       <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>78</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>77</v>
-      </c>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="inlineStr"/>
       <c r="CK2" t="inlineStr"/>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="n">
+      <c r="CL2" t="n">
         <v>5</v>
       </c>
-      <c r="CO2" t="n">
-        <v>78</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>76</v>
-      </c>
+      <c r="CM2" t="n">
+        <v>77</v>
+      </c>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
       <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="inlineStr"/>
@@ -1147,27 +1151,27 @@
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 Level 1 Ounahi 79 CM PAC 77 SHO 73 PAS 78 DRI 82 DEF 68 PHY 72 R 4 ★ 3 Ounahi 80 CM PAC 77 SHO 73 PAS 79 DRI 82 DEF 68 PHY 72 R 4 ★ 3 UPGRADES +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75</t>
+          <t>A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 Level 1 Holdt 79 CAM PAC 74 SHO 73 PAS 72 DRI 78 DEF 57 PHY 72 CM LM LW R 4 ★ 2 Holdt 80 CAM PAC 77 SHO 73 PAS 72 DRI 78 DEF 57 PHY 72 CM LM LW R 4 ★ 2 UPGRADES +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Pivot Shift</t>
+          <t>Flank Identity NEW</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Avdullahu 79 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 72 PHY 75 CM R 2 ★ 4 CDM 77.5 Avdullahu 80 CDM PAC 72 SHO 61 PAS 79 DRI 79 DEF 74 PHY 79 CM R 2 ★ 4 CDM 80.0 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 9 days in 16 days 26% 74%</t>
+          <t>Flank Identity NEW Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 10 days in 17 days 25% 75%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1188,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1202,19 +1206,19 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>CDM, CM</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CM, LM, RM</t>
+          <t>ST, CAM, CB</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -1235,7 +1239,7 @@
         <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -1250,147 +1254,147 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="n">
         <v>5</v>
       </c>
-      <c r="AM3" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN3" t="n">
+      <c r="BC3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD3" t="n">
         <v>5</v>
       </c>
-      <c r="AO3" t="n">
-        <v>82</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>78</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>81</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>78</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>82</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>82</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
+      <c r="BE3" t="n">
+        <v>76</v>
+      </c>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
+      <c r="BH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>75</v>
+      </c>
       <c r="BN3" t="n">
         <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="BP3" t="n">
         <v>5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>78</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>77</v>
-      </c>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
+      <c r="BZ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>78</v>
+      </c>
       <c r="CB3" t="inlineStr"/>
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="inlineStr"/>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
-      <c r="CI3" t="inlineStr"/>
+      <c r="CF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>78</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>77</v>
+      </c>
       <c r="CJ3" t="inlineStr"/>
       <c r="CK3" t="inlineStr"/>
       <c r="CL3" t="inlineStr"/>
       <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
+      <c r="CN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>78</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>76</v>
+      </c>
       <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>ST Advanced Forward +</t>
-        </is>
-      </c>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 Level 1 Amanda Gutierres 79 ST PAC 73 SHO 78 PAS 62 DRI 74 DEF 37 PHY 77 R 3 ★ 4 Amanda Gutierres 81 ST PAC 76 SHO 79 PAS 62 DRI 74 DEF 37 PHY 77 R 3 ★ 4 UPGRADES +5 OVR 81 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82</t>
+          <t>B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 Level 1 Ounahi 79 CM PAC 77 SHO 73 PAS 78 DRI 82 DEF 68 PHY 72 R 4 ★ 3 Ounahi 80 CM PAC 77 SHO 73 PAS 79 DRI 82 DEF 68 PHY 72 R 4 ★ 3 UPGRADES +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>Frontline Paradox</t>
+          <t>Pivot Shift</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Paulinho 70 ST PAC 82 SHO 70 PAS 68 DRI 75 DEF 44 PHY 66 CAM RW L 4 ★ 3 ST 74.7 Paulinho 75 ST PAC 84 SHO 75 PAS 68 DRI 75 DEF 44 PHY 70 CAM RW L 4 ★ 3 ST 78.4 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 8 days in 15 days 73% 27%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 8 days in 15 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -1407,30 +1411,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CAM, CB, ST</t>
+          <t>CM, LM, RM</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1455,10 +1459,10 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -1473,155 +1477,147 @@
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AN4" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>77</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>75</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>78</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>81</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>78</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>82</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>82</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>80</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>79</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>78</v>
+      </c>
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
+      <c r="BT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>78</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>77</v>
+      </c>
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>75</v>
-      </c>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
       <c r="CB4" t="inlineStr"/>
       <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>80</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>80</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>75</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>76</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>76</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>77</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>40</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>75</v>
-      </c>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
+      <c r="CT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>3</v>
+      </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>CDM Deep Lying Playmaker +; CDM Box Crasher +</t>
+          <t>ST Advanced Forward +</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>+40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 Level 1 Guiagon 74 LM PAC 71 SHO 70 PAS 70 DRI 78 DEF 26 PHY 59 CDM CM LW R 4 ★ 3 Guiagon 79 LM PAC 71 SHO 70 PAS 73 DRI 78 DEF 38 PHY 66 CDM CM LW R 4 ★ 3 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77</t>
+          <t>A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 Level 1 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 Gabriel Jesus 81 ST PAC 81 SHO 80 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 UPGRADES +5 OVR 81 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>Midfield Glow Up</t>
+          <t>Frontline Paradox</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 25 days in 25 days 84% 16%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 7 days in 14 days 75% 25%</t>
         </is>
       </c>
     </row>
@@ -1638,30 +1634,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CDM, ST</t>
+          <t>CAM, CB, ST</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1686,10 +1682,10 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="Y5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1704,151 +1700,155 @@
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="AO5" t="n">
-        <v>82</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>79</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>77</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>77</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>75</v>
+      </c>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="BI5" t="n">
-        <v>78</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>79</v>
+      </c>
       <c r="BL5" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="BM5" t="n">
-        <v>79</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>82</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>82</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr"/>
       <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>80</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>75</v>
+      </c>
       <c r="CB5" t="inlineStr"/>
       <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
-      <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="inlineStr"/>
-      <c r="CK5" t="inlineStr"/>
+      <c r="CD5" t="n">
+        <v>40</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>80</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>40</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>80</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>75</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>40</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>76</v>
+      </c>
       <c r="CL5" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="CM5" t="n">
+        <v>76</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>40</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>77</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>40</v>
+      </c>
+      <c r="CQ5" t="n">
         <v>75</v>
       </c>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>CAM Shadow Striker +</t>
+          <t>CDM Deep Lying Playmaker +; CDM Box Crasher +</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 Level 1 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 Tanikawa 81 CAM PAC 76 SHO 77 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 UPGRADES +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82</t>
+          <t>+40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 Level 1 Ana Velázquez 74 CDM PAC 77 SHO 38 PAS 61 DRI 58 DEF 71 PHY 63 CM R 2 ★ 3 Ana Velázquez 79 CDM PAC 77 SHO 38 PAS 65 DRI 58 DEF 73 PHY 75 CM R 2 ★ 3 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 3 days Expiry in 10 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 3 days Expiry in 10 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150</t>
+          <t>Midfield Glow Up</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 3 days in 10 days 52% 48%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 24 days in 24 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -1865,35 +1865,59 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CAM</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CDM, ST</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>81</v>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1906,20 +1930,48 @@
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>82</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>82</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>79</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>77</v>
+      </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
@@ -1928,24 +1980,48 @@
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
+      <c r="BH6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>78</v>
+      </c>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>79</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>82</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>82</v>
+      </c>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
+      <c r="BV6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>76</v>
+      </c>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
       <c r="CB6" t="inlineStr"/>
@@ -1958,8 +2034,12 @@
       <c r="CI6" t="inlineStr"/>
       <c r="CJ6" t="inlineStr"/>
       <c r="CK6" t="inlineStr"/>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
+      <c r="CL6" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>75</v>
+      </c>
       <c r="CN6" t="inlineStr"/>
       <c r="CO6" t="inlineStr"/>
       <c r="CP6" t="inlineStr"/>
@@ -1968,30 +2048,34 @@
       <c r="CS6" t="inlineStr"/>
       <c r="CT6" t="inlineStr"/>
       <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>CAM Shadow Striker +</t>
+        </is>
+      </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Cruyff 93 CAM PAC 90 SHO 91 PAS 90 DRI 94 DEF 42 PHY 73 ST R 5 ★ 5 Cruyff 93 CAM PAC 90 SHO 91 PAS 90 DRI 94 DEF 42 PHY 73 ST R 5 ★ 5 UPGRADES No upgrades</t>
+          <t>B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 Level 1 Konstantelias 79 CAM PAC 80 SHO 69 PAS 76 DRI 84 DEF 38 PHY 63 CM LM LW R 4 ★ 4 Konstantelias 81 CAM PAC 82 SHO 70 PAS 76 DRI 84 DEF 38 PHY 63 CM LM LW R 4 ★ 4 UPGRADES +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200</t>
+          <t>Creative Crossroads 15,000 150</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 20% 80%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 2 days in 9 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2092,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 20 - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
+          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -2114,27 +2198,27 @@
       <c r="CV7" t="inlineStr"/>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Pelé 95 CAM PAC 93 SHO 94 PAS 91 DRI 94 DEF 58 PHY 74 ST R 5 ★ 4 Pelé 95 CAM PAC 93 SHO 94 PAS 91 DRI 94 DEF 58 PHY 74 ST R 5 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Ronaldo 94 ST PAC 94 SHO 94 PAS 79 DRI 94 DEF 43 PHY 75 R 5 ★ 5 Ronaldo 94 ST PAC 94 SHO 94 PAS 79 DRI 94 DEF 43 PHY 75 R 5 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200</t>
+          <t>Ones to Watch Retro 20 25,000 200</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 16% 84%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2235,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 19 - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
+          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -2262,22 +2346,22 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost 25,000 Points Cost 200</t>
+          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200</t>
+          <t>Ones to Watch Retro 19 25,000 200</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 22% 78%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -2294,59 +2378,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 18 - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>LB, RB</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>CB, CM</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>80</v>
-      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
@@ -2359,18 +2419,10 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>82</v>
-      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
@@ -2407,60 +2459,24 @@
       <c r="BW9" t="inlineStr"/>
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>78</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>75</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>79</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>80</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>80</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>75</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>76</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>77</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>5</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>76</v>
-      </c>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
       <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="inlineStr"/>
@@ -2468,27 +2484,27 @@
       <c r="CV9" t="inlineStr"/>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 Level 1 Amad 79 RM PAC 83 SHO 75 PAS 74 DRI 83 DEF 54 PHY 53 RB RW L 4 ★ 4 Amad 80 RM PAC 85 SHO 75 PAS 74 DRI 83 DEF 56 PHY 53 RB RW L 4 ★ 4 UPGRADES +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80</t>
+          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 21 hours Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 21 hours Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>Fullback Fork</t>
+          <t>Ones to Watch Retro 18 25,000 200</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.6 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 79.5 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 21 hours in 8 days 89% 11%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2695,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Esposito 76 ST PAC 78 SHO 78 PAS 78 DRI 77 DEF 50 PHY 72 CAM R 4 ★ 5 CAM 76.6 Esposito 77 ST PAC 78 SHO 78 PAS 78 DRI 79 DEF 50 PHY 72 CAM R 4 ★ 5 CAM 77.3 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 84% 16%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.3 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.5 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 82% 18%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2910,7 @@
       </c>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Purtscheller 75 RM PAC 79 SHO 70 PAS 69 DRI 73 DEF 39 PHY 65 RB R 3 ★ 2 Purtscheller 79 RM PAC 79 SHO 70 PAS 70 DRI 74 DEF 51 PHY 65 RB R 3 ★ 2 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
+          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Merino Gonzalez 75 RB PAC 75 SHO 65 PAS 68 DRI 70 DEF 72 PHY 61 RM R 2 ★ 2 Merino Gonzalez 79 RB PAC 77 SHO 65 PAS 69 DRI 71 DEF 73 PHY 61 RM R 2 ★ 2 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
         </is>
       </c>
       <c r="CX11" t="inlineStr">
@@ -2914,7 +2930,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 89% 11%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3065,7 @@
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 87% of GG users upvoted this Evolution. Vote Now! 87% 13% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Williams 80 RB PAC 79 SHO 50 PAS 72 DRI 72 DEF 78 PHY 65 RM RW R 3 ★ 3 Williams 80 RB PAC 79 SHO 50 PAS 72 DRI 72 DEF 78 PHY 65 RM RW R 3 ★ 3 UPGRADES RB Fullback +</t>
+          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 85% of GG users upvoted this Evolution. Vote Now! 85% 15% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 De Almeida 80 CB PAC 74 SHO 34 PAS 64 DRI 61 DEF 81 PHY 82 RB CM R 2 ★ 2 De Almeida 80 CB PAC 74 SHO 34 PAS 64 DRI 61 DEF 81 PHY 82 RB CM R 2 ★ 2 UPGRADES RB Fullback +</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
@@ -3069,7 +3085,7 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Álex Jiménez 79 RB PAC 85 SHO 55 PAS 71 DRI 78 DEF 76 PHY 64 RM R 2 ★ 4 RB 76.9 Álex Jiménez 79 RB PAC 85 SHO 55 PAS 71 DRI 78 DEF 76 PHY 64 RM R 2 ★ 4 RB 78.3 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 87% 13%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 85% 15%</t>
         </is>
       </c>
     </row>
@@ -3280,17 +3296,17 @@
       <c r="CV13" t="inlineStr"/>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Moses 74 CM PAC 75 SHO 64 PAS 70 DRI 74 DEF 70 PHY 74 CDM RM R 2 ★ 3 Moses 78 CM PAC 78 SHO 64 PAS 70 DRI 74 DEF 70 PHY 74 CDM RM R 2 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
+          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Mateus Mané 74 CAM PAC 77 SHO 70 PAS 74 DRI 76 DEF 51 PHY 64 RM CM LM RW LW R 3 ★ 3 Mateus Mané 78 CAM PAC 79 SHO 70 PAS 75 DRI 76 DEF 51 PHY 64 RM CM LM RW LW R 3 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
         </is>
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 23 days Expiry in 23 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 23 days Expiry in 23 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
@@ -3300,7 +3316,7 @@
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 24 days in 24 days 93% 7%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 23 days in 23 days 92% 8%</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3447,7 @@
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 88% of GG users upvoted this Evolution. Vote Now! 88% 12% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 88% of GG users upvoted this Evolution. Vote Now! 88% 12% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX14" t="inlineStr">
@@ -3451,7 +3467,7 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.8 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 82.5 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3598,7 @@
       <c r="CV15" t="inlineStr"/>
       <c r="CW15" t="inlineStr">
         <is>
-          <t>3 Level 1 Mayulu 79 CM PAC 75 SHO 75 PAS 75 DRI 79 DEF 64 PHY 62 CDM CAM ST L 3 ★ 5 Mayulu 79 CM PAC 75 SHO 75 PAS 75 DRI 79 DEF 64 PHY 62 CDM CAM ST L 3 ★ 5 UPGRADES 3</t>
+          <t>3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX15" t="inlineStr">
@@ -3602,7 +3618,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Vargas 78 LW PAC 87 SHO 72 PAS 73 DRI 80 DEF 56 PHY 67 LM CAM RW R 4 ★ 4 LM 80.0 Vargas 78 LW PAC 87 SHO 72 PAS 73 DRI 80 DEF 56 PHY 67 LM CAM RW R 4 ★ 4 LM 80.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 97% 3%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 94% 6%</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3761,7 @@
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="inlineStr">
         <is>
-          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Igor Thiago 82 ST PAC 74 SHO 83 PAS 67 DRI 75 DEF 44 PHY 85 R 2 ★ 4 Igor Thiago 83 ST PAC 74 SHO 83 PAS 69 DRI 75 DEF 44 PHY 85 R 2 ★ 4 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
+          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Kofane 82 ST PAC 85 SHO 81 PAS 70 DRI 78 DEF 38 PHY 80 R 3 ★ 3 Kofane 83 ST PAC 85 SHO 81 PAS 71 DRI 78 DEF 38 PHY 80 R 3 ★ 3 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
         </is>
       </c>
       <c r="CX16" t="inlineStr">
@@ -3765,7 +3781,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Rashford 82 LW PAC 92 SHO 83 PAS 78 DRI 81 DEF 33 PHY 68 LM ST R 5 ★ 3 ST 85.2 Rashford 83 LW PAC 92 SHO 83 PAS 80 DRI 81 DEF 33 PHY 68 LM ST R 5 ★ 3 ST 85.5 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3920,7 @@
       <c r="CV17" t="inlineStr"/>
       <c r="CW17" t="inlineStr">
         <is>
-          <t>B · A 4 Level 1 Lewis-Potter 81 LB PAC 81 SHO 74 PAS 78 DRI 82 DEF 76 PHY 70 RM LM RW LW R 3 ★ 4 Lewis-Potter 81 LB PAC 81 SHO 74 PAS 78 DRI 82 DEF 76 PHY 70 RM LM RW LW R 3 ★ 4 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>B · A 4 Level 1 Svensson 81 LB PAC 77 SHO 62 PAS 78 DRI 81 DEF 77 PHY 77 LM LW L 3 ★ 4 Svensson 81 LB PAC 77 SHO 62 PAS 78 DRI 81 DEF 77 PHY 77 LM LW L 3 ★ 4 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX17" t="inlineStr">
@@ -3924,7 +3940,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.8 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 82.7 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 1 month in 1 month 88% 12%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 1 month in 1 month 89% 11%</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4091,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 79.5 Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 81.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 76% 24%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 76% 24%</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4330,7 @@
       <c r="CV19" t="inlineStr"/>
       <c r="CW19" t="inlineStr">
         <is>
-          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Godts 78 LW PAC 83 SHO 72 PAS 71 DRI 84 DEF 42 PHY 65 LM R 4 ★ 3 Godts 83 LW PAC 83 SHO 72 PAS 72 DRI 84 DEF 42 PHY 65 LM R 4 ★ 3 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
+          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Zicai 78 LW PAC 77 SHO 76 PAS 74 DRI 79 DEF 51 PHY 66 LM R 4 ★ 4 Zicai 83 LW PAC 77 SHO 76 PAS 74 DRI 81 DEF 51 PHY 66 LM R 4 ★ 4 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
         </is>
       </c>
       <c r="CX19" t="inlineStr">
@@ -4334,7 +4350,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LM 71.7 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 82.0 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 91% 9%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 92% 8%</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4481,7 @@
       <c r="CV20" t="inlineStr"/>
       <c r="CW20" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>A · A 3 Level 1 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX20" t="inlineStr">
@@ -4616,7 +4632,7 @@
       <c r="CV21" t="inlineStr"/>
       <c r="CW21" t="inlineStr">
         <is>
-          <t>3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADES 3</t>
+          <t>3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX21" t="inlineStr">
@@ -4636,7 +4652,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Bertaccini 75 ST PAC 90 SHO 75 PAS 62 DRI 77 DEF 29 PHY 73 RM LM CAM RW LW R 2 ★ 4 ST 79.3 Bertaccini 75 ST PAC 90 SHO 75 PAS 62 DRI 77 DEF 29 PHY 73 RM LM CAM RW LW R 2 ★ 4 ST 79.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 36% 64%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 35% 65%</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5050,7 @@
       <c r="CV23" t="inlineStr"/>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Lucas Beraldo 79 CDM PAC 64 SHO 45 PAS 71 DRI 68 DEF 80 PHY 75 CB CM L 2 ★ 2 Lucas Beraldo 80 CDM PAC 64 SHO 45 PAS 72 DRI 68 DEF 80 PHY 75 CB CM L 2 ★ 2 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
+          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Morton 79 CDM PAC 65 SHO 65 PAS 80 DRI 77 DEF 74 PHY 74 CM R 3 ★ 3 Morton 80 CDM PAC 65 SHO 65 PAS 80 DRI 77 DEF 75 PHY 74 CM R 3 ★ 3 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
         </is>
       </c>
       <c r="CX23" t="inlineStr">
@@ -5054,7 +5070,7 @@
       </c>
       <c r="DA23" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Diks 77 CB PAC 79 SHO 67 PAS 70 DRI 72 DEF 77 PHY 78 RB LB CM R 3 ★ 4 CM 77.7 Diks 78 CB PAC 79 SHO 67 PAS 71 DRI 72 DEF 78 PHY 78 RB LB CM R 3 ★ 4 CM 78.3 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 28% 72%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5149,7 +5165,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5164,7 +5180,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5181,19 +5197,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3 Sprint Speed 75</t>
+          <t>+5 Sprint Speed 83</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5208,7 +5224,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5221,23 +5237,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5 Crossing 76</t>
+          <t>+5 Agility 82</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5252,7 +5268,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5265,23 +5281,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Reactions</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5 Long Pass 80</t>
+          <t>+5 Reactions 78</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5296,7 +5312,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5309,23 +5325,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+5 Agility 75</t>
+          <t>+5 Dribbling 80</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5340,7 +5356,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5353,23 +5369,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3 Acceleration 75</t>
+          <t>+5 Stamina 77</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5384,7 +5400,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5397,23 +5413,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5 Vision 80</t>
+          <t>+5 Acceleration 83</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5428,7 +5444,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5441,23 +5457,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+5 Short Pass 78</t>
+          <t>+5 Positioning 79</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5472,7 +5488,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5485,23 +5501,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5 Curve 75</t>
+          <t>+5 Balance 80</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5516,7 +5532,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5529,23 +5545,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Ball Control</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5 Balance 75</t>
+          <t>+5 Ball Control 79</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5560,7 +5576,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5573,23 +5589,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Interceptions</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5 Interceptions 78</t>
+          <t>+5 Composure 76</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5604,7 +5620,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5617,23 +5633,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Standing Tackle</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+5 Standing Tackle 78</t>
+          <t>+4 Finishing 79</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5648,7 +5664,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5661,23 +5677,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sliding Tackle</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5 Sliding Tackle 77</t>
+          <t>+4 Shot Power 78</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5692,7 +5708,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5705,23 +5721,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+5 Strength 78</t>
+          <t>+5 Vision 77</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5736,7 +5752,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5749,23 +5765,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aggression</t>
+          <t>Crossing</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+5 Aggression 76</t>
+          <t>+5 Crossing 79</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5780,7 +5796,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5788,28 +5804,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5 OVR 81</t>
+          <t>+5 Curve 78</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5824,7 +5840,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -5832,28 +5848,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1 WF 3</t>
+          <t>+5 OVR 80</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5868,7 +5884,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -5885,19 +5901,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+5 Sprint Speed 82</t>
+          <t>+3 Sprint Speed 75</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5912,7 +5928,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -5925,23 +5941,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Crossing</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+5 Finishing 81</t>
+          <t>+5 Crossing 76</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5956,7 +5972,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -5969,23 +5985,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Long Shots</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+5 Long Shots 78</t>
+          <t>+5 Long Pass 80</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6000,7 +6016,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6013,23 +6029,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Penalties</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+5 Penalties 82</t>
+          <t>+5 Agility 75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6044,7 +6060,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6061,19 +6077,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+5 Acceleration 82</t>
+          <t>+3 Acceleration 75</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6088,7 +6104,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6101,23 +6117,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+5 Positioning 78</t>
+          <t>+5 Vision 80</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6132,7 +6148,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6145,23 +6161,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shot Power</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+5 Shot Power 80</t>
+          <t>+5 Short Pass 78</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6176,7 +6192,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6189,23 +6205,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Volleys</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+5 Volleys 82</t>
+          <t>+5 Curve 75</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -6220,7 +6236,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6233,23 +6249,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+5 Agility 78</t>
+          <t>+5 Balance 75</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6264,7 +6280,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6293,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Interceptions</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -6288,12 +6304,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+5 Balance 78</t>
+          <t>+5 Interceptions 78</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -6308,7 +6324,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6337,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>Standing Tackle</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -6332,12 +6348,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+5 Ball Control 78</t>
+          <t>+5 Standing Tackle 78</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6352,7 +6368,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6381,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Sliding Tackle</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -6376,12 +6392,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+5 Dribbling 77</t>
+          <t>+5 Sliding Tackle 77</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6396,7 +6412,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6404,28 +6420,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+40 OVR 79</t>
+          <t>+5 Strength 78</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6440,7 +6456,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6453,23 +6469,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Aggression</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+50 Vision 77</t>
+          <t>+5 Aggression 76</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6484,7 +6500,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -6492,28 +6508,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+50 Long Pass 79</t>
+          <t>+5 OVR 81</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6528,7 +6544,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6536,28 +6552,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Standing Tackle</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+40 Standing Tackle 80</t>
+          <t>+1 WF 3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6572,7 +6588,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6585,23 +6601,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+40 Strength 77</t>
+          <t>+5 Sprint Speed 82</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6616,7 +6632,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6629,23 +6645,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+50 Crossing 75</t>
+          <t>+5 Finishing 81</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6660,7 +6676,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6673,23 +6689,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Long Shots</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+50 Curve 75</t>
+          <t>+5 Long Shots 78</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6704,7 +6720,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6717,23 +6733,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sliding Tackle</t>
+          <t>Penalties</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+40 Sliding Tackle 75</t>
+          <t>+5 Penalties 82</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6748,7 +6764,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6761,23 +6777,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Aggression</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+40 Aggression 75</t>
+          <t>+5 Acceleration 82</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6792,7 +6808,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6805,23 +6821,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+40 Acceleration 75</t>
+          <t>+5 Positioning 78</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6836,7 +6852,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6849,23 +6865,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fk Accuracy</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+50 Fk Accuracy 74</t>
+          <t>+5 Shot Power 80</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6880,7 +6896,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6893,23 +6909,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Interceptions</t>
+          <t>Volleys</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+40 Interceptions 75</t>
+          <t>+5 Volleys 82</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6924,7 +6940,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6937,23 +6953,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jumping</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+40 Jumping 76</t>
+          <t>+5 Agility 78</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6968,7 +6984,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -6981,23 +6997,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+40 Sprint Speed 75</t>
+          <t>+5 Balance 78</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7012,7 +7028,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -7025,23 +7041,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Ball Control</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+50 Short Pass 80</t>
+          <t>+5 Ball Control 78</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7056,7 +7072,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -7069,23 +7085,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Defensive Awareness</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+40 Defensive Awareness 80</t>
+          <t>+5 Dribbling 77</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7100,7 +7116,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -7108,23 +7124,23 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>40</v>
       </c>
       <c r="E47" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+40 Stamina 76</t>
+          <t>+40 OVR 79</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7152,28 +7168,28 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E48" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+5 OVR 81</t>
+          <t>+50 Vision 77</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7188,7 +7204,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7201,23 +7217,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E49" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+7 Sprint Speed 82</t>
+          <t>+50 Long Pass 79</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7232,7 +7248,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7245,23 +7261,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Shot Power</t>
+          <t>Standing Tackle</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E50" t="n">
         <v>80</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+7 Shot Power 80</t>
+          <t>+40 Standing Tackle 80</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7276,7 +7292,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7289,23 +7305,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fk Accuracy</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E51" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+7 Fk Accuracy 80</t>
+          <t>+40 Strength 77</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7320,7 +7336,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7333,23 +7349,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Crossing</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+7 Curve 79</t>
+          <t>+50 Crossing 75</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7364,7 +7380,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7377,23 +7393,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E53" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+7 Balance 82</t>
+          <t>+50 Curve 75</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -7408,7 +7424,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7421,23 +7437,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Sliding Tackle</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E54" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>+7 Acceleration 82</t>
+          <t>+40 Sliding Tackle 75</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7452,7 +7468,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7465,23 +7481,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Aggression</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E55" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+7 Positioning 79</t>
+          <t>+40 Aggression 75</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7496,7 +7512,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7509,23 +7525,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Volleys</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E56" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+7 Volleys 77</t>
+          <t>+40 Acceleration 75</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7540,7 +7556,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7553,23 +7569,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Fk Accuracy</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+7 Short Pass 78</t>
+          <t>+50 Fk Accuracy 74</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7584,7 +7600,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7597,23 +7613,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Interceptions</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E58" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>+7 Agility 82</t>
+          <t>+40 Interceptions 75</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7628,7 +7644,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7641,23 +7657,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Jumping</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E59" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>+5 Stamina 75</t>
+          <t>+40 Jumping 76</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7672,7 +7688,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7685,23 +7701,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E60" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>+7 Finishing 80</t>
+          <t>+40 Sprint Speed 75</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7716,7 +7732,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7729,23 +7745,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Long Shots</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E61" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>+7 Long Shots 77</t>
+          <t>+50 Short Pass 80</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7760,7 +7776,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7773,23 +7789,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Defensive Awareness</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E62" t="n">
         <v>80</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>+7 Dribbling 80</t>
+          <t>+40 Defensive Awareness 80</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7804,7 +7820,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7817,23 +7833,23 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E63" t="n">
         <v>76</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>+7 Composure 76</t>
+          <t>+40 Stamina 76</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7848,7 +7864,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -7868,16 +7884,16 @@
         <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>+5 OVR 80</t>
+          <t>+5 OVR 81</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7892,7 +7908,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -7909,19 +7925,19 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
         <v>82</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>+5 Sprint Speed 82</t>
+          <t>+7 Sprint Speed 82</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7936,7 +7952,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -7949,23 +7965,23 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Defensive Awareness</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>+5 Defensive Awareness 79</t>
+          <t>+7 Shot Power 80</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7980,7 +7996,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -7993,23 +8009,23 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sliding Tackle</t>
+          <t>Fk Accuracy</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E67" t="n">
         <v>80</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>+5 Sliding Tackle 80</t>
+          <t>+7 Fk Accuracy 80</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8024,7 +8040,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8037,23 +8053,23 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>+5 Acceleration 82</t>
+          <t>+7 Curve 79</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8068,7 +8084,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8081,23 +8097,23 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Interceptions</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E69" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>+5 Interceptions 78</t>
+          <t>+7 Balance 82</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8112,7 +8128,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8125,23 +8141,23 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Standing Tackle</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>+5 Standing Tackle 80</t>
+          <t>+7 Acceleration 82</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8156,7 +8172,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8169,23 +8185,23 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>+5 Stamina 76</t>
+          <t>+7 Positioning 79</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8200,7 +8216,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8213,23 +8229,23 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Heading Accuracy</t>
+          <t>Volleys</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>+5 Heading Acc. 75</t>
+          <t>+7 Volleys 77</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8244,7 +8260,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8257,23 +8273,23 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jumping</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>+5 Jumping 75</t>
+          <t>+7 Short Pass 78</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8288,7 +8304,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8301,23 +8317,23 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>+5 Strength 77</t>
+          <t>+7 Agility 82</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8332,7 +8348,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8345,23 +8361,23 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Aggression</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>+5 Aggression 76</t>
+          <t>+5 Stamina 75</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8376,7 +8392,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8384,28 +8400,28 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E76" t="n">
         <v>80</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>+1 OVR 80</t>
+          <t>+7 Finishing 80</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8420,7 +8436,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8437,19 +8453,19 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E77" t="n">
         <v>77</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>+4 Long Shots 77</t>
+          <t>+7 Long Shots 77</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8464,7 +8480,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8477,23 +8493,23 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>+3 Vision 79</t>
+          <t>+7 Dribbling 80</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8508,7 +8524,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8521,23 +8537,23 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E79" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>+3 Short Pass 78</t>
+          <t>+7 Composure 76</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8552,7 +8568,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -8560,23 +8576,23 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
         <v>80</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>+4 Reactions 80</t>
+          <t>+1 OVR 80</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8609,18 +8625,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shot Power</t>
+          <t>Long Shots</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>+3 Shot Power 78</t>
+          <t>+4 Long Shots 77</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8653,18 +8669,18 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Volleys</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>+3 Volleys 78</t>
+          <t>+3 Vision 79</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8697,18 +8713,18 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fk Accuracy</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>+4 Fk Accuracy 80</t>
+          <t>+3 Short Pass 78</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8741,18 +8757,18 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Reactions</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>+4 Long Pass 77</t>
+          <t>+4 Reactions 80</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8785,18 +8801,18 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>+4 Dribbling 80</t>
+          <t>+3 Shot Power 78</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8824,28 +8840,28 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Volleys</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>+34 OVR 79</t>
+          <t>+3 Volleys 78</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Intro to Evolutions - EA SPORTS FC 27</t>
+          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8860,7 +8876,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
     </row>
@@ -8873,23 +8889,23 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>Fk Accuracy</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
         <v>80</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>+40 Sprint Speed 80</t>
+          <t>+4 Fk Accuracy 80</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Intro to Evolutions - EA SPORTS FC 27</t>
+          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8904,7 +8920,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
     </row>
@@ -8917,23 +8933,23 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>+40 Short Pass 76</t>
+          <t>+4 Long Pass 77</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Intro to Evolutions - EA SPORTS FC 27</t>
+          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8948,7 +8964,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
     </row>
@@ -8961,23 +8977,23 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>+40 Balance 77</t>
+          <t>+4 Dribbling 80</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Intro to Evolutions - EA SPORTS FC 27</t>
+          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8992,7 +9008,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
     </row>
@@ -9000,23 +9016,23 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Interceptions</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E90" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>+40 Interceptions 76</t>
+          <t>+34 OVR 79</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9049,18 +9065,18 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sliding Tackle</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>40</v>
       </c>
       <c r="E91" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>+40 Sliding Tackle 75</t>
+          <t>+40 Sprint Speed 80</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9093,18 +9109,18 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>40</v>
       </c>
       <c r="E92" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>+40 Vision 75</t>
+          <t>+40 Short Pass 76</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -9137,18 +9153,18 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D93" t="n">
         <v>40</v>
       </c>
       <c r="E93" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>+40 Curve 80</t>
+          <t>+40 Balance 77</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9181,18 +9197,18 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>Interceptions</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>40</v>
       </c>
       <c r="E94" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>+40 Ball Control 80</t>
+          <t>+40 Interceptions 76</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9225,18 +9241,18 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Defensive Awareness</t>
+          <t>Sliding Tackle</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>40</v>
       </c>
       <c r="E95" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>+40 Defensive Awareness 77</t>
+          <t>+40 Sliding Tackle 75</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9269,18 +9285,18 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>40</v>
       </c>
       <c r="E96" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>+40 Stamina 80</t>
+          <t>+40 Vision 75</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9313,7 +9329,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -9324,7 +9340,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>+40 Acceleration 80</t>
+          <t>+40 Curve 80</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9357,18 +9373,18 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Ball Control</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>40</v>
       </c>
       <c r="E98" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>+40 Crossing 78</t>
+          <t>+40 Ball Control 80</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9401,18 +9417,18 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Defensive Awareness</t>
         </is>
       </c>
       <c r="D99" t="n">
         <v>40</v>
       </c>
       <c r="E99" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>+40 Agility 78</t>
+          <t>+40 Defensive Awareness 77</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -9445,7 +9461,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -9456,7 +9472,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>+40 Dribbling 80</t>
+          <t>+40 Stamina 80</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -9489,18 +9505,18 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Standing Tackle</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>40</v>
       </c>
       <c r="E101" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>+40 Standing Tackle 78</t>
+          <t>+40 Acceleration 80</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9528,28 +9544,28 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Crossing</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E102" t="n">
         <v>78</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>+8 OVR 78</t>
+          <t>+40 Crossing 78</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Intro to Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9564,7 +9580,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
     </row>
@@ -9572,28 +9588,28 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>+2 SM 3</t>
+          <t>+40 Agility 78</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Intro to Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9608,7 +9624,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
     </row>
@@ -9616,28 +9632,28 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>+2 WF 3</t>
+          <t>+40 Dribbling 80</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Intro to Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9652,7 +9668,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
     </row>
@@ -9665,23 +9681,23 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>Standing Tackle</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E105" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>+5 Sprint Speed 80</t>
+          <t>+40 Standing Tackle 78</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Intro to Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9696,7 +9712,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
     </row>
@@ -9704,23 +9720,23 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E106" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>+15 Short Pass 76</t>
+          <t>+8 OVR 78</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -9748,23 +9764,23 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>+12 Balance 75</t>
+          <t>+2 SM 3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9792,23 +9808,23 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>+10 Composure 75</t>
+          <t>+2 WF 3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9841,18 +9857,18 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>+15 Vision 84</t>
+          <t>+5 Sprint Speed 80</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9885,18 +9901,18 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E110" t="n">
         <v>76</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>+12 Long Pass 76</t>
+          <t>+15 Short Pass 76</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9929,18 +9945,18 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>12</v>
       </c>
       <c r="E111" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>+12 Reactions 73</t>
+          <t>+12 Balance 75</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9973,18 +9989,18 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E112" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>+15 Stamina 78</t>
+          <t>+10 Composure 75</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -10017,18 +10033,18 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E113" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>+10 Crossing 78</t>
+          <t>+15 Vision 84</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10061,18 +10077,18 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>12</v>
       </c>
       <c r="E114" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>+12 Curve 78</t>
+          <t>+12 Long Pass 76</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10105,18 +10121,18 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>Reactions</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E115" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>+8 Ball Control 74</t>
+          <t>+12 Reactions 73</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10149,18 +10165,18 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E116" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>+5 Acceleration 80</t>
+          <t>+15 Stamina 78</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10193,18 +10209,18 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fk Accuracy</t>
+          <t>Crossing</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E117" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>+4 Fk Accuracy 80</t>
+          <t>+10 Crossing 78</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10237,18 +10253,18 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E118" t="n">
         <v>78</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>+8 Agility 78</t>
+          <t>+12 Curve 78</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10281,7 +10297,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Ball Control</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -10292,7 +10308,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>+8 Dribbling 74</t>
+          <t>+8 Ball Control 74</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10320,43 +10336,43 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E120" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>+1 OVR 83</t>
+          <t>+5 Acceleration 80</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -10369,38 +10385,38 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Fk Accuracy</t>
         </is>
       </c>
       <c r="D121" t="n">
         <v>4</v>
       </c>
       <c r="E121" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>+4 Short Pass 83</t>
+          <t>+4 Fk Accuracy 80</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -10413,38 +10429,38 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E122" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>+3 Composure 84</t>
+          <t>+8 Agility 78</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -10452,43 +10468,43 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E123" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>+10 OVR 83</t>
+          <t>+8 Dribbling 74</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Current Evolutions</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -10496,28 +10512,28 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D124" t="n">
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>+1 SM 3</t>
+          <t>+1 OVR 83</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -10527,12 +10543,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
@@ -10545,23 +10561,23 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>+10 Positioning 80</t>
+          <t>+4 Short Pass 83</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -10571,12 +10587,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
@@ -10589,23 +10605,23 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Volleys</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>+10 Volleys 74</t>
+          <t>+3 Composure 84</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10615,12 +10631,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
@@ -10628,23 +10644,23 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Fk Accuracy</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D127" t="n">
         <v>10</v>
       </c>
       <c r="E127" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>+10 Fk Accuracy 73</t>
+          <t>+10 OVR 83</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -10672,23 +10688,23 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>+15 Agility 86</t>
+          <t>+1 SM 3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10721,18 +10737,18 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E129" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>+15 Dribbling 84</t>
+          <t>+10 Positioning 80</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -10765,18 +10781,18 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Volleys</t>
         </is>
       </c>
       <c r="D130" t="n">
         <v>10</v>
       </c>
       <c r="E130" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>+10 Finishing 78</t>
+          <t>+10 Volleys 74</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -10809,18 +10825,18 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Penalties</t>
+          <t>Fk Accuracy</t>
         </is>
       </c>
       <c r="D131" t="n">
         <v>10</v>
       </c>
       <c r="E131" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>+10 Penalties 74</t>
+          <t>+10 Fk Accuracy 73</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -10853,18 +10869,18 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>+10 Short Pass 76</t>
+          <t>+15 Agility 86</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -10897,18 +10913,18 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>15</v>
       </c>
       <c r="E133" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>+15 Balance 85</t>
+          <t>+15 Dribbling 84</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -10941,18 +10957,18 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E134" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>+15 Composure 80</t>
+          <t>+10 Finishing 78</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10985,18 +11001,18 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Penalties</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E135" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>+15 Acceleration 85</t>
+          <t>+10 Penalties 74</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11029,18 +11045,18 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Shot Power</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>10</v>
       </c>
       <c r="E136" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>+10 Shot Power 77</t>
+          <t>+10 Short Pass 76</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -11073,18 +11089,18 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E137" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>+10 Vision 81</t>
+          <t>+15 Balance 85</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -11117,18 +11133,18 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E138" t="n">
         <v>80</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>+10 Long Pass 80</t>
+          <t>+15 Composure 80</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -11161,18 +11177,18 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>15</v>
       </c>
       <c r="E139" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>+15 Reactions 78</t>
+          <t>+15 Acceleration 85</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11205,18 +11221,18 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>10</v>
       </c>
       <c r="E140" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>+10 Stamina 72</t>
+          <t>+10 Shot Power 77</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -11249,18 +11265,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E141" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>+15 Sprint Speed 85</t>
+          <t>+10 Vision 81</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11293,7 +11309,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Long Shots</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -11304,7 +11320,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>+10 Long Shots 80</t>
+          <t>+10 Long Pass 80</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -11337,18 +11353,18 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Reactions</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E143" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>+10 Crossing 82</t>
+          <t>+15 Reactions 78</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -11381,18 +11397,18 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D144" t="n">
         <v>10</v>
       </c>
       <c r="E144" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>+10 Curve 78</t>
+          <t>+10 Stamina 72</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -11425,7 +11441,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -11436,7 +11452,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>+15 Ball Control 85</t>
+          <t>+15 Sprint Speed 85</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -11464,12 +11480,12 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Long Shots</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -11480,12 +11496,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>+10 OVR 80</t>
+          <t>+10 Long Shots 80</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11495,12 +11511,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11513,23 +11529,23 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Crossing</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E147" t="n">
         <v>82</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>+15 Positioning 82</t>
+          <t>+10 Crossing 82</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11539,12 +11555,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11557,23 +11573,23 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Volleys</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E148" t="n">
         <v>78</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>+15 Volleys 78</t>
+          <t>+10 Curve 78</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11583,12 +11599,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11601,23 +11617,23 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Ball Control</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E149" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>+8 Long Pass 62</t>
+          <t>+15 Ball Control 85</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11627,12 +11643,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11640,23 +11656,23 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D150" t="n">
         <v>10</v>
       </c>
       <c r="E150" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>+10 Reactions 76</t>
+          <t>+10 OVR 80</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11689,18 +11705,18 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jumping</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E151" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>+10 Jumping 78</t>
+          <t>+15 Positioning 82</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11733,18 +11749,18 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Volleys</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>15</v>
       </c>
       <c r="E152" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>+15 Finishing 83</t>
+          <t>+15 Volleys 78</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11777,18 +11793,18 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Penalties</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E153" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>+10 Penalties 75</t>
+          <t>+8 Long Pass 62</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11821,18 +11837,18 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Reactions</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E154" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>+15 Curve 77</t>
+          <t>+10 Reactions 76</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11865,18 +11881,18 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>Jumping</t>
         </is>
       </c>
       <c r="D155" t="n">
         <v>10</v>
       </c>
       <c r="E155" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>+10 Ball Control 76</t>
+          <t>+10 Jumping 78</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11909,18 +11925,18 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E156" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>+10 Stamina 67</t>
+          <t>+15 Finishing 83</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11953,18 +11969,18 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Penalties</t>
         </is>
       </c>
       <c r="D157" t="n">
         <v>10</v>
       </c>
       <c r="E157" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>+10 Acceleration 80</t>
+          <t>+10 Penalties 75</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11997,18 +12013,18 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Shot Power</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D158" t="n">
         <v>15</v>
       </c>
       <c r="E158" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>+15 Shot Power 82</t>
+          <t>+15 Curve 77</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -12041,18 +12057,18 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Ball Control</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E159" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>+8 Vision 70</t>
+          <t>+10 Ball Control 76</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -12085,18 +12101,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E160" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>+15 Agility 78</t>
+          <t>+10 Stamina 67</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -12129,18 +12145,18 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D161" t="n">
         <v>10</v>
       </c>
       <c r="E161" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>+10 Dribbling 76</t>
+          <t>+10 Acceleration 80</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12173,18 +12189,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E162" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>+10 Sprint Speed 78</t>
+          <t>+15 Shot Power 82</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12217,18 +12233,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Long Shots</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E163" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>+15 Long Shots 78</t>
+          <t>+8 Vision 70</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12261,18 +12277,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E164" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>+8 Short Pass 72</t>
+          <t>+15 Agility 78</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12305,18 +12321,18 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E165" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>+15 Balance 77</t>
+          <t>+10 Dribbling 76</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12349,18 +12365,18 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E166" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>+8 Composure 80</t>
+          <t>+10 Sprint Speed 78</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12388,28 +12404,28 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Long Shots</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E167" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>+1 OVR 80</t>
+          <t>+15 Long Shots 78</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12419,12 +12435,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
@@ -12432,28 +12448,28 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E168" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>+1 PAS 79</t>
+          <t>+8 Short Pass 72</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12463,12 +12479,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
@@ -12476,41 +12492,217 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>15</v>
+      </c>
+      <c r="E169" t="n">
+        <v>77</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>+15 Balance 77</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Composure</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>8</v>
+      </c>
+      <c r="E170" t="n">
+        <v>80</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>+8 Composure 80</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
           <t>Face Stat</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>OVR</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>80</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>+1 OVR 80</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Premium Season Pass</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Face Stat</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PAS</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="n">
+        <v>79</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>+1 PAS 79</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Premium Season Pass</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Face Stat</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="D169" t="n">
+      <c r="D173" t="n">
         <v>1</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E173" t="n">
         <v>79</v>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>+1 DEF 79</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>Reward</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t>Premium Season Pass</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
+      <c r="J173" t="inlineStr">
         <is>
           <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
@@ -12605,7 +12797,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -12620,7 +12812,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -12642,17 +12834,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pace Max. 83</t>
+          <t>Pace Max. 85</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -12667,7 +12859,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12891,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -12714,7 +12906,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -12736,17 +12928,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ST, CAM, CB</t>
+          <t>ST, CDM, LB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Excluded Position ST, CAM, CB</t>
+          <t>Excluded Position ST, CDM, LB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -12761,7 +12953,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -12783,17 +12975,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CDM, CM</t>
+          <t>LM, LW</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Position CDM, CM</t>
+          <t>Position LM, LW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -12808,7 +13000,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
@@ -12840,7 +13032,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -12855,7 +13047,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -12877,17 +13069,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pace Max. 85</t>
+          <t>Pace Max. 83</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -12902,7 +13094,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -12934,7 +13126,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -12949,7 +13141,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -12971,17 +13163,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CM, LM, RM</t>
+          <t>ST, CAM, CB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Excluded Position CM, LM, RM</t>
+          <t>Excluded Position ST, CAM, CB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -12996,7 +13188,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -13018,17 +13210,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>CDM, CM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Position ST</t>
+          <t>Position CDM, CM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13043,7 +13235,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
@@ -13065,17 +13257,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Overall Max. 74</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -13090,7 +13282,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13314,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -13137,7 +13329,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -13169,7 +13361,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -13184,7 +13376,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -13206,17 +13398,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CAM, CB, ST</t>
+          <t>CM, LM, RM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Excluded Position CAM, CB, ST</t>
+          <t>Excluded Position CM, LM, RM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -13231,7 +13423,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -13253,17 +13445,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Position CDM</t>
+          <t>Position ST</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -13278,7 +13470,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
@@ -13300,17 +13492,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Overall Max. 74</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13325,7 +13517,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13549,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -13372,7 +13564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13596,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -13419,7 +13611,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -13441,17 +13633,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CDM, ST</t>
+          <t>CAM, CB, ST</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Excluded Position CDM, ST</t>
+          <t>Excluded Position CAM, CB, ST</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -13466,7 +13658,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -13488,17 +13680,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Position CAM</t>
+          <t>Position CDM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Creative Crossroads - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -13513,7 +13705,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13737,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -13560,7 +13752,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -13582,17 +13774,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pace Max. 83</t>
+          <t>Pace Max. 85</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -13607,7 +13799,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13831,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -13654,7 +13846,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -13676,17 +13868,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CB, CM</t>
+          <t>CDM, ST</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Excluded Position CB, CM</t>
+          <t>Excluded Position CDM, ST</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -13701,7 +13893,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -13723,17 +13915,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LB, RB</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Position LB, RB</t>
+          <t>Position CAM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fullback Fork - EA SPORTS FC 27</t>
+          <t>Creative Crossroads - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -13748,7 +13940,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
     </row>
@@ -16062,17 +16254,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pivot Shift</t>
+          <t>Flank Identity NEW</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Avdullahu 79 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 72 PHY 75 CM R 2 ★ 4 CDM 77.5 Avdullahu 80 CDM PAC 72 SHO 61 PAS 79 DRI 79 DEF 74 PHY 79 CM R 2 ★ 4 CDM 80.0 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 9 days in 16 days 26% 74%</t>
+          <t>Flank Identity NEW Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 10 days in 17 days 25% 75%</t>
         </is>
       </c>
     </row>
@@ -16089,17 +16281,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Frontline Paradox</t>
+          <t>Pivot Shift</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Paulinho 70 ST PAC 82 SHO 70 PAS 68 DRI 75 DEF 44 PHY 66 CAM RW L 4 ★ 3 ST 74.7 Paulinho 75 ST PAC 84 SHO 75 PAS 68 DRI 75 DEF 44 PHY 70 CAM RW L 4 ★ 3 ST 78.4 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 8 days in 15 days 73% 27%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 8 days in 15 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -16116,17 +16308,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Midfield Glow Up</t>
+          <t>Frontline Paradox</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 25 days in 25 days 84% 16%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 7 days in 14 days 75% 25%</t>
         </is>
       </c>
     </row>
@@ -16143,17 +16335,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150</t>
+          <t>Midfield Glow Up</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 3 days in 10 days 52% 48%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 24 days in 24 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -16170,17 +16362,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
+          <t>https://www.fut.gg/evolutions/2506-creative-crossroads/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200</t>
+          <t>Creative Crossroads 15,000 150</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 20% 80%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 2 days in 9 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -16197,17 +16389,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
+          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200</t>
+          <t>Ones to Watch Retro 20 25,000 200</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 16% 84%</t>
+          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -16224,17 +16416,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
+          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200</t>
+          <t>Ones to Watch Retro 19 25,000 200</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Nuno Mendes 89 LB LM L 4 ★ 4 LB 93.6 Nuno Mendes 89 LB PAC 94 SHO 78 PAS 81 DRI 86 DEF 84 PHY 82 LM L 4 ★ 4 LB 93.6 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 22% 78%</t>
+          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -16251,17 +16443,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2502-fullback-fork/</t>
+          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fullback Fork</t>
+          <t>Ones to Watch Retro 18 25,000 200</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fullback Fork Sharpen your outer defender’s key attributes, culminating in a choice to tailor their game toward attacking width or defensive stability Gayà 77 LB PAC 76 SHO 61 PAS 74 DRI 75 DEF 74 PHY 71 LM L 4 ★ 3 LB 73.6 Gayà 80 LB PAC 81 SHO 61 PAS 74 DRI 75 DEF 78 PHY 74 LM L 4 ★ 3 LB 79.5 REQUIREMENTS Overall Max. 79 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +5 Sprint Speed 82 +5 Defensive Awareness 79 +5 Sliding Tackle 80 +5 Acceleration 82 +5 Interceptions 78 +5 Standing Tackle 80 +5 Stamina 76 +5 Heading Acc. 75 +5 Jumping 75 +5 Strength 77 +5 Aggression 76 3 in 21 hours in 8 days 89% 11%</t>
+          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -16288,7 +16480,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Esposito 76 ST PAC 78 SHO 78 PAS 78 DRI 77 DEF 50 PHY 72 CAM R 4 ★ 5 CAM 76.6 Esposito 77 ST PAC 78 SHO 78 PAS 78 DRI 79 DEF 50 PHY 72 CAM R 4 ★ 5 CAM 77.3 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 84% 16%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.3 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.5 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 82% 18%</t>
         </is>
       </c>
     </row>
@@ -16315,7 +16507,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 90% 10%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 89% 11%</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16534,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Álex Jiménez 79 RB PAC 85 SHO 55 PAS 71 DRI 78 DEF 76 PHY 64 RM R 2 ★ 4 RB 76.9 Álex Jiménez 79 RB PAC 85 SHO 55 PAS 71 DRI 78 DEF 76 PHY 64 RM R 2 ★ 4 RB 78.3 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 87% 13%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 85% 15%</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16561,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 24 days in 24 days 93% 7%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 23 days in 23 days 92% 8%</t>
         </is>
       </c>
     </row>
@@ -16396,7 +16588,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.8 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 82.5 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
         </is>
       </c>
     </row>
@@ -16423,7 +16615,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Vargas 78 LW PAC 87 SHO 72 PAS 73 DRI 80 DEF 56 PHY 67 LM CAM RW R 4 ★ 4 LM 80.0 Vargas 78 LW PAC 87 SHO 72 PAS 73 DRI 80 DEF 56 PHY 67 LM CAM RW R 4 ★ 4 LM 80.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 97% 3%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 94% 6%</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16642,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Rashford 82 LW PAC 92 SHO 83 PAS 78 DRI 81 DEF 33 PHY 68 LM ST R 5 ★ 3 ST 85.2 Rashford 83 LW PAC 92 SHO 83 PAS 80 DRI 81 DEF 33 PHY 68 LM ST R 5 ★ 3 ST 85.5 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16669,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.8 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 82.7 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 1 month in 1 month 88% 12%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 1 month in 1 month 89% 11%</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16696,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 79.5 Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 81.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 76% 24%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 76% 24%</t>
         </is>
       </c>
     </row>
@@ -16531,7 +16723,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Di Francesco 72 LM PAC 73 SHO 69 PAS 71 DRI 74 DEF 51 PHY 60 LW R 4 ★ 4 LM 71.7 Di Francesco 82 LM PAC 85 SHO 77 PAS 78 DRI 84 DEF 51 PHY 62 LW R 4 ★ 4 LM 82.0 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 91% 9%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 92% 8%</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16777,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Bertaccini 75 ST PAC 90 SHO 75 PAS 62 DRI 77 DEF 29 PHY 73 RM LM CAM RW LW R 2 ★ 4 ST 79.3 Bertaccini 75 ST PAC 90 SHO 75 PAS 62 DRI 77 DEF 29 PHY 73 RM LM CAM RW LW R 2 ★ 4 ST 79.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 36% 64%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 35% 65%</t>
         </is>
       </c>
     </row>
@@ -16639,7 +16831,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Diks 77 CB PAC 79 SHO 67 PAS 70 DRI 72 DEF 77 PHY 78 RB LB CM R 3 ★ 4 CM 77.7 Diks 78 CB PAC 79 SHO 67 PAS 71 DRI 72 DEF 78 PHY 78 RB LB CM R 3 ★ 4 CM 78.3 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 28% 72%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16902,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27T20:08:42</t>
+          <t>2026-09-28T22:32:21</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA23"/>
+  <dimension ref="A1:DA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,22 +1156,22 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Flank Identity NEW</t>
+          <t>Flank Identity</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Flank Identity NEW Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 10 days in 17 days 25% 75%</t>
+          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 9 days in 16 days 25% 75%</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 8 days in 15 days 26% 74%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 7 days in 14 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 7 days in 14 days 75% 25%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 6 days in 13 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 23 days Expiry in 23 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 23 days Expiry in 23 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 24 days in 24 days 84% 16%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 23 days in 23 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 20 hours Expiry in 8 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost 15,000 Points Cost 150</t>
+          <t>Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 20 hours Expiry in 8 days Coins Cost 15,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 2 days in 9 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 20 hours in 8 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -2092,23 +2092,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 - EA SPORTS FC 27</t>
+          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2119,8 +2131,12 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>80</v>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
@@ -2141,36 +2157,68 @@
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>78</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>78</v>
+      </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>79</v>
+      </c>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
+      <c r="BH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>78</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>77</v>
+      </c>
       <c r="BL7" t="inlineStr"/>
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr"/>
       <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
+      <c r="BR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>80</v>
+      </c>
       <c r="BT7" t="inlineStr"/>
       <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
+      <c r="BV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>80</v>
+      </c>
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="inlineStr"/>
@@ -2198,27 +2246,27 @@
       <c r="CV7" t="inlineStr"/>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Ronaldo 94 ST PAC 94 SHO 94 PAS 79 DRI 94 DEF 43 PHY 75 R 5 ★ 5 Ronaldo 94 ST PAC 94 SHO 94 PAS 79 DRI 94 DEF 43 PHY 75 R 5 ★ 5 UPGRADES No upgrades</t>
+          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 80 ST PAC 75 SHO 80 PAS 67 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
+          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
+          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200</t>
+          <t>Intro to Repeatable Evolutions 2</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 19% 81%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.3 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.5 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 82% 18%</t>
         </is>
       </c>
     </row>
@@ -2235,35 +2283,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 - EA SPORTS FC 27</t>
+          <t>Intro to Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>79</v>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
@@ -2276,10 +2352,18 @@
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>80</v>
+      </c>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
@@ -2292,44 +2376,96 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>78</v>
+      </c>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
+      <c r="BH8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>76</v>
+      </c>
       <c r="BJ8" t="inlineStr"/>
       <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
+      <c r="BL8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>77</v>
+      </c>
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr"/>
+      <c r="BT8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>80</v>
+      </c>
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
-      <c r="BZ8" t="inlineStr"/>
-      <c r="CA8" t="inlineStr"/>
+      <c r="BZ8" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>76</v>
+      </c>
       <c r="CB8" t="inlineStr"/>
       <c r="CC8" t="inlineStr"/>
-      <c r="CD8" t="inlineStr"/>
-      <c r="CE8" t="inlineStr"/>
-      <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="inlineStr"/>
-      <c r="CH8" t="inlineStr"/>
-      <c r="CI8" t="inlineStr"/>
+      <c r="CD8" t="n">
+        <v>40</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>77</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>40</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>78</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>75</v>
+      </c>
       <c r="CJ8" t="inlineStr"/>
       <c r="CK8" t="inlineStr"/>
-      <c r="CL8" t="inlineStr"/>
-      <c r="CM8" t="inlineStr"/>
+      <c r="CL8" t="n">
+        <v>40</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>80</v>
+      </c>
       <c r="CN8" t="inlineStr"/>
       <c r="CO8" t="inlineStr"/>
       <c r="CP8" t="inlineStr"/>
@@ -2338,30 +2474,34 @@
       <c r="CS8" t="inlineStr"/>
       <c r="CT8" t="inlineStr"/>
       <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>RB Wingback +</t>
+        </is>
+      </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
+          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Merino Gonzalez 75 RB PAC 75 SHO 65 PAS 68 DRI 70 DEF 72 PHY 61 RM R 2 ★ 2 Merino Gonzalez 79 RB PAC 77 SHO 65 PAS 69 DRI 71 DEF 73 PHY 61 RM R 2 ★ 2 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
+          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
+          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200</t>
+          <t>Intro to Evolutions</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 16% 84%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 89% 11%</t>
         </is>
       </c>
     </row>
@@ -2378,19 +2518,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 - EA SPORTS FC 27</t>
+          <t>Intro to Training Camp EVOs - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
+          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -2481,30 +2629,34 @@
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="inlineStr"/>
       <c r="CU9" t="inlineStr"/>
-      <c r="CV9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>RB Fullback +</t>
+        </is>
+      </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
+          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 86% of GG users upvoted this Evolution. Vote Now! 86% 14% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 De Almeida 80 CB PAC 74 SHO 34 PAS 64 DRI 61 DEF 81 PHY 82 RB CM R 2 ★ 2 De Almeida 80 CB PAC 74 SHO 34 PAS 64 DRI 61 DEF 81 PHY 82 RB CM R 2 ★ 2 UPGRADES RB Fullback +</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
+          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 23 days Expiry in 23 days Coins Cost 25,000 Points Cost 200</t>
+          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200</t>
+          <t>Intro to Training Camp EVOs</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 21% 79%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 86% 14%</t>
         </is>
       </c>
     </row>
@@ -2521,33 +2673,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>LM, RM</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>LB, RB</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>83</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -2555,16 +2711,20 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -2578,78 +2738,98 @@
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
+      <c r="AL10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>80</v>
+      </c>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>78</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>77</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>78</v>
-      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
-        <v>79</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>78</v>
+      </c>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="BI10" t="n">
+        <v>76</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>76</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BM10" t="n">
         <v>78</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>77</v>
-      </c>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
+      <c r="BN10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>75</v>
+      </c>
       <c r="BR10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BS10" t="n">
-        <v>80</v>
-      </c>
-      <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>74</v>
+      </c>
       <c r="BV10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BW10" t="n">
-        <v>80</v>
-      </c>
-      <c r="BX10" t="inlineStr"/>
-      <c r="BY10" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>75</v>
+      </c>
       <c r="BZ10" t="inlineStr"/>
       <c r="CA10" t="inlineStr"/>
       <c r="CB10" t="inlineStr"/>
@@ -2662,40 +2842,52 @@
       <c r="CI10" t="inlineStr"/>
       <c r="CJ10" t="inlineStr"/>
       <c r="CK10" t="inlineStr"/>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
+      <c r="CL10" t="n">
+        <v>15</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>78</v>
+      </c>
       <c r="CN10" t="inlineStr"/>
       <c r="CO10" t="inlineStr"/>
       <c r="CP10" t="inlineStr"/>
       <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="inlineStr"/>
+      <c r="CR10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>3</v>
+      </c>
       <c r="CV10" t="inlineStr"/>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 80 ST PAC 75 SHO 80 PAS 67 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
+          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Mateus Mané 74 CAM PAC 77 SHO 70 PAS 74 DRI 76 DEF 51 PHY 64 RM CM LM RW LW R 3 ★ 3 Mateus Mané 78 CAM PAC 79 SHO 70 PAS 75 DRI 76 DEF 51 PHY 64 RM CM LM RW LW R 3 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 22 days Expiry in 22 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 22 days Expiry in 22 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2</t>
+          <t>Repeat Delivery 2</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.3 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.5 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 82% 18%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 22 days in 22 days 92% 8%</t>
         </is>
       </c>
     </row>
@@ -2712,39 +2904,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions - EA SPORTS FC 27</t>
+          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -2752,23 +2932,15 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>79</v>
-      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
@@ -2781,18 +2953,10 @@
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>80</v>
-      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
@@ -2805,96 +2969,44 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>75</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>78</v>
-      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>76</v>
-      </c>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
       <c r="BJ11" t="inlineStr"/>
       <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>77</v>
-      </c>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
       <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="inlineStr"/>
-      <c r="BT11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>80</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>80</v>
-      </c>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
       <c r="BX11" t="inlineStr"/>
       <c r="BY11" t="inlineStr"/>
-      <c r="BZ11" t="n">
-        <v>40</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>76</v>
-      </c>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
       <c r="CB11" t="inlineStr"/>
       <c r="CC11" t="inlineStr"/>
-      <c r="CD11" t="n">
-        <v>40</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>77</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>40</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>78</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>40</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>75</v>
-      </c>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr"/>
+      <c r="CI11" t="inlineStr"/>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="inlineStr"/>
-      <c r="CL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>80</v>
-      </c>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
       <c r="CN11" t="inlineStr"/>
       <c r="CO11" t="inlineStr"/>
       <c r="CP11" t="inlineStr"/>
@@ -2903,71 +3015,59 @@
       <c r="CS11" t="inlineStr"/>
       <c r="CT11" t="inlineStr"/>
       <c r="CU11" t="inlineStr"/>
-      <c r="CV11" t="inlineStr">
-        <is>
-          <t>RB Wingback +</t>
-        </is>
-      </c>
+      <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Merino Gonzalez 75 RB PAC 75 SHO 65 PAS 68 DRI 70 DEF 72 PHY 61 RM R 2 ★ 2 Merino Gonzalez 79 RB PAC 77 SHO 65 PAS 69 DRI 71 DEF 73 PHY 61 RM R 2 ★ 2 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 88% of GG users upvoted this Evolution. Vote Now! 88% 12% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Engelhardt 80 CDM PAC 84 SHO 60 PAS 72 DRI 71 DEF 80 PHY 84 CM R 3 ★ 3 CDM 82.2 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 RB 82.9 Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 RB 82.9 Engelhardt 80 CDM PAC 84 SHO 60 PAS 72 DRI 71 DEF 80 PHY 84 CM R 3 ★ 3 CDM 82.2 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Evolution Upgrades B 4 Level 1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions</t>
+          <t>Intro to Pathway Evolutions</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 89% 11%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs - EA SPORTS FC 27</t>
+          <t>Gallery Excellence - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
+          <t>https://www.fut.gg/evolutions/2527-gallery-excellence/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -3058,103 +3158,75 @@
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="inlineStr">
-        <is>
-          <t>RB Fullback +</t>
-        </is>
-      </c>
+      <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 85% of GG users upvoted this Evolution. Vote Now! 85% 15% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 De Almeida 80 CB PAC 74 SHO 34 PAS 64 DRI 61 DEF 81 PHY 82 RB CM R 2 ★ 2 De Almeida 80 CB PAC 74 SHO 34 PAS 64 DRI 61 DEF 81 PHY 82 RB CM R 2 ★ 2 UPGRADES RB Fullback +</t>
+          <t>No upgrades Level 1 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs</t>
+          <t>Gallery Excellence NEW</t>
         </is>
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 85% 15%</t>
+          <t>Gallery Excellence NEW Unlocked by completing the Gallery Milestone objective REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 25% 75%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Season Ladder Excellence [SP 27] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2526-season-ladder-excellence-sp-27/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>LM, RM</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>LB, RB</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>78</v>
-      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
@@ -3167,18 +3239,10 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>80</v>
-      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
@@ -3191,74 +3255,30 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>84</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>78</v>
-      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>76</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>76</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>78</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>75</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>73</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>74</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>74</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>75</v>
-      </c>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="inlineStr"/>
       <c r="CA13" t="inlineStr"/>
       <c r="CB13" t="inlineStr"/>
@@ -3271,83 +3291,67 @@
       <c r="CI13" t="inlineStr"/>
       <c r="CJ13" t="inlineStr"/>
       <c r="CK13" t="inlineStr"/>
-      <c r="CL13" t="n">
-        <v>15</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>78</v>
-      </c>
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
       <c r="CN13" t="inlineStr"/>
       <c r="CO13" t="inlineStr"/>
       <c r="CP13" t="inlineStr"/>
       <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="n">
-        <v>2</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>2</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>3</v>
-      </c>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="inlineStr"/>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Mateus Mané 74 CAM PAC 77 SHO 70 PAS 74 DRI 76 DEF 51 PHY 64 RM CM LM RW LW R 3 ★ 3 Mateus Mané 78 CAM PAC 79 SHO 70 PAS 75 DRI 76 DEF 51 PHY 64 RM CM LM RW LW R 3 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
+          <t>No upgrades Level 1 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 23 days Expiry in 23 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 23 days Expiry in 23 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2</t>
+          <t>Season Ladder Excellence [SP 27] NEW</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 23 days in 23 days 92% 8%</t>
+          <t>Season Ladder Excellence [SP 27] NEW Unlocked by reaching level 27 in the Standard Season Pass. REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 33% 67%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 20 [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -3359,11 +3363,7 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -3447,27 +3447,27 @@
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 88% of GG users upvoted this Evolution. Vote Now! 88% 12% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades B 4 Level 1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>No upgrades Level 1 Ronaldo 94 ST PAC 94 SHO 94 PAS 79 DRI 94 DEF 43 PHY 75 R 5 ★ 5 Ronaldo 94 ST PAC 94 SHO 94 PAS 79 DRI 94 DEF 43 PHY 75 R 5 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions</t>
+          <t>Ones to Watch Retro 20 [SP+ 26]</t>
         </is>
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
+          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -3479,26 +3479,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pinged Pass - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 19 [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -3510,11 +3506,7 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -3598,27 +3590,27 @@
       <c r="CV15" t="inlineStr"/>
       <c r="CW15" t="inlineStr">
         <is>
-          <t>3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADES 3</t>
+          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
-          <t>Pinged Pass</t>
+          <t>Ones to Watch Retro 19 [SP+ 26]</t>
         </is>
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 94% 6%</t>
+          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -3630,32 +3622,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Ones to Watch Retro 18 [SP 27] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -3670,12 +3654,8 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>83</v>
-      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
@@ -3710,12 +3690,8 @@
       <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="inlineStr"/>
       <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>83</v>
-      </c>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
       <c r="BJ16" t="inlineStr"/>
       <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr"/>
@@ -3730,12 +3706,8 @@
       <c r="BU16" t="inlineStr"/>
       <c r="BV16" t="inlineStr"/>
       <c r="BW16" t="inlineStr"/>
-      <c r="BX16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>84</v>
-      </c>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="inlineStr"/>
       <c r="CA16" t="inlineStr"/>
       <c r="CB16" t="inlineStr"/>
@@ -3761,27 +3733,27 @@
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="inlineStr">
         <is>
-          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Kofane 82 ST PAC 85 SHO 81 PAS 70 DRI 78 DEF 38 PHY 80 R 3 ★ 3 Kofane 83 ST PAC 85 SHO 81 PAS 71 DRI 78 DEF 38 PHY 80 R 3 ★ 3 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
+          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>Overall Max. 82 Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>Overall Max. 82 Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 29 days Expiry in 29 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Ones to Watch Retro 18 [SP 27]</t>
         </is>
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
+          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -3793,32 +3765,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
+          <t>Pinged Pass - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>LW, RW, ST</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -3830,14 +3798,10 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -3920,27 +3884,27 @@
       <c r="CV17" t="inlineStr"/>
       <c r="CW17" t="inlineStr">
         <is>
-          <t>B · A 4 Level 1 Svensson 81 LB PAC 77 SHO 62 PAS 78 DRI 81 DEF 77 PHY 77 LM LW L 3 ★ 4 Svensson 81 LB PAC 77 SHO 62 PAS 78 DRI 81 DEF 77 PHY 77 LM LW L 3 ★ 4 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28]</t>
+          <t>Pinged Pass</t>
         </is>
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 1 month in 1 month 89% 11%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 30 days in 30 days 95% 5%</t>
         </is>
       </c>
     </row>
@@ -3952,28 +3916,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -3983,17 +3951,17 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>83</v>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
@@ -4028,8 +3996,12 @@
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
+      <c r="BH18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>83</v>
+      </c>
       <c r="BJ18" t="inlineStr"/>
       <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr"/>
@@ -4044,8 +4016,12 @@
       <c r="BU18" t="inlineStr"/>
       <c r="BV18" t="inlineStr"/>
       <c r="BW18" t="inlineStr"/>
-      <c r="BX18" t="inlineStr"/>
-      <c r="BY18" t="inlineStr"/>
+      <c r="BX18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>84</v>
+      </c>
       <c r="BZ18" t="inlineStr"/>
       <c r="CA18" t="inlineStr"/>
       <c r="CB18" t="inlineStr"/>
@@ -4071,27 +4047,27 @@
       <c r="CV18" t="inlineStr"/>
       <c r="CW18" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Kofane 82 ST PAC 85 SHO 81 PAS 70 DRI 78 DEF 38 PHY 80 R 3 ★ 3 Kofane 83 ST PAC 85 SHO 81 PAS 71 DRI 78 DEF 38 PHY 80 R 3 ★ 3 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
         </is>
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 82 Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 82 Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27]</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 76% 24%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 33% 67%</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4084,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -4126,21 +4102,13 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LW</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>LB, ST</t>
-        </is>
-      </c>
+          <t>LW, RW, ST</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -4148,7 +4116,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -4156,19 +4124,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>83</v>
-      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
@@ -4181,122 +4141,46 @@
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>78</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>77</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>74</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>74</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>81</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>82</v>
-      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="inlineStr"/>
       <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>76</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>80</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>78</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>86</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>85</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>78</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>85</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>84</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>80</v>
-      </c>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="inlineStr"/>
       <c r="CA19" t="inlineStr"/>
       <c r="CB19" t="inlineStr"/>
@@ -4309,48 +4193,40 @@
       <c r="CI19" t="inlineStr"/>
       <c r="CJ19" t="inlineStr"/>
       <c r="CK19" t="inlineStr"/>
-      <c r="CL19" t="n">
-        <v>10</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>72</v>
-      </c>
+      <c r="CL19" t="inlineStr"/>
+      <c r="CM19" t="inlineStr"/>
       <c r="CN19" t="inlineStr"/>
       <c r="CO19" t="inlineStr"/>
       <c r="CP19" t="inlineStr"/>
       <c r="CQ19" t="inlineStr"/>
-      <c r="CR19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>3</v>
-      </c>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
       <c r="CT19" t="inlineStr"/>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="inlineStr"/>
       <c r="CW19" t="inlineStr">
         <is>
-          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Zicai 78 LW PAC 77 SHO 76 PAS 74 DRI 79 DEF 51 PHY 66 LM R 4 ★ 4 Zicai 83 LW PAC 77 SHO 76 PAS 74 DRI 81 DEF 51 PHY 66 LM R 4 ★ 4 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
+          <t>B · A 4 Level 1 Svensson 81 LB PAC 77 SHO 62 PAS 78 DRI 81 DEF 77 PHY 77 LM LW L 3 ★ 4 Svensson 81 LB PAC 77 SHO 62 PAS 78 DRI 81 DEF 77 PHY 77 LM LW L 3 ★ 4 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26]</t>
+          <t>Shooting Practice [SP+ 28]</t>
         </is>
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 92% 8%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 30 days in 30 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -4362,17 +4238,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
+          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -4481,27 +4357,27 @@
       <c r="CV20" t="inlineStr"/>
       <c r="CW20" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>A · A 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14]</t>
+          <t>Creative or Composed? [SP 27]</t>
         </is>
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 88% 12%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 30 days in 30 days 79% 21%</t>
         </is>
       </c>
     </row>
@@ -4513,32 +4389,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>LB, ST</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -4546,15 +4434,27 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>83</v>
+      </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
@@ -4567,46 +4467,122 @@
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>78</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>74</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>81</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>82</v>
+      </c>
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr"/>
-      <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="inlineStr"/>
-      <c r="BL21" t="inlineStr"/>
-      <c r="BM21" t="inlineStr"/>
-      <c r="BN21" t="inlineStr"/>
-      <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr"/>
-      <c r="BQ21" t="inlineStr"/>
-      <c r="BR21" t="inlineStr"/>
-      <c r="BS21" t="inlineStr"/>
-      <c r="BT21" t="inlineStr"/>
-      <c r="BU21" t="inlineStr"/>
-      <c r="BV21" t="inlineStr"/>
-      <c r="BW21" t="inlineStr"/>
-      <c r="BX21" t="inlineStr"/>
-      <c r="BY21" t="inlineStr"/>
+      <c r="BH21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>76</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>80</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>78</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>86</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>85</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>78</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>85</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>84</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>80</v>
+      </c>
       <c r="BZ21" t="inlineStr"/>
       <c r="CA21" t="inlineStr"/>
       <c r="CB21" t="inlineStr"/>
@@ -4619,40 +4595,48 @@
       <c r="CI21" t="inlineStr"/>
       <c r="CJ21" t="inlineStr"/>
       <c r="CK21" t="inlineStr"/>
-      <c r="CL21" t="inlineStr"/>
-      <c r="CM21" t="inlineStr"/>
+      <c r="CL21" t="n">
+        <v>10</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>72</v>
+      </c>
       <c r="CN21" t="inlineStr"/>
       <c r="CO21" t="inlineStr"/>
       <c r="CP21" t="inlineStr"/>
       <c r="CQ21" t="inlineStr"/>
-      <c r="CR21" t="inlineStr"/>
-      <c r="CS21" t="inlineStr"/>
+      <c r="CR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>3</v>
+      </c>
       <c r="CT21" t="inlineStr"/>
       <c r="CU21" t="inlineStr"/>
       <c r="CV21" t="inlineStr"/>
       <c r="CW21" t="inlineStr">
         <is>
-          <t>3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES 3</t>
+          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Zicai 78 LW PAC 77 SHO 76 PAS 74 DRI 79 DEF 51 PHY 66 LM R 4 ★ 4 Zicai 83 LW PAC 77 SHO 76 PAS 74 DRI 81 DEF 51 PHY 66 LM R 4 ★ 4 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
         </is>
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11]</t>
+          <t>Winger Glow Up [SP+ 26]</t>
         </is>
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 35% 65%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 30 days in 30 days 92% 8%</t>
         </is>
       </c>
     </row>
@@ -4664,17 +4648,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -4685,23 +4669,11 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>CAM, CM</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -4709,23 +4681,15 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>80</v>
-      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
@@ -4738,118 +4702,46 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>78</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>82</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>83</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>82</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>78</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>78</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>70</v>
-      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
       <c r="BD22" t="inlineStr"/>
       <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="inlineStr"/>
       <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>72</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>62</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>77</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>77</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>76</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>76</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>76</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>80</v>
-      </c>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="inlineStr"/>
       <c r="CA22" t="inlineStr"/>
       <c r="CB22" t="inlineStr"/>
@@ -4860,18 +4752,10 @@
       <c r="CG22" t="inlineStr"/>
       <c r="CH22" t="inlineStr"/>
       <c r="CI22" t="inlineStr"/>
-      <c r="CJ22" t="n">
-        <v>10</v>
-      </c>
-      <c r="CK22" t="n">
-        <v>78</v>
-      </c>
-      <c r="CL22" t="n">
-        <v>10</v>
-      </c>
-      <c r="CM22" t="n">
-        <v>67</v>
-      </c>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="inlineStr"/>
+      <c r="CM22" t="inlineStr"/>
       <c r="CN22" t="inlineStr"/>
       <c r="CO22" t="inlineStr"/>
       <c r="CP22" t="inlineStr"/>
@@ -4883,27 +4767,27 @@
       <c r="CV22" t="inlineStr"/>
       <c r="CW22" t="inlineStr">
         <is>
-          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Hoffmann 79 ST PAC 79 SHO 79 PAS 71 DRI 77 DEF 47 PHY 75 R 3 ★ 2 Hoffmann 80 ST PAC 79 SHO 79 PAS 71 DRI 77 DEF 47 PHY 75 R 3 ★ 2 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
+          <t>A · A 3 Level 1 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7]</t>
+          <t>Tactical Ascent [SP+ 14]</t>
         </is>
       </c>
       <c r="DA22" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 89% 11%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 30 days in 30 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -4915,17 +4799,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -4936,16 +4820,8 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>CM, CDM</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -4954,35 +4830,27 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>80</v>
-      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>79</v>
-      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>79</v>
-      </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="inlineStr"/>
@@ -5050,27 +4918,445 @@
       <c r="CV23" t="inlineStr"/>
       <c r="CW23" t="inlineStr">
         <is>
+          <t>3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES 3</t>
+        </is>
+      </c>
+      <c r="CX23" t="inlineStr">
+        <is>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CZ23" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11]</t>
+        </is>
+      </c>
+      <c r="DA23" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 30 days in 30 days 36% 64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CAM, CM</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>78</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>82</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>83</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>82</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>78</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>78</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>70</v>
+      </c>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>72</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>62</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>77</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>77</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>76</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>76</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>76</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr"/>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>78</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>10</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>67</v>
+      </c>
+      <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr"/>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr"/>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Hoffmann 79 ST PAC 79 SHO 79 PAS 71 DRI 77 DEF 47 PHY 75 R 3 ★ 2 Hoffmann 80 ST PAC 79 SHO 79 PAS 71 DRI 77 DEF 47 PHY 75 R 3 ★ 2 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
+        </is>
+      </c>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CZ24" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7]</t>
+        </is>
+      </c>
+      <c r="DA24" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 30 days in 30 days 90% 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Premium Season Pass</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CM, CDM</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>CAM Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>79</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>79</v>
+      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr"/>
+      <c r="CG25" t="inlineStr"/>
+      <c r="CH25" t="inlineStr"/>
+      <c r="CI25" t="inlineStr"/>
+      <c r="CJ25" t="inlineStr"/>
+      <c r="CK25" t="inlineStr"/>
+      <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr"/>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="inlineStr"/>
+      <c r="CV25" t="inlineStr"/>
+      <c r="CW25" t="inlineStr">
+        <is>
           <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Morton 79 CDM PAC 65 SHO 65 PAS 80 DRI 77 DEF 74 PHY 74 CM R 3 ★ 3 Morton 80 CDM PAC 65 SHO 65 PAS 80 DRI 77 DEF 75 PHY 74 CM R 3 ★ 3 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
         </is>
       </c>
-      <c r="CX23" t="inlineStr">
-        <is>
-          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
-      <c r="CY23" t="inlineStr">
-        <is>
-          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
-      <c r="CZ23" t="inlineStr">
+      <c r="CX25" t="inlineStr">
+        <is>
+          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CY25" t="inlineStr">
+        <is>
+          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CZ25" t="inlineStr">
         <is>
           <t>Midfield Polish [SP+ 1]</t>
         </is>
       </c>
-      <c r="DA23" t="inlineStr">
-        <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
+      <c r="DA25" t="inlineStr">
+        <is>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 30 days in 30 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -16124,12 +16410,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>CAM Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Excluded Position CAM Details Submit by in 1 month Expiry in 1 month Coins Cost Free Points Cost Free</t>
+          <t>Excluded Position CAM Details Submit by in 30 days Expiry in 30 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -16211,7 +16497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16259,12 +16545,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Flank Identity NEW</t>
+          <t>Flank Identity</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Flank Identity NEW Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 10 days in 17 days 25% 75%</t>
+          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 9 days in 16 days 25% 75%</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16577,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 8 days in 15 days 26% 74%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 7 days in 14 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -16318,7 +16604,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 7 days in 14 days 75% 25%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 6 days in 13 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -16345,7 +16631,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 24 days in 24 days 84% 16%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 23 days in 23 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16658,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 2 days in 9 days 52% 48%</t>
+          <t>Creative Crossroads 15,000 150 Refine your central creator's technical foundation, deciding at a crucial turn whether to direct their game toward decisive distribution or a sharper scoring edge. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 81 RM PAC 83 SHO 74 PAS 79 DRI 79 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 80.5 REQUIREMENTS Overall Max. 79 Position CAM Excluded Position CDM, ST Max PS 7 Pace Max. 85 UPGRADES B +5 OVR 81 +7 Sprint Speed 82 +7 Shot Power 80 +7 Fk Accuracy 80 +7 Curve 79 +7 Balance 82 +7 Acceleration 82 +7 Positioning 79 +7 Volleys 77 +7 Short Pass 78 +7 Agility 82 +5 Stamina 75 +7 Finishing 80 +7 Long Shots 77 +7 Dribbling 80 +7 Composure 76 CAM Shadow Striker + 3 in 20 hours in 8 days 52% 48%</t>
         </is>
       </c>
     </row>
@@ -16389,17 +16675,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200</t>
+          <t>Intro to Repeatable Evolutions 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 20 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 19% 81%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.3 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.5 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 82% 18%</t>
         </is>
       </c>
     </row>
@@ -16416,17 +16702,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200</t>
+          <t>Intro to Evolutions</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 19 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 16% 84%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 89% 11%</t>
         </is>
       </c>
     </row>
@@ -16443,17 +16729,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
+          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200</t>
+          <t>Intro to Training Camp EVOs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 25,000 200 Turn back the clock and apply the exclusive Ones to Watch Retro 18 rarity to any qualified player. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 23 days in 23 days 21% 79%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 86% 14%</t>
         </is>
       </c>
     </row>
@@ -16470,17 +16756,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2</t>
+          <t>Repeat Delivery 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.3 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.5 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 82% 18%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 22 days in 22 days 92% 8%</t>
         </is>
       </c>
     </row>
@@ -16497,98 +16783,98 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions</t>
+          <t>Intro to Pathway Evolutions</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Cerezo 65 RB PAC 63 SHO 39 PAS 49 DRI 58 DEF 64 PHY 77 LB R 2 ★ 3 RB 56.5 Cerezo 79 RB PAC 80 SHO 39 PAS 70 DRI 78 DEF 75 PHY 78 LB R 2 ★ 3 RB 75.9 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 89% 11%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
+          <t>https://www.fut.gg/evolutions/2527-gallery-excellence/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs</t>
+          <t>Gallery Excellence NEW</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 85% 15%</t>
+          <t>Gallery Excellence NEW Unlocked by completing the Gallery Milestone objective REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 25% 75%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2526-season-ladder-excellence-sp-27/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2</t>
+          <t>Season Ladder Excellence [SP 27] NEW</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 23 days in 23 days 92% 8%</t>
+          <t>Season Ladder Excellence [SP 27] NEW Unlocked by reaching level 27 in the Standard Season Pass. REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 33% 67%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2505-ones-to-watch-retro-20/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions</t>
+          <t>Ones to Watch Retro 20 [SP+ 26]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 12%</t>
+          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -16600,22 +16886,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2504-ones-to-watch-retro-19/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pinged Pass</t>
+          <t>Ones to Watch Retro 19 [SP+ 26]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 94% 6%</t>
+          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -16627,22 +16913,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2503-ones-to-watch-retro-18/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Ones to Watch Retro 18 [SP 27]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
+          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 29 days in 29 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -16654,22 +16940,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28]</t>
+          <t>Pinged Pass</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 1 month in 1 month 89% 11%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 30 days in 30 days 95% 5%</t>
         </is>
       </c>
     </row>
@@ -16681,22 +16967,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27]</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 76% 24%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 33% 67%</t>
         </is>
       </c>
     </row>
@@ -16713,17 +16999,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26]</t>
+          <t>Shooting Practice [SP+ 28]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 1 month in 1 month 92% 8%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 30 days in 30 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -16735,22 +17021,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14]</t>
+          <t>Creative or Composed? [SP 27]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 1 month in 1 month 88% 12%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 30 days in 30 days 79% 21%</t>
         </is>
       </c>
     </row>
@@ -16762,22 +17048,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11]</t>
+          <t>Winger Glow Up [SP+ 26]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 1 month in 1 month 35% 65%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 30 days in 30 days 92% 8%</t>
         </is>
       </c>
     </row>
@@ -16789,22 +17075,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7]</t>
+          <t>Tactical Ascent [SP+ 14]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 1 month in 1 month 89% 11%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 30 days in 30 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -16816,22 +17102,76 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11]</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 30 days in 30 days 36% 64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Standard Season Pass</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7]</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 30 days in 30 days 90% 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Premium Season Pass</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Midfield Polish [SP+ 1]</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 1 month in 1 month 27% 73%</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 30 days in 30 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -16877,21 +17217,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Current_Count</t>
+          <t>Reward_Count</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reward_Count</t>
+          <t>Current_Count</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -16902,7 +17242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28T22:32:21</t>
+          <t>2026-09-29T21:23:55</t>
         </is>
       </c>
     </row>
@@ -16925,7 +17265,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA27"/>
+  <dimension ref="A1:DA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,12 +961,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -979,21 +979,17 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RM, RW</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>LB, RB</t>
+          <t>ST, CDM</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -1009,10 +1005,10 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -1026,140 +1022,136 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>82</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>81</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>80</v>
+      </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>76</v>
-      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>75</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>75</v>
-      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
       <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
+      <c r="BN2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>76</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>76</v>
+      </c>
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="inlineStr"/>
       <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="n">
+      <c r="BX2" t="n">
         <v>5</v>
       </c>
-      <c r="CA2" t="n">
-        <v>79</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>81</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>80</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CG2" t="n">
+      <c r="BY2" t="n">
         <v>78</v>
       </c>
-      <c r="CH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>81</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>75</v>
-      </c>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
       <c r="CL2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CM2" t="n">
         <v>75</v>
       </c>
-      <c r="CN2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>78</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>79</v>
-      </c>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>3</v>
+      </c>
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>+5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 Level 1 Natan 79 CB PAC 66 SHO 33 PAS 59 DRI 66 DEF 79 PHY 80 L 2 ★ 2 Natan 80 CB PAC 66 SHO 33 PAS 60 DRI 66 DEF 79 PHY 80 L 2 ★ 2 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78</t>
+          <t>A +7 OVR 83 +1 SM 3 +8 Sprint Speed 82 +5 Balance 76 +5 Composure 78 +8 Acceleration 82 +5 Agility 78 +5 Reactions 76 +10 Stamina 75 +5 Positioning 81 +5 Finishing 80 +5 Shot Power 80 3 Level 1 Víctor Muñoz 79 LM PAC 94 SHO 74 PAS 70 DRI 80 DEF 50 PHY 65 RM RW LW R 3 ★ 3 Víctor Muñoz 83 LM PAC 94 SHO 74 PAS 70 DRI 80 DEF 50 PHY 65 RM RW LW R 3 ★ 3 UPGRADES +7 OVR 83 +1 SM 3 +5 Sprint Speed 82 +5 Balance 76 +5 Composure 78</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 Details Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 Details Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Backline Conductor NEW 2</t>
+          <t>Wing Specialization NEW</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Backline Conductor NEW 2 Fortify your central defender's core defensive instincts and physical stature while sharpening their distribution to build play confidently from the deep. Egan-Riley 75 CB PAC 80 SHO 32 PAS 61 DRI 66 DEF 74 PHY 79 R 2 ★ 3 CB 73.5 Egan-Riley 80 CB PAC 80 SHO 32 PAS 64 DRI 66 DEF 79 PHY 80 R 2 ★ 3 CB 76.8 REQUIREMENTS Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 in 10 days in 17 days 71% 29%</t>
+          <t>Wing Specialization NEW Boost your winger's attributes and specialize your Level 3 rewards to gain clinical finishing, rapid speed, or precise Tiki Taka play. Müller 77 LB PAC 78 SHO 69 PAS 77 DRI 79 DEF 76 PHY 69 RB RM R 3 ★ 3 RB 77.7 Müller 83 LB PAC 86 SHO 69 PAS 77 DRI 80 DEF 76 PHY 70 RB RM R 3 ★ 3 RB 82.1 REQUIREMENTS Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 UPGRADES A +7 OVR 83 +1 SM 3 +8 Sprint Speed 82 +5 Balance 76 +5 Composure 78 +8 Acceleration 82 +5 Agility 78 +5 Reactions 76 +10 Stamina 75 +5 Positioning 81 +5 Finishing 80 +5 Shot Power 80 3 in 10 days in 17 days 37% 63%</t>
         </is>
       </c>
     </row>
@@ -1310,17 +1302,17 @@
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>+10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 Level 1 Diaw 74 GK DIV 75 HAN 72 KIC 71 REF 75 SPD 43 POS 73 R 1 ★ 2 Diaw 79 GK DIV 75 HAN 72 KIC 74 REF 80 SPD 47 POS 73 R 1 ★ 2 UPGRADES +10 OVR 79 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80</t>
+          <t>+10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 Level 1 Kokubo 74 GK DIV 76 HAN 70 KIC 64 REF 75 SPD 41 POS 71 R 1 ★ 3 Kokubo 79 GK DIV 76 HAN 70 KIC 72 REF 80 SPD 44 POS 71 R 1 ★ 3 UPGRADES +10 OVR 79 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position GK Max PS 7 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position GK Max PS 7 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position GK Max PS 7 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position GK Max PS 7 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1330,7 +1322,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Trust the Keeper Trust the keeper and give them time to work their magic. Sharpen their skills between the sticks and turn your last line of defence into a wall attackers cannot break. Berisha 71 GK DIV 67 HAN 71 KIC 67 REF 70 SPD 24 POS 71 L 1 ★ 2 GK 70.5 Berisha 79 GK DIV 80 HAN 77 KIC 74 REF 80 SPD 34 POS 77 L 1 ★ 2 GK 80.4 REQUIREMENTS Overall Max. 74 Position GK Max PS 7 UPGRADES +10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 TRAINING TIME 1 day in 9 days in 16 days 73% 27%</t>
+          <t>Trust the Keeper Trust the keeper and give them time to work their magic. Sharpen their skills between the sticks and turn your last line of defence into a wall attackers cannot break. Berisha 71 GK DIV 67 HAN 71 KIC 67 REF 70 SPD 24 POS 71 L 1 ★ 2 GK 70.5 Berisha 79 GK DIV 80 HAN 77 KIC 74 REF 80 SPD 34 POS 77 L 1 ★ 2 GK 80.4 REQUIREMENTS Overall Max. 74 Position GK Max PS 7 UPGRADES +10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 TRAINING TIME 1 day in 8 days in 15 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -1537,17 +1529,17 @@
       <c r="CV4" t="inlineStr"/>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 Level 1 Akgün 79 CAM PAC 85 SHO 75 PAS 75 DRI 81 DEF 46 PHY 58 RM LM RW LW L 4 ★ 3 Akgün 80 CAM PAC 85 SHO 75 PAS 75 DRI 81 DEF 46 PHY 58 RM LM RW LW L 4 ★ 3 UPGRADES +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77</t>
+          <t>A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 Level 1 Yeremy Pino 79 LW PAC 75 SHO 74 PAS 80 DRI 81 DEF 38 PHY 51 RM LM RW R 3 ★ 4 Yeremy Pino 80 LW PAC 78 SHO 74 PAS 80 DRI 81 DEF 38 PHY 52 RM LM RW R 3 ★ 4 UPGRADES +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1557,7 +1549,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 7 days in 14 days 26% 74%</t>
+          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 6 days in 13 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -1760,17 +1752,17 @@
       <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 Level 1 Amrabat 79 CDM PAC 73 SHO 70 PAS 74 DRI 76 DEF 76 PHY 84 CM R 3 ★ 2 Amrabat 80 CDM PAC 73 SHO 70 PAS 76 DRI 76 DEF 76 PHY 84 CM R 3 ★ 2 UPGRADES +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75</t>
+          <t>B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 Level 1 Angelina 79 CM PAC 72 SHO 70 PAS 78 DRI 79 DEF 65 PHY 68 CDM LM LW R 4 ★ 4 Angelina 80 CM PAC 74 SHO 70 PAS 79 DRI 79 DEF 65 PHY 68 CDM LM LW R 4 ★ 4 UPGRADES +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1780,7 +1772,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 5 days in 12 days 26% 74%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 4 days in 11 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -1983,17 +1975,17 @@
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 Level 1 Gabriel Jesus 79 ST PAC 78 SHO 79 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 Gabriel Jesus 81 ST PAC 81 SHO 80 PAS 74 DRI 84 DEF 39 PHY 68 CAM R 4 ★ 3 UPGRADES +5 OVR 81 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82</t>
+          <t>A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 Level 1 Evanilson 79 ST PAC 75 SHO 78 PAS 69 DRI 77 DEF 37 PHY 75 R 3 ★ 4 Evanilson 81 ST PAC 78 SHO 80 PAS 69 DRI 77 DEF 37 PHY 75 R 3 ★ 4 UPGRADES +5 OVR 81 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -2003,7 +1995,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 4 days in 11 days 74% 26%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 3 days in 10 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2206,17 @@
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>+40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 Level 1 Puerta 74 CDM PAC 63 SHO 64 PAS 72 DRI 74 DEF 69 PHY 78 CM R 2 ★ 3 Puerta 79 CDM PAC 63 SHO 64 PAS 74 DRI 74 DEF 72 PHY 78 CM R 2 ★ 3 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77</t>
+          <t>+40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 Level 1 Matondo 74 CM PAC 74 SHO 61 PAS 68 DRI 77 DEF 65 PHY 75 CDM R 3 ★ 3 Matondo 79 CM PAC 74 SHO 61 PAS 70 DRI 77 DEF 67 PHY 76 CDM R 3 ★ 3 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 21 days Expiry in 21 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 20 days Expiry in 20 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 21 days Expiry in 21 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 20 days Expiry in 20 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
@@ -2234,7 +2226,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 21 days in 21 days 83% 17%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 20 days in 20 days 83% 17%</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2397,7 @@
       <c r="CV8" t="inlineStr"/>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 Millene Cabral 79 ST PAC 78 SHO 79 PAS 72 DRI 78 DEF 32 PHY 72 CAM R 4 ★ 3 Millene Cabral 80 ST PAC 78 SHO 79 PAS 73 DRI 78 DEF 32 PHY 72 CAM R 4 ★ 3 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
+          <t>+1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 Level 1 DeMelo 79 CM PAC 64 SHO 76 PAS 80 DRI 80 DEF 62 PHY 70 CAM ST R 4 ★ 3 DeMelo 80 CM PAC 64 SHO 76 PAS 80 DRI 80 DEF 62 PHY 70 CAM ST R 4 ★ 3 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
@@ -2640,7 +2632,7 @@
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Neville 75 RB PAC 73 SHO 70 PAS 73 DRI 72 DEF 74 PHY 79 LB R 3 ★ 4 Neville 79 RB PAC 76 SHO 70 PAS 73 DRI 72 DEF 75 PHY 79 LB R 3 ★ 4 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
+          <t>+34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 Level 1 Assignon 75 RB PAC 76 SHO 53 PAS 64 DRI 73 DEF 73 PHY 72 RM R 3 ★ 3 Assignon 79 RB PAC 77 SHO 53 PAS 67 DRI 73 DEF 74 PHY 72 RM R 3 ★ 3 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
@@ -2795,7 +2787,7 @@
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 85% of GG users upvoted this Evolution. Vote Now! 85% 15% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Sara Ortega 80 LM PAC 85 SHO 77 PAS 79 DRI 83 DEF 62 PHY 70 RB LB CDM RM CM R 3 ★ 3 Sara Ortega 80 LM PAC 85 SHO 77 PAS 79 DRI 83 DEF 62 PHY 70 RB LB CDM RM CM R 3 ★ 3 UPGRADES RB Fullback +</t>
+          <t>when the training session concludes. OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 84% of GG users upvoted this Evolution. Vote Now! 84% 16% Completion Difficulty Easy Number of Games 0 Recommended Position RB Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Evolution Upgrades RB Fullback + Level 1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 UPGRADES RB Fullback +</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
@@ -2815,7 +2807,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 85% 15%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 84% 16%</t>
         </is>
       </c>
     </row>
@@ -2832,39 +2824,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>LM, RM</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>LB, RB</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -2872,19 +2852,15 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>78</v>
-      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
@@ -2897,18 +2873,10 @@
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>80</v>
-      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
@@ -2921,74 +2889,30 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>84</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>78</v>
-      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>76</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>76</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>78</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>75</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>73</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>74</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>74</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>75</v>
-      </c>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
       <c r="BZ11" t="inlineStr"/>
       <c r="CA11" t="inlineStr"/>
       <c r="CB11" t="inlineStr"/>
@@ -3001,89 +2925,89 @@
       <c r="CI11" t="inlineStr"/>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="inlineStr"/>
-      <c r="CL11" t="n">
-        <v>15</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>78</v>
-      </c>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
       <c r="CN11" t="inlineStr"/>
       <c r="CO11" t="inlineStr"/>
       <c r="CP11" t="inlineStr"/>
       <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="n">
-        <v>2</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>2</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>3</v>
-      </c>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Erenbjerg 74 CAM PAC 67 SHO 72 PAS 71 DRI 75 DEF 52 PHY 64 CDM RM CM RW L 3 ★ 3 Erenbjerg 78 CAM PAC 70 SHO 72 PAS 72 DRI 75 DEF 52 PHY 64 CDM RM CM RW L 3 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 87% of GG users upvoted this Evolution. Vote Now! 87% 13% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 RB 82.9 Rosario 80 CDM PAC 73 SHO 66 PAS 72 DRI 77 DEF 80 PHY 84 CB CM R 3 ★ 3 CDM 81.1 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 RB 82.9 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Rosario 80 CDM PAC 73 SHO 66 PAS 72 DRI 77 DEF 80 PHY 84 CB CM R 3 ★ 3 CDM 81.1 Evolution Upgrades B 4 Level 1 Mastantuono 80 RM PAC 80 SHO 78 PAS 79 DRI 83 DEF 53 PHY 70 CAM RW L 3 ★ 3 Mastantuono 80 RM PAC 80 SHO 78 PAS 79 DRI 83 DEF 53 PHY 70 CAM RW L 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 20 days Expiry in 20 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 20 days Expiry in 20 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2</t>
+          <t>Intro to Pathway Evolutions</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 20 days in 20 days 92% 8%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 87% 13%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>LB, RB</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -3091,15 +3015,19 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>80</v>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
@@ -3128,16 +3056,28 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>76</v>
+      </c>
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
+      <c r="BH12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>75</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>75</v>
+      </c>
       <c r="BL12" t="inlineStr"/>
       <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="inlineStr"/>
@@ -3152,24 +3092,60 @@
       <c r="BW12" t="inlineStr"/>
       <c r="BX12" t="inlineStr"/>
       <c r="BY12" t="inlineStr"/>
-      <c r="BZ12" t="inlineStr"/>
-      <c r="CA12" t="inlineStr"/>
-      <c r="CB12" t="inlineStr"/>
-      <c r="CC12" t="inlineStr"/>
-      <c r="CD12" t="inlineStr"/>
-      <c r="CE12" t="inlineStr"/>
-      <c r="CF12" t="inlineStr"/>
-      <c r="CG12" t="inlineStr"/>
-      <c r="CH12" t="inlineStr"/>
-      <c r="CI12" t="inlineStr"/>
-      <c r="CJ12" t="inlineStr"/>
-      <c r="CK12" t="inlineStr"/>
-      <c r="CL12" t="inlineStr"/>
-      <c r="CM12" t="inlineStr"/>
-      <c r="CN12" t="inlineStr"/>
-      <c r="CO12" t="inlineStr"/>
-      <c r="CP12" t="inlineStr"/>
-      <c r="CQ12" t="inlineStr"/>
+      <c r="BZ12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>79</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>81</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>80</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>78</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>81</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>75</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>75</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>78</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>79</v>
+      </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
@@ -3177,27 +3153,27 @@
       <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 88% of GG users upvoted this Evolution. Vote Now! 88% 13% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Rosario 80 CDM PAC 73 SHO 66 PAS 72 DRI 77 DEF 80 PHY 84 CB CM R 3 ★ 3 CDM 81.1 Černý 77 RM PAC 85 SHO 72 PAS 71 DRI 77 DEF 39 PHY 65 CM CAM RW L 4 ★ 3 RM 78.0 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 RB 82.9 Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 RB 82.9 Evolution Upgrades B 4 Level 1 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>+5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 Level 1 Boyomo 79 CB PAC 77 SHO 38 PAS 59 DRI 57 DEF 78 PHY 86 R 2 ★ 2 Boyomo 80 CB PAC 77 SHO 38 PAS 59 DRI 57 DEF 79 PHY 86 R 2 ★ 2 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions</t>
+          <t>Backline Conductor 2</t>
         </is>
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 13%</t>
+          <t>Backline Conductor 2 Fortify your central defender's core defensive instincts and physical stature while sharpening their distribution to build play confidently from the deep. Egan-Riley 75 CB PAC 80 SHO 32 PAS 61 DRI 66 DEF 74 PHY 79 R 2 ★ 3 CB 73.5 Egan-Riley 80 CB PAC 80 SHO 32 PAS 64 DRI 66 DEF 79 PHY 80 R 2 ★ 3 CB 76.8 REQUIREMENTS Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 in 9 days in 16 days 69% 31%</t>
         </is>
       </c>
     </row>
@@ -3356,27 +3332,27 @@
       <c r="CV13" t="inlineStr"/>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>+1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 Level 1 Muriqi 83 ST PAC 75 SHO 85 PAS 70 DRI 75 DEF 35 PHY 85 L 3 ★ 4 Muriqi 84 ST PAC 77 SHO 85 PAS 70 DRI 77 DEF 35 PHY 85 L 3 ★ 4 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3</t>
+          <t>+1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 Level 1 Edna Imade 83 ST PAC 76 SHO 83 PAS 65 DRI 77 DEF 45 PHY 80 R 3 ★ 3 Edna Imade 84 ST PAC 78 SHO 83 PAS 65 DRI 79 DEF 45 PHY 80 R 3 ★ 3 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3</t>
         </is>
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 21 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 20 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 21 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 20 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>Frontline Flair NEW 2</t>
+          <t>Frontline Flair 2</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Frontline Flair NEW 2 Unlocked via the Token Store for 100 tokens Ueda 80 ST PAC 80 SHO 80 PAS 66 DRI 79 DEF 32 PHY 77 R 3 ★ 4 ST 80.2 Ueda 81 ST PAC 82 SHO 81 PAS 66 DRI 81 DEF 32 PHY 77 R 3 ★ 4 ST 81.7 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 21 days in 28 days 73% 27%</t>
+          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Ueda 80 ST PAC 80 SHO 80 PAS 66 DRI 79 DEF 32 PHY 77 R 3 ★ 4 ST 80.2 Ueda 81 ST PAC 82 SHO 81 PAS 66 DRI 81 DEF 32 PHY 77 R 3 ★ 4 ST 81.7 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 20 days in 27 days 77% 23%</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3475,7 @@
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Zidane 94 CAM PAC 83 SHO 90 PAS 94 DRI 94 DEF 73 PHY 84 CM R 5 ★ 5 Zidane 94 CAM PAC 83 SHO 90 PAS 94 DRI 94 DEF 73 PHY 84 CM R 5 ★ 5 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX14" t="inlineStr">
@@ -3519,7 +3495,7 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Gallery Excellence Unlocked by completing the Gallery Milestone objective Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 64% 36%</t>
+          <t>Gallery Excellence Unlocked by completing the Gallery Milestone objective Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 69% 31%</t>
         </is>
       </c>
     </row>
@@ -3642,17 +3618,17 @@
       <c r="CV15" t="inlineStr"/>
       <c r="CW15" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Beckenbauer 93 CB PAC 82 SHO 73 PAS 88 DRI 84 DEF 93 PHY 83 CDM CM R 3 ★ 4 Beckenbauer 93 CB PAC 82 SHO 73 PAS 88 DRI 84 DEF 93 PHY 83 CDM CM R 3 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Garrincha 93 RW PAC 90 SHO 87 PAS 92 DRI 95 DEF 40 PHY 66 RM R 5 ★ 4 Garrincha 93 RW PAC 90 SHO 87 PAS 92 DRI 95 DEF 40 PHY 66 RM R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ15" t="inlineStr">
@@ -3662,7 +3638,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 43% 57%</t>
+          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 26 days in 26 days 50% 50%</t>
         </is>
       </c>
     </row>
@@ -3785,17 +3761,17 @@
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Beckenbauer 93 CB PAC 82 SHO 73 PAS 88 DRI 84 DEF 93 PHY 83 CDM CM R 3 ★ 4 Beckenbauer 93 CB PAC 82 SHO 73 PAS 88 DRI 84 DEF 93 PHY 83 CDM CM R 3 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ16" t="inlineStr">
@@ -3805,7 +3781,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 19% 81%</t>
+          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 26 days in 26 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3904,17 @@
       <c r="CV17" t="inlineStr"/>
       <c r="CW17" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Maldini 93 CB PAC 85 SHO 55 PAS 75 DRI 72 DEF 95 PHY 84 LB R 2 ★ 4 Maldini 93 CB PAC 85 SHO 55 PAS 75 DRI 72 DEF 95 PHY 84 LB R 2 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Cruyff 93 CAM PAC 90 SHO 91 PAS 90 DRI 94 DEF 42 PHY 73 ST R 5 ★ 5 Cruyff 93 CAM PAC 90 SHO 91 PAS 90 DRI 94 DEF 42 PHY 73 ST R 5 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ17" t="inlineStr">
@@ -3948,7 +3924,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 16% 84%</t>
+          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 26 days in 26 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -4071,17 +4047,17 @@
       <c r="CV18" t="inlineStr"/>
       <c r="CW18" t="inlineStr">
         <is>
-          <t>No upgrades Level 1 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 Ronaldinho 93 LW PAC 91 SHO 89 PAS 90 DRI 95 DEF 38 PHY 80 LM CAM R 5 ★ 4 UPGRADES No upgrades</t>
+          <t>No upgrades Level 1 Ronaldo 94 ST PAC 94 SHO 94 PAS 79 DRI 94 DEF 43 PHY 75 R 5 ★ 5 Ronaldo 94 ST PAC 94 SHO 94 PAS 79 DRI 94 DEF 43 PHY 75 R 5 ★ 5 UPGRADES No upgrades</t>
         </is>
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ18" t="inlineStr">
@@ -4091,7 +4067,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 21% 79%</t>
+          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 26 days in 26 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -4222,17 +4198,17 @@
       <c r="CV19" t="inlineStr"/>
       <c r="CW19" t="inlineStr">
         <is>
-          <t>3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 UPGRADES 3</t>
+          <t>3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ19" t="inlineStr">
@@ -4242,7 +4218,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 28 days in 28 days 95% 5%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 27 days in 27 days 95% 5%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4361,7 @@
       <c r="CV20" t="inlineStr"/>
       <c r="CW20" t="inlineStr">
         <is>
-          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Sinayoko 82 ST PAC 81 SHO 83 PAS 73 DRI 81 DEF 48 PHY 82 LM CAM LW R 3 ★ 4 Sinayoko 83 ST PAC 81 SHO 83 PAS 74 DRI 81 DEF 48 PHY 82 LM CAM LW R 3 ★ 4 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
+          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Kostoulas 82 ST PAC 85 SHO 79 PAS 68 DRI 81 DEF 50 PHY 79 R 3 ★ 3 Kostoulas 83 ST PAC 85 SHO 79 PAS 70 DRI 81 DEF 50 PHY 79 R 3 ★ 3 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
         </is>
       </c>
       <c r="CX20" t="inlineStr">
@@ -4405,7 +4381,7 @@
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 32% 68%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
         </is>
       </c>
     </row>
@@ -4544,17 +4520,17 @@
       <c r="CV21" t="inlineStr"/>
       <c r="CW21" t="inlineStr">
         <is>
-          <t>B · A 4 Level 1 Dudinha 81 LM PAC 71 SHO 73 PAS 78 DRI 81 DEF 41 PHY 52 LW L 4 ★ 3 Dudinha 81 LM PAC 71 SHO 73 PAS 78 DRI 81 DEF 41 PHY 52 LW L 4 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>B · A 4 Level 1 Akliouche 81 CAM PAC 74 SHO 72 PAS 80 DRI 84 DEF 48 PHY 62 RM CM RW L 4 ★ 3 Akliouche 81 CAM PAC 74 SHO 72 PAS 80 DRI 84 DEF 48 PHY 62 RM CM RW L 4 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ21" t="inlineStr">
@@ -4564,7 +4540,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 28 days in 28 days 86% 14%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 27 days in 27 days 86% 14%</t>
         </is>
       </c>
     </row>
@@ -4695,17 +4671,17 @@
       <c r="CV22" t="inlineStr"/>
       <c r="CW22" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Sarr 79 CM PAC 66 SHO 66 PAS 77 DRI 79 DEF 78 PHY 74 CDM R 2 ★ 3 Sarr 79 CM PAC 66 SHO 66 PAS 77 DRI 79 DEF 78 PHY 74 CDM R 2 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>A · A 3 Level 1 Gerard Martín 79 CB PAC 74 SHO 53 PAS 75 DRI 70 DEF 80 PHY 79 LB LM L 3 ★ 3 Gerard Martín 79 CB PAC 74 SHO 53 PAS 75 DRI 70 DEF 80 PHY 79 LB LM L 3 ★ 3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ22" t="inlineStr">
@@ -4715,7 +4691,7 @@
       </c>
       <c r="DA22" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 28 days in 28 days 79% 21%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 27 days in 27 days 79% 21%</t>
         </is>
       </c>
     </row>
@@ -4954,17 +4930,17 @@
       <c r="CV23" t="inlineStr"/>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Sudakov 78 CAM PAC 80 SHO 76 PAS 77 DRI 80 DEF 60 PHY 72 LM LW R 3 ★ 4 Sudakov 83 CAM PAC 80 SHO 76 PAS 77 DRI 82 DEF 60 PHY 72 LM LW R 3 ★ 4 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
+          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Godts 78 LW PAC 83 SHO 72 PAS 71 DRI 84 DEF 42 PHY 65 LM R 4 ★ 3 Godts 83 LW PAC 83 SHO 72 PAS 72 DRI 84 DEF 42 PHY 65 LM R 4 ★ 3 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
         </is>
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ23" t="inlineStr">
@@ -4974,7 +4950,7 @@
       </c>
       <c r="DA23" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 28 days in 28 days 93% 7%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 27 days in 27 days 93% 7%</t>
         </is>
       </c>
     </row>
@@ -5110,12 +5086,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ24" t="inlineStr">
@@ -5125,7 +5101,7 @@
       </c>
       <c r="DA24" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 28 days in 28 days 88% 12%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 27 days in 27 days 87% 13%</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5237,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ25" t="inlineStr">
@@ -5276,7 +5252,7 @@
       </c>
       <c r="DA25" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 28 days in 28 days 38% 62%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 27 days in 27 days 38% 62%</t>
         </is>
       </c>
     </row>
@@ -5507,17 +5483,17 @@
       <c r="CV26" t="inlineStr"/>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Panichelli 79 ST PAC 69 SHO 81 PAS 63 DRI 73 DEF 28 PHY 82 R 3 ★ 3 Panichelli 80 ST PAC 69 SHO 81 PAS 64 DRI 73 DEF 28 PHY 82 R 3 ★ 3 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
+          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Amanda Gutierres 79 ST PAC 73 SHO 78 PAS 62 DRI 74 DEF 37 PHY 77 R 3 ★ 4 Amanda Gutierres 80 ST PAC 73 SHO 79 PAS 62 DRI 74 DEF 37 PHY 77 R 3 ★ 4 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
         </is>
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ26" t="inlineStr">
@@ -5527,7 +5503,7 @@
       </c>
       <c r="DA26" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 28 days in 28 days 89% 11%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 27 days in 27 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5543,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CAM Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>CAM Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -5674,17 +5650,17 @@
       <c r="CV27" t="inlineStr"/>
       <c r="CW27" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Nildén 79 LB PAC 83 SHO 52 PAS 73 DRI 72 DEF 74 PHY 75 CDM L 3 ★ 3 Nildén 80 LB PAC 83 SHO 52 PAS 74 DRI 72 DEF 75 PHY 75 CDM L 3 ★ 3 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
+          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Avdullahu 79 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 72 PHY 75 CM R 2 ★ 4 Avdullahu 80 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 73 PHY 75 CM R 2 ★ 4 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
         </is>
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ27" t="inlineStr">
@@ -5694,7 +5670,238 @@
       </c>
       <c r="DA27" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 28 days in 28 days 26% 74%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 27 days in 27 days 25% 75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LM, RM</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>LB, RB</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>84</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>78</v>
+      </c>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>76</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>76</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>78</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>75</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>73</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>74</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ28" t="inlineStr"/>
+      <c r="CA28" t="inlineStr"/>
+      <c r="CB28" t="inlineStr"/>
+      <c r="CC28" t="inlineStr"/>
+      <c r="CD28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr"/>
+      <c r="CF28" t="inlineStr"/>
+      <c r="CG28" t="inlineStr"/>
+      <c r="CH28" t="inlineStr"/>
+      <c r="CI28" t="inlineStr"/>
+      <c r="CJ28" t="inlineStr"/>
+      <c r="CK28" t="inlineStr"/>
+      <c r="CL28" t="n">
+        <v>15</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>78</v>
+      </c>
+      <c r="CN28" t="inlineStr"/>
+      <c r="CO28" t="inlineStr"/>
+      <c r="CP28" t="inlineStr"/>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV28" t="inlineStr"/>
+      <c r="CW28" t="inlineStr">
+        <is>
+          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Moses 74 CM PAC 75 SHO 64 PAS 70 DRI 74 DEF 70 PHY 74 CDM RM R 2 ★ 3 Moses 78 CM PAC 78 SHO 64 PAS 70 DRI 74 DEF 70 PHY 74 CDM RM R 2 ★ 3 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
+        </is>
+      </c>
+      <c r="CX28" t="inlineStr">
+        <is>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 19 days Expiry in 19 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CY28" t="inlineStr">
+        <is>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 19 days Expiry in 19 days Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
+      <c r="CZ28" t="inlineStr">
+        <is>
+          <t>Repeat Delivery 2</t>
+        </is>
+      </c>
+      <c r="DA28" t="inlineStr">
+        <is>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 19 days in 19 days 92% 8%</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J178"/>
+  <dimension ref="A1:J191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5777,19 +5984,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+5 OVR 80</t>
+          <t>+7 OVR 83</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5804,7 +6011,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -5812,28 +6019,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+5 Short Pass 75</t>
+          <t>+1 SM 3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5848,7 +6055,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -5861,23 +6068,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Heading Accuracy</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5 Heading Acc. 81</t>
+          <t>+8 Sprint Speed 82</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5892,7 +6099,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -5905,23 +6112,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sliding Tackle</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5 Sliding Tackle 81</t>
+          <t>+5 Balance 76</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5936,7 +6143,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -5949,7 +6156,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -5960,12 +6167,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+5 Strength 78</t>
+          <t>+5 Composure 78</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5980,7 +6187,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -5993,23 +6200,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5 Long Pass 75</t>
+          <t>+8 Acceleration 82</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -6024,7 +6231,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -6037,23 +6244,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Defensive Awareness</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5 Defensive Awareness 80</t>
+          <t>+5 Agility 78</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6068,7 +6275,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -6081,23 +6288,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jumping</t>
+          <t>Reactions</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+5 Jumping 75</t>
+          <t>+5 Reactions 76</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6112,7 +6319,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -6125,23 +6332,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aggression</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5 Aggression 79</t>
+          <t>+10 Stamina 75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -6156,7 +6363,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -6169,23 +6376,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5 Vision 76</t>
+          <t>+5 Positioning 81</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -6200,7 +6407,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -6213,23 +6420,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Interceptions</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5 Interceptions 79</t>
+          <t>+5 Finishing 80</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6244,7 +6451,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -6257,23 +6464,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Standing Tackle</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+5 Standing Tackle 78</t>
+          <t>+5 Shot Power 80</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -6288,7 +6495,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -6301,23 +6508,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5 Stamina 75</t>
+          <t>+5 Sprint Speed 82</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6332,7 +6539,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
@@ -10397,34 +10604,34 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>+8 OVR 78</t>
+          <t>+5 OVR 80</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10432,43 +10639,43 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>+2 SM 3</t>
+          <t>+5 Short Pass 75</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10476,43 +10683,43 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>Heading Accuracy</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>+2 WF 3</t>
+          <t>+5 Heading Acc. 81</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10525,38 +10732,38 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>Sliding Tackle</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>+5 Sprint Speed 80</t>
+          <t>+5 Sliding Tackle 81</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10569,38 +10776,38 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E111" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>+15 Short Pass 76</t>
+          <t>+5 Strength 78</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10613,38 +10820,38 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E112" t="n">
         <v>75</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>+12 Balance 75</t>
+          <t>+5 Long Pass 75</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10657,38 +10864,38 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>Defensive Awareness</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E113" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>+10 Composure 75</t>
+          <t>+5 Defensive Awareness 80</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10701,38 +10908,38 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Jumping</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E114" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>+15 Vision 84</t>
+          <t>+5 Jumping 75</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10745,38 +10952,38 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Aggression</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E115" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>+12 Long Pass 76</t>
+          <t>+5 Aggression 79</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10789,38 +10996,38 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E116" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>+12 Reactions 73</t>
+          <t>+5 Vision 76</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10833,38 +11040,38 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Interceptions</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E117" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>+15 Stamina 78</t>
+          <t>+5 Interceptions 79</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10877,38 +11084,38 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Standing Tackle</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E118" t="n">
         <v>78</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>+10 Crossing 78</t>
+          <t>+5 Standing Tackle 78</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10921,38 +11128,38 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E119" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>+12 Curve 78</t>
+          <t>+5 Stamina 75</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
@@ -10960,43 +11167,43 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>+8 Ball Control 74</t>
+          <t>+1 OVR 84</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Frontline Flair - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
     </row>
@@ -11004,43 +11211,43 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>+5 Acceleration 80</t>
+          <t>+2 PAC 84</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Frontline Flair - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
     </row>
@@ -11048,43 +11255,43 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fk Accuracy</t>
+          <t>SHO</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>+4 Fk Accuracy 80</t>
+          <t>+1 SHO 82</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Frontline Flair - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
     </row>
@@ -11092,43 +11299,43 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>+8 Agility 78</t>
+          <t>+2 DRI 84</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Frontline Flair - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
     </row>
@@ -11136,43 +11343,43 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>+8 Dribbling 74</t>
+          <t>+1 OVR 83</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
@@ -11180,28 +11387,28 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>+1 OVR 84</t>
+          <t>+4 Short Pass 83</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Frontline Flair - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11211,12 +11418,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
@@ -11224,28 +11431,28 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
         <v>84</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>+2 PAC 84</t>
+          <t>+3 Composure 84</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Frontline Flair - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11255,12 +11462,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
@@ -11273,23 +11480,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SHO</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E127" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>+1 SHO 82</t>
+          <t>+10 OVR 83</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Frontline Flair - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11299,12 +11506,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11312,28 +11519,28 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>+2 DRI 84</t>
+          <t>+1 SM 3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Frontline Flair - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -11343,12 +11550,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11356,28 +11563,28 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E129" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>+1 OVR 83</t>
+          <t>+10 Positioning 80</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11387,12 +11594,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11405,23 +11612,23 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Volleys</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E130" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>+4 Short Pass 83</t>
+          <t>+10 Volleys 74</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -11431,12 +11638,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11449,23 +11656,23 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>Fk Accuracy</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E131" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>+3 Composure 84</t>
+          <t>+10 Fk Accuracy 73</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -11475,12 +11682,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
@@ -11488,23 +11695,23 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>+10 OVR 83</t>
+          <t>+15 Agility 86</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11532,23 +11739,23 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E133" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>+1 SM 3</t>
+          <t>+15 Dribbling 84</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11581,18 +11788,18 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D134" t="n">
         <v>10</v>
       </c>
       <c r="E134" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>+10 Positioning 80</t>
+          <t>+10 Finishing 78</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11625,7 +11832,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Volleys</t>
+          <t>Penalties</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -11636,7 +11843,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>+10 Volleys 74</t>
+          <t>+10 Penalties 74</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11669,18 +11876,18 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fk Accuracy</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>10</v>
       </c>
       <c r="E136" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>+10 Fk Accuracy 73</t>
+          <t>+10 Short Pass 76</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -11713,18 +11920,18 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D137" t="n">
         <v>15</v>
       </c>
       <c r="E137" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>+15 Agility 86</t>
+          <t>+15 Balance 85</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -11757,18 +11964,18 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D138" t="n">
         <v>15</v>
       </c>
       <c r="E138" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>+15 Dribbling 84</t>
+          <t>+15 Composure 80</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -11801,18 +12008,18 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E139" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>+10 Finishing 78</t>
+          <t>+15 Acceleration 85</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11845,18 +12052,18 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Penalties</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>10</v>
       </c>
       <c r="E140" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>+10 Penalties 74</t>
+          <t>+10 Shot Power 77</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -11889,18 +12096,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>10</v>
       </c>
       <c r="E141" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>+10 Short Pass 76</t>
+          <t>+10 Vision 81</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11933,18 +12140,18 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E142" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>+15 Balance 85</t>
+          <t>+10 Long Pass 80</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -11977,18 +12184,18 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>Reactions</t>
         </is>
       </c>
       <c r="D143" t="n">
         <v>15</v>
       </c>
       <c r="E143" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>+15 Composure 80</t>
+          <t>+15 Reactions 78</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -12021,18 +12228,18 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E144" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>+15 Acceleration 85</t>
+          <t>+10 Stamina 72</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12065,18 +12272,18 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Shot Power</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E145" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>+10 Shot Power 77</t>
+          <t>+15 Sprint Speed 85</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -12109,18 +12316,18 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Long Shots</t>
         </is>
       </c>
       <c r="D146" t="n">
         <v>10</v>
       </c>
       <c r="E146" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>+10 Vision 81</t>
+          <t>+10 Long Shots 80</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -12153,18 +12360,18 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Crossing</t>
         </is>
       </c>
       <c r="D147" t="n">
         <v>10</v>
       </c>
       <c r="E147" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>+10 Long Pass 80</t>
+          <t>+10 Crossing 82</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12197,18 +12404,18 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E148" t="n">
         <v>78</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>+15 Reactions 78</t>
+          <t>+10 Curve 78</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -12241,18 +12448,18 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Ball Control</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E149" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>+10 Stamina 72</t>
+          <t>+15 Ball Control 85</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -12280,28 +12487,28 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E150" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>+15 Sprint Speed 85</t>
+          <t>+10 OVR 80</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -12311,12 +12518,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
@@ -12329,23 +12536,23 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Long Shots</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E151" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>+10 Long Shots 80</t>
+          <t>+15 Positioning 82</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -12355,12 +12562,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
@@ -12373,23 +12580,23 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Volleys</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E152" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>+10 Crossing 82</t>
+          <t>+15 Volleys 78</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -12399,12 +12606,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
@@ -12417,23 +12624,23 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Long Passing</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E153" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>+10 Curve 78</t>
+          <t>+8 Long Pass 62</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12443,12 +12650,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
@@ -12461,23 +12668,23 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>Reactions</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E154" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>+15 Ball Control 85</t>
+          <t>+10 Reactions 76</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12487,12 +12694,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
@@ -12500,23 +12707,23 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>Jumping</t>
         </is>
       </c>
       <c r="D155" t="n">
         <v>10</v>
       </c>
       <c r="E155" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>+10 OVR 80</t>
+          <t>+10 Jumping 78</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -12549,18 +12756,18 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Positioning</t>
+          <t>Finishing</t>
         </is>
       </c>
       <c r="D156" t="n">
         <v>15</v>
       </c>
       <c r="E156" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>+15 Positioning 82</t>
+          <t>+15 Finishing 83</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -12593,18 +12800,18 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Volleys</t>
+          <t>Penalties</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E157" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>+15 Volleys 78</t>
+          <t>+10 Penalties 75</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -12637,18 +12844,18 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Long Passing</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E158" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>+8 Long Pass 62</t>
+          <t>+15 Curve 77</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -12681,7 +12888,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Reactions</t>
+          <t>Ball Control</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -12692,7 +12899,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>+10 Reactions 76</t>
+          <t>+10 Ball Control 76</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -12725,18 +12932,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jumping</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D160" t="n">
         <v>10</v>
       </c>
       <c r="E160" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>+10 Jumping 78</t>
+          <t>+10 Stamina 67</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -12769,18 +12976,18 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Finishing</t>
+          <t>Acceleration</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E161" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>+15 Finishing 83</t>
+          <t>+10 Acceleration 80</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12813,18 +13020,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Penalties</t>
+          <t>Shot Power</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E162" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>+10 Penalties 75</t>
+          <t>+15 Shot Power 82</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12857,18 +13064,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Vision</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E163" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>+15 Curve 77</t>
+          <t>+8 Vision 70</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12901,18 +13108,18 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ball Control</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E164" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>+10 Ball Control 76</t>
+          <t>+15 Agility 78</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12945,18 +13152,18 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Stamina</t>
+          <t>Dribbling</t>
         </is>
       </c>
       <c r="D165" t="n">
         <v>10</v>
       </c>
       <c r="E165" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>+10 Stamina 67</t>
+          <t>+10 Dribbling 76</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12989,18 +13196,18 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D166" t="n">
         <v>10</v>
       </c>
       <c r="E166" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>+10 Acceleration 80</t>
+          <t>+10 Sprint Speed 78</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -13033,18 +13240,18 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Shot Power</t>
+          <t>Long Shots</t>
         </is>
       </c>
       <c r="D167" t="n">
         <v>15</v>
       </c>
       <c r="E167" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>+15 Shot Power 82</t>
+          <t>+15 Long Shots 78</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -13077,18 +13284,18 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D168" t="n">
         <v>8</v>
       </c>
       <c r="E168" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>+8 Vision 70</t>
+          <t>+8 Short Pass 72</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -13121,18 +13328,18 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Agility</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="D169" t="n">
         <v>15</v>
       </c>
       <c r="E169" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>+15 Agility 78</t>
+          <t>+15 Balance 77</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -13165,18 +13372,18 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Dribbling</t>
+          <t>Composure</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E170" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>+10 Dribbling 76</t>
+          <t>+8 Composure 80</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -13204,28 +13411,28 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sprint Speed</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>+10 Sprint Speed 78</t>
+          <t>+1 OVR 80</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13235,12 +13442,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
     </row>
@@ -13248,28 +13455,28 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Long Shots</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>+15 Long Shots 78</t>
+          <t>+1 PAS 79</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13279,12 +13486,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
     </row>
@@ -13292,28 +13499,28 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Short Passing</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>+8 Short Pass 72</t>
+          <t>+1 DEF 79</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13323,12 +13530,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
     </row>
@@ -13336,28 +13543,28 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Face Stat</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>OVR</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E174" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>+15 Balance 77</t>
+          <t>+8 OVR 78</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13367,12 +13574,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -13380,28 +13587,28 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sub Stat</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Composure</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>+8 Composure 80</t>
+          <t>+2 SM 3</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13411,12 +13618,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -13424,28 +13631,28 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>OVR</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>+1 OVR 80</t>
+          <t>+2 WF 3</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13455,12 +13662,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -13468,28 +13675,28 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>Sprint Speed</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E177" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>+1 PAS 79</t>
+          <t>+5 Sprint Speed 80</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13499,12 +13706,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -13512,28 +13719,28 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Face Stat</t>
+          <t>Sub Stat</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>Short Passing</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E178" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>+1 DEF 79</t>
+          <t>+15 Short Pass 76</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13543,12 +13750,584 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>12</v>
+      </c>
+      <c r="E179" t="n">
+        <v>75</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>+12 Balance 75</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Composure</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10</v>
+      </c>
+      <c r="E180" t="n">
+        <v>75</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>+10 Composure 75</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>15</v>
+      </c>
+      <c r="E181" t="n">
+        <v>84</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>+15 Vision 84</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Long Passing</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>12</v>
+      </c>
+      <c r="E182" t="n">
+        <v>76</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>+12 Long Pass 76</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Reactions</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>12</v>
+      </c>
+      <c r="E183" t="n">
+        <v>73</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>+12 Reactions 73</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>15</v>
+      </c>
+      <c r="E184" t="n">
+        <v>78</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>+15 Stamina 78</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Crossing</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10</v>
+      </c>
+      <c r="E185" t="n">
+        <v>78</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>+10 Crossing 78</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Curve</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>12</v>
+      </c>
+      <c r="E186" t="n">
+        <v>78</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>+12 Curve 78</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ball Control</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>8</v>
+      </c>
+      <c r="E187" t="n">
+        <v>74</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>+8 Ball Control 74</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Acceleration</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>5</v>
+      </c>
+      <c r="E188" t="n">
+        <v>80</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>+5 Acceleration 80</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Fk Accuracy</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>4</v>
+      </c>
+      <c r="E189" t="n">
+        <v>80</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>+4 Fk Accuracy 80</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>8</v>
+      </c>
+      <c r="E190" t="n">
+        <v>78</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>+8 Agility 78</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sub Stat</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Dribbling</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>8</v>
+      </c>
+      <c r="E191" t="n">
+        <v>74</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>+8 Dribbling 74</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -13563,7 +14342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13641,7 +14420,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -13656,19 +14435,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13678,17 +14457,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pace Max. 80</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -13703,39 +14482,39 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>ST, CDM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Excluded Position ST, CDM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -13750,39 +14529,39 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LB, RB</t>
+          <t>RM, RW</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Excluded Position LB, RB</t>
+          <t>Position RM, RW</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Wing Specialization - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -13797,39 +14576,39 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Position CB</t>
+          <t>Overall Max. 74</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backline Conductor - EA SPORTS FC 27</t>
+          <t>Trust the Keeper - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -13844,19 +14623,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2531-trust-the-keeper/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13866,12 +14645,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Overall Max. 74</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13898,27 +14677,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Position GK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13945,32 +14724,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Position GK</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trust the Keeper - EA SPORTS FC 27</t>
+          <t>Flank Identity - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13985,19 +14764,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2531-trust-the-keeper/</t>
+          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14007,12 +14786,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Pace Max. 85</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -14039,12 +14818,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14054,12 +14833,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pace Max. 85</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -14086,27 +14865,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>ST, CDM, LB</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Excluded Position ST, CDM, LB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -14133,27 +14912,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ST, CDM, LB</t>
+          <t>LM, LW</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Excluded Position ST, CDM, LB</t>
+          <t>Position LM, LW</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -14180,32 +14959,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LM, LW</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Position LM, LW</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flank Identity - EA SPORTS FC 27</t>
+          <t>Pivot Shift - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14220,19 +14999,19 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2525-flank-identity/</t>
+          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14242,12 +15021,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Pace Max. 83</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -14274,12 +15053,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -14289,12 +15068,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pace Max. 83</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -14321,27 +15100,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>ST, CAM, CB</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Excluded Position ST, CAM, CB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -14368,27 +15147,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ST, CAM, CB</t>
+          <t>CDM, CM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Excluded Position ST, CAM, CB</t>
+          <t>Position CDM, CM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -14415,32 +15194,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CDM, CM</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Position CDM, CM</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pivot Shift - EA SPORTS FC 27</t>
+          <t>Frontline Paradox - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -14455,19 +15234,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2524-pivot-shift/</t>
+          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14477,12 +15256,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Pace Max. 85</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -14509,12 +15288,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -14524,12 +15303,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pace Max. 85</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -14556,27 +15335,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>CM, LM, RM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Excluded Position CM, LM, RM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -14603,27 +15382,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CM, LM, RM</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Excluded Position CM, LM, RM</t>
+          <t>Position ST</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -14650,32 +15429,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Position ST</t>
+          <t>Overall Max. 74</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Frontline Paradox - EA SPORTS FC 27</t>
+          <t>Midfield Glow Up - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -14690,19 +15469,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2508-frontline-paradox/</t>
+          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -14712,12 +15491,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Overall Max. 74</t>
+          <t>Pace Max. 85</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -14744,12 +15523,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -14759,12 +15538,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pace Max. 85</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -14791,27 +15570,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>CAM, CB, ST</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Excluded Position CAM, CB, ST</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -14838,27 +15617,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CAM, CB, ST</t>
+          <t>CDM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Excluded Position CAM, CB, ST</t>
+          <t>Position CDM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -14885,32 +15664,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CDM</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Position CDM</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Midfield Glow Up - EA SPORTS FC 27</t>
+          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14925,19 +15704,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2507-midfield-glow-up/</t>
+          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14947,12 +15726,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Pace Max. 81</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14979,27 +15758,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pace Max. 81</t>
+          <t>Position ST</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -15026,32 +15805,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Position ST</t>
+          <t>Overall Max. 75</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions - EA SPORTS FC 27</t>
+          <t>Intro to Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -15066,19 +15845,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2492-intro-to-repeatable-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15088,12 +15867,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Overall Max. 75</t>
+          <t>Pace Max. 80</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -15120,12 +15899,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15135,12 +15914,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pace Max. 80</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -15167,12 +15946,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15182,12 +15961,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Max Pos. 2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -15214,27 +15993,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Max Pos. 2</t>
+          <t>Excluded Position CB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -15261,27 +16040,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Excluded Position CB</t>
+          <t>Position RB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -15308,32 +16087,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Position RB</t>
+          <t>Overall Max. 80</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Intro to Evolutions - EA SPORTS FC 27</t>
+          <t>Intro to Training Camp EVOs - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -15348,34 +16127,34 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2491-intro-to-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Overall Max. 80</t>
+          <t>Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -15402,32 +16181,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs - EA SPORTS FC 27</t>
+          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -15442,19 +16221,19 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2490-intro-to-training-camp-evos/</t>
+          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15464,17 +16243,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Overall Max. 74</t>
+          <t>Max PS 3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -15489,19 +16268,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -15511,44 +16290,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pace Max. 83</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -15558,185 +16337,185 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Pace Max. 80</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LB, RB</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Excluded Position LB, RB</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LM, RM</t>
+          <t>LB, RB</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Position LM, RM</t>
+          <t>Excluded Position LB, RB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Overall Max. 80</t>
+          <t>Position CB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
+          <t>Backline Conductor - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -15746,44 +16525,44 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Max PS 3</t>
+          <t>Overall Max. 83</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions - EA SPORTS FC 27</t>
+          <t>Frontline Flair - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -15793,12 +16572,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Overall Max. 83</t>
+          <t>Pace Max. 84</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -15825,12 +16604,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -15840,12 +16619,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pace Max. 84</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -15872,27 +16651,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Excluded Position CAM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -15919,27 +16698,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>LW, RW, ST</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Excluded Position CAM</t>
+          <t>Position LW, RW, ST</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -15966,32 +16745,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LW, RW, ST</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Position LW, RW, ST</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Frontline Flair - EA SPORTS FC 27</t>
+          <t>Pinged Pass - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -16001,24 +16780,24 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16028,12 +16807,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Max PS 2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -16060,12 +16839,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16075,17 +16854,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Max PS 2</t>
+          <t>Overall Max. 82</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pinged Pass - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -16100,34 +16879,34 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Overall Max. 82</t>
+          <t>Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -16154,32 +16933,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Position ST Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -16189,24 +16968,24 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS_Plus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS_Plus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16216,12 +16995,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Overall Max. 81</t>
+          <t>Max PS+ 0</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -16248,12 +17027,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Max_PS_Plus</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Max_PS_Plus</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16263,12 +17042,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Max PS+ 0</t>
+          <t>Max PS 3</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -16295,27 +17074,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>LW, RW, ST</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Max PS 3</t>
+          <t>Position LW, RW, ST</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -16342,32 +17121,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LW, RW, ST</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Position LW, RW, ST</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
+          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -16377,24 +17156,24 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16404,12 +17183,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Max PS 2</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -16436,12 +17215,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -16451,17 +17230,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Max PS 2</t>
+          <t>Overall Max. 81</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -16471,24 +17250,24 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16498,12 +17277,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Overall Max. 81</t>
+          <t>Pace Max. 85</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -16530,12 +17309,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS_Plus</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS_Plus</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16545,12 +17324,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pace Max. 85</t>
+          <t>Max PS+ 0</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -16577,12 +17356,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Max_PS_Plus</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Max_PS_Plus</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -16592,12 +17371,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Max PS+ 0</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -16624,12 +17403,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -16639,12 +17418,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Max Pos. 3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -16671,27 +17450,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>LB, ST</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Max Pos. 3</t>
+          <t>Excluded Position LB, ST</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -16718,27 +17497,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LB, ST</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Excluded Position LB, ST</t>
+          <t>Position LW</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -16765,32 +17544,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Position LW</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -16805,19 +17584,19 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -16827,12 +17606,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Max PS 2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -16859,12 +17638,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -16874,17 +17653,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Max PS 2</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
+          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -16894,24 +17673,24 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -16921,12 +17700,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Max PS 2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -16953,12 +17732,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -16968,17 +17747,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Max PS 2</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -16993,19 +17772,19 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17015,12 +17794,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Pace Max. 84</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -17047,12 +17826,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -17062,12 +17841,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pace Max. 84</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -17094,12 +17873,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -17109,12 +17888,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Max Pos. 3</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -17141,27 +17920,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>CAM, CM</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Max Pos. 3</t>
+          <t>Excluded Position CAM, CM</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -17188,27 +17967,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CAM, CM</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Excluded Position CAM, CM</t>
+          <t>Position ST</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -17235,32 +18014,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Position ST</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -17270,39 +18049,39 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>CAM Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Excluded Position CAM Details Submit by in 27 days Expiry in 27 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -17329,27 +18108,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CAM Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>CM, CDM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Excluded Position CAM Details Submit by in 28 days Expiry in 28 days Coins Cost Free Points Cost Free</t>
+          <t>Position CM, CDM</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -17376,47 +18155,235 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>OVR_Max</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OVR_Max</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Overall Max. 74</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PAC_Max</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PAC_Max</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Pace Max. 83</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Max_PS</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Max_PS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Max PS 7</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Excluded_Position</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Excluded Position</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LB, RB</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Excluded Position LB, RB</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Include</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>CM, CDM</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Position CM, CDM</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Premium Season Pass</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LM, RM</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Position LM, RM</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
@@ -17431,7 +18398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17474,17 +18441,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
+          <t>https://www.fut.gg/evolutions/2534-wing-specialization/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Backline Conductor NEW 2</t>
+          <t>Wing Specialization NEW</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Backline Conductor NEW 2 Fortify your central defender's core defensive instincts and physical stature while sharpening their distribution to build play confidently from the deep. Egan-Riley 75 CB PAC 80 SHO 32 PAS 61 DRI 66 DEF 74 PHY 79 R 2 ★ 3 CB 73.5 Egan-Riley 80 CB PAC 80 SHO 32 PAS 64 DRI 66 DEF 79 PHY 80 R 2 ★ 3 CB 76.8 REQUIREMENTS Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 in 10 days in 17 days 71% 29%</t>
+          <t>Wing Specialization NEW Boost your winger's attributes and specialize your Level 3 rewards to gain clinical finishing, rapid speed, or precise Tiki Taka play. Müller 77 LB PAC 78 SHO 69 PAS 77 DRI 79 DEF 76 PHY 69 RB RM R 3 ★ 3 RB 77.7 Müller 83 LB PAC 86 SHO 69 PAS 77 DRI 80 DEF 76 PHY 70 RB RM R 3 ★ 3 RB 82.1 REQUIREMENTS Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 UPGRADES A +7 OVR 83 +1 SM 3 +8 Sprint Speed 82 +5 Balance 76 +5 Composure 78 +8 Acceleration 82 +5 Agility 78 +5 Reactions 76 +10 Stamina 75 +5 Positioning 81 +5 Finishing 80 +5 Shot Power 80 3 in 10 days in 17 days 37% 63%</t>
         </is>
       </c>
     </row>
@@ -17511,7 +18478,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trust the Keeper Trust the keeper and give them time to work their magic. Sharpen their skills between the sticks and turn your last line of defence into a wall attackers cannot break. Berisha 71 GK DIV 67 HAN 71 KIC 67 REF 70 SPD 24 POS 71 L 1 ★ 2 GK 70.5 Berisha 79 GK DIV 80 HAN 77 KIC 74 REF 80 SPD 34 POS 77 L 1 ★ 2 GK 80.4 REQUIREMENTS Overall Max. 74 Position GK Max PS 7 UPGRADES +10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 TRAINING TIME 1 day in 9 days in 16 days 73% 27%</t>
+          <t>Trust the Keeper Trust the keeper and give them time to work their magic. Sharpen their skills between the sticks and turn your last line of defence into a wall attackers cannot break. Berisha 71 GK DIV 67 HAN 71 KIC 67 REF 70 SPD 24 POS 71 L 1 ★ 2 GK 70.5 Berisha 79 GK DIV 80 HAN 77 KIC 74 REF 80 SPD 34 POS 77 L 1 ★ 2 GK 80.4 REQUIREMENTS Overall Max. 74 Position GK Max PS 7 UPGRADES +10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 TRAINING TIME 1 day in 8 days in 15 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -17538,7 +18505,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 7 days in 14 days 26% 74%</t>
+          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 6 days in 13 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -17565,7 +18532,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 5 days in 12 days 26% 74%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 4 days in 11 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -17592,7 +18559,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 4 days in 11 days 74% 26%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 3 days in 10 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -17619,7 +18586,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 21 days in 21 days 83% 17%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 20 days in 20 days 83% 17%</t>
         </is>
       </c>
     </row>
@@ -17700,7 +18667,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 85% 15%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 78.2 Thierry Correia 74 RB PAC 89 SHO 50 PAS 68 DRI 72 DEF 69 PHY 69 LB RM LM R 3 ★ 4 RB 79.6 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 84% 16%</t>
         </is>
       </c>
     </row>
@@ -17717,44 +18684,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2</t>
+          <t>Intro to Pathway Evolutions</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 20 days in 20 days 92% 8%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 87% 13%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Current Evolutions</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2488-intro-to-pathway-evolutions/</t>
+          <t>https://www.fut.gg/evolutions/2533-backline-conductor/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions</t>
+          <t>Backline Conductor 2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 84.4 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.2 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES B 4 in 1 year in 1 year 88% 13%</t>
+          <t>Backline Conductor 2 Fortify your central defender's core defensive instincts and physical stature while sharpening their distribution to build play confidently from the deep. Egan-Riley 75 CB PAC 80 SHO 32 PAS 61 DRI 66 DEF 74 PHY 79 R 2 ★ 3 CB 73.5 Egan-Riley 80 CB PAC 80 SHO 32 PAS 64 DRI 66 DEF 79 PHY 80 R 2 ★ 3 CB 76.8 REQUIREMENTS Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 in 9 days in 16 days 69% 31%</t>
         </is>
       </c>
     </row>
@@ -17776,12 +18743,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Frontline Flair NEW 2</t>
+          <t>Frontline Flair 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Frontline Flair NEW 2 Unlocked via the Token Store for 100 tokens Ueda 80 ST PAC 80 SHO 80 PAS 66 DRI 79 DEF 32 PHY 77 R 3 ★ 4 ST 80.2 Ueda 81 ST PAC 82 SHO 81 PAS 66 DRI 81 DEF 32 PHY 77 R 3 ★ 4 ST 81.7 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 21 days in 28 days 73% 27%</t>
+          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Ueda 80 ST PAC 80 SHO 80 PAS 66 DRI 79 DEF 32 PHY 77 R 3 ★ 4 ST 80.2 Ueda 81 ST PAC 82 SHO 81 PAS 66 DRI 81 DEF 32 PHY 77 R 3 ★ 4 ST 81.7 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 20 days in 27 days 77% 23%</t>
         </is>
       </c>
     </row>
@@ -17808,7 +18775,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gallery Excellence Unlocked by completing the Gallery Milestone objective Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 64% 36%</t>
+          <t>Gallery Excellence Unlocked by completing the Gallery Milestone objective Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 69% 31%</t>
         </is>
       </c>
     </row>
@@ -17835,7 +18802,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 43% 57%</t>
+          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 26 days in 26 days 50% 50%</t>
         </is>
       </c>
     </row>
@@ -17862,7 +18829,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 19% 81%</t>
+          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 26 days in 26 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -17889,7 +18856,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 16% 84%</t>
+          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 26 days in 26 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +18883,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 27 days in 27 days 21% 79%</t>
+          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 26 days in 26 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -17943,7 +18910,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 28 days in 28 days 95% 5%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 27 days in 27 days 95% 5%</t>
         </is>
       </c>
     </row>
@@ -17970,7 +18937,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 32% 68%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
         </is>
       </c>
     </row>
@@ -17997,7 +18964,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 28 days in 28 days 86% 14%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 27 days in 27 days 86% 14%</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18991,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 28 days in 28 days 79% 21%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 27 days in 27 days 79% 21%</t>
         </is>
       </c>
     </row>
@@ -18051,7 +19018,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 28 days in 28 days 93% 7%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 27 days in 27 days 93% 7%</t>
         </is>
       </c>
     </row>
@@ -18078,7 +19045,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 28 days in 28 days 88% 12%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 27 days in 27 days 87% 13%</t>
         </is>
       </c>
     </row>
@@ -18105,7 +19072,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 28 days in 28 days 38% 62%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 27 days in 27 days 38% 62%</t>
         </is>
       </c>
     </row>
@@ -18132,7 +19099,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 28 days in 28 days 89% 11%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 27 days in 27 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -18159,7 +19126,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 28 days in 28 days 26% 74%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 27 days in 27 days 25% 75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Repeat Delivery 2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 19 days in 19 days 92% 8%</t>
         </is>
       </c>
     </row>
@@ -18209,7 +19203,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -18219,7 +19213,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -18230,7 +19224,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01T21:48:29</t>
+          <t>2026-10-02T21:19:40</t>
         </is>
       </c>
     </row>
@@ -18253,7 +19247,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -1148,22 +1148,22 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Regista Realm NEW</t>
+          <t>Regista Realm</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Regista Realm NEW Control the tempo from central areas by shaping a midfielder to suit your team's tactical framework. Bellingham 77 CM PAC 70 SHO 69 PAS 73 DRI 76 DEF 80 PHY 83 CDM R 3 ★ 3 CDM 78.5 Bellingham 81 CM PAC 75 SHO 69 PAS 77 DRI 77 DEF 80 PHY 83 CDM R 3 ★ 3 CDM 81.4 REQUIREMENTS Overall Max. 80 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES A +5 OVR 81 +2 WF 3 +5 Crossing 80 +5 Short Pass 82 +5 Curve 81 +5 Stamina 75 +5 Vision 81 +5 Fk Accuracy 80 +5 Long Pass 82 +5 Composure 76 +5 Acceleration 75 +5 Sprint Speed 75 +5 Interceptions 79 +5 Defensive Awareness 78 +5 Standing Tackle 78 3 in 10 days in 17 days 42% 58%</t>
+          <t>Regista Realm Control the tempo from central areas by shaping a midfielder to suit your team's tactical framework. Bellingham 77 CM PAC 70 SHO 69 PAS 73 DRI 76 DEF 80 PHY 83 CDM R 3 ★ 3 CDM 78.5 Bellingham 81 CM PAC 75 SHO 69 PAS 77 DRI 77 DEF 80 PHY 83 CDM R 3 ★ 3 CDM 81.4 REQUIREMENTS Overall Max. 80 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES A +5 OVR 81 +2 WF 3 +5 Crossing 80 +5 Short Pass 82 +5 Curve 81 +5 Stamina 75 +5 Vision 81 +5 Fk Accuracy 80 +5 Long Pass 82 +5 Composure 76 +5 Acceleration 75 +5 Sprint Speed 75 +5 Interceptions 79 +5 Defensive Awareness 78 +5 Standing Tackle 78 3 in 9 days in 16 days 41% 59%</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 Details Type Pathway, pick one option per level Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Wing Specialization Boost your winger's attributes and specialize your Level 3 rewards to gain clinical finishing, rapid speed, or precise Tiki Taka play. Müller 77 LB PAC 78 SHO 69 PAS 77 DRI 79 DEF 76 PHY 69 RB RM R 3 ★ 3 RB 77.7 Müller 83 LB PAC 86 SHO 69 PAS 77 DRI 80 DEF 76 PHY 70 RB RM R 3 ★ 3 RB 82.1 REQUIREMENTS Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 UPGRADES A +7 OVR 83 +1 SM 3 +8 Sprint Speed 82 +5 Balance 76 +5 Composure 78 +8 Acceleration 82 +5 Agility 78 +5 Reactions 76 +10 Stamina 75 +5 Positioning 81 +5 Finishing 80 +5 Shot Power 80 3 in 9 days in 16 days 33% 67%</t>
+          <t>Wing Specialization Boost your winger's attributes and specialize your Level 3 rewards to gain clinical finishing, rapid speed, or precise Tiki Taka play. Müller 77 LB PAC 78 SHO 69 PAS 77 DRI 79 DEF 76 PHY 69 RB RM R 3 ★ 3 RB 77.7 Müller 83 LB PAC 86 SHO 69 PAS 77 DRI 80 DEF 76 PHY 70 RB RM R 3 ★ 3 RB 82.1 REQUIREMENTS Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 UPGRADES A +7 OVR 83 +1 SM 3 +8 Sprint Speed 82 +5 Balance 76 +5 Composure 78 +8 Acceleration 82 +5 Agility 78 +5 Reactions 76 +10 Stamina 75 +5 Positioning 81 +5 Finishing 80 +5 Shot Power 80 3 in 8 days in 15 days 32% 68%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position GK Max PS 7 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position GK Max PS 7 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position GK Max PS 7 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position GK Max PS 7 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Trust the Keeper Trust the keeper and give them time to work their magic. Sharpen their skills between the sticks and turn your last line of defence into a wall attackers cannot break. Berisha 71 GK DIV 67 HAN 71 KIC 67 REF 70 SPD 24 POS 71 L 1 ★ 2 GK 70.5 Berisha 79 GK DIV 80 HAN 77 KIC 74 REF 80 SPD 34 POS 77 L 1 ★ 2 GK 80.4 REQUIREMENTS Overall Max. 74 Position GK Max PS 7 UPGRADES +10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 TRAINING TIME 1 day in 7 days in 14 days 74% 26%</t>
+          <t>Trust the Keeper Trust the keeper and give them time to work their magic. Sharpen their skills between the sticks and turn your last line of defence into a wall attackers cannot break. Berisha 71 GK DIV 67 HAN 71 KIC 67 REF 70 SPD 24 POS 71 L 1 ★ 2 GK 70.5 Berisha 79 GK DIV 80 HAN 77 KIC 74 REF 80 SPD 34 POS 77 L 1 ★ 2 GK 80.4 REQUIREMENTS Overall Max. 74 Position GK Max PS 7 UPGRADES +10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 TRAINING TIME 1 day in 6 days in 13 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 5 days in 12 days 25% 75%</t>
+          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 4 days in 11 days 25% 75%</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 3 days in 10 days 26% 74%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 2 days in 9 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 21 hours Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 Details Type Pathway, pick one option per level Submit by in 21 hours Expiry in 8 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 2 days in 9 days 74% 26%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 21 hours in 8 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 19 days Expiry in 19 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 18 days Expiry in 18 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 19 days Expiry in 19 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 18 days Expiry in 18 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 19 days in 19 days 83% 17%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 18 days in 18 days 83% 17%</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       <c r="CV12" t="inlineStr"/>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 86% of GG users upvoted this Evolution. Vote Now! 86% 14% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Engelhardt 80 CDM PAC 84 SHO 60 PAS 72 DRI 71 DEF 80 PHY 84 CM R 3 ★ 3 CDM 82.2 Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 RB 82.9 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Rosario 80 CDM PAC 73 SHO 66 PAS 72 DRI 77 DEF 80 PHY 84 CB CM R 3 ★ 3 CDM 81.1 Delcroix 80 CB PAC 77 SHO 46 PAS 72 DRI 71 DEF 80 PHY 82 LB CDM L 2 ★ 3 CDM 80.2 Evolution Upgrades B 4 Level 1 Martín 80 ST PAC 80 SHO 82 PAS 71 DRI 80 DEF 47 PHY 82 R 3 ★ 3 Martín 80 ST PAC 80 SHO 82 PAS 71 DRI 80 DEF 47 PHY 82 R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 86% of GG users upvoted this Evolution. Vote Now! 86% 14% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Sterling 80 RB PAC 80 SHO 58 PAS 74 DRI 77 DEF 79 PHY 83 CB LB RM LM R 3 ★ 3 RB 82.9 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Rosario 80 CDM PAC 73 SHO 66 PAS 72 DRI 77 DEF 80 PHY 84 CB CM R 3 ★ 3 CDM 81.1 Engelhardt 80 CDM PAC 84 SHO 60 PAS 72 DRI 71 DEF 80 PHY 84 CM R 3 ★ 3 CDM 82.2 Černý 77 RM PAC 85 SHO 72 PAS 71 DRI 77 DEF 39 PHY 65 CM CAM RW L 4 ★ 3 RM 78.0 Tiago Santos 80 RB PAC 87 SHO 61 PAS 77 DRI 81 DEF 78 PHY 70 RM R 3 ★ 3 RB 83.5 Evolution Upgrades B 4 Level 1 Martín 80 ST PAC 80 SHO 82 PAS 71 DRI 80 DEF 47 PHY 82 R 3 ★ 3 Martín 80 ST PAC 80 SHO 82 PAS 71 DRI 80 DEF 47 PHY 82 R 3 ★ 3 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Backline Conductor 2 Fortify your central defender's core defensive instincts and physical stature while sharpening their distribution to build play confidently from the deep. Egan-Riley 75 CB PAC 80 SHO 32 PAS 61 DRI 66 DEF 74 PHY 79 R 2 ★ 3 CB 73.5 Egan-Riley 80 CB PAC 80 SHO 32 PAS 64 DRI 66 DEF 79 PHY 80 R 2 ★ 3 CB 76.8 REQUIREMENTS Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 in 8 days in 15 days 69% 31%</t>
+          <t>Backline Conductor 2 Fortify your central defender's core defensive instincts and physical stature while sharpening their distribution to build play confidently from the deep. Egan-Riley 75 CB PAC 80 SHO 32 PAS 61 DRI 66 DEF 74 PHY 79 R 2 ★ 3 CB 73.5 Egan-Riley 80 CB PAC 80 SHO 32 PAS 64 DRI 66 DEF 79 PHY 80 R 2 ★ 3 CB 76.8 REQUIREMENTS Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 in 7 days in 14 days 69% 31%</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 19 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 18 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 19 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 18 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Ueda 80 ST PAC 80 SHO 80 PAS 66 DRI 79 DEF 32 PHY 77 R 3 ★ 4 ST 80.2 Ueda 81 ST PAC 82 SHO 81 PAS 66 DRI 81 DEF 32 PHY 77 R 3 ★ 4 ST 81.7 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 19 days in 26 days 77% 23%</t>
+          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Ueda 80 ST PAC 80 SHO 80 PAS 66 DRI 79 DEF 32 PHY 77 R 3 ★ 4 ST 80.2 Ueda 81 ST PAC 82 SHO 81 PAS 66 DRI 81 DEF 32 PHY 77 R 3 ★ 4 ST 81.7 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 18 days in 25 days 76% 24%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Gallery Excellence Unlocked by completing the Gallery Milestone objective Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 67% 33%</t>
+          <t>Gallery Excellence Unlocked by completing the Gallery Milestone objective Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 65% 35%</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ16" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 50% 50%</t>
+          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 50% 50%</t>
         </is>
       </c>
     </row>
@@ -3985,12 +3985,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ17" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 19% 81%</t>
+          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ18" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 16% 84%</t>
+          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>No requirements Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
+          <t>No requirements Details Submit by in 24 days Expiry in 24 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ19" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 21% 79%</t>
+          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -4422,12 +4422,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ20" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 26 days in 26 days 95% 5%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 25 days in 25 days 96% 4%</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 35% 65%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
         </is>
       </c>
     </row>
@@ -4744,12 +4744,12 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ22" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="DA22" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 26 days in 26 days 87% 13%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 25 days in 25 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -4895,12 +4895,12 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ23" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="DA23" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 26 days in 26 days 81% 19%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 25 days in 25 days 81% 19%</t>
         </is>
       </c>
     </row>
@@ -5154,12 +5154,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ24" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="DA24" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 26 days in 26 days 91% 9%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 25 days in 25 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -5305,12 +5305,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ25" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="DA25" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 26 days in 26 days 87% 13%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 25 days in 25 days 88% 13%</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ26" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="DA26" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 26 days in 26 days 37% 63%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 25 days in 25 days 36% 64%</t>
         </is>
       </c>
     </row>
@@ -5707,12 +5707,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ27" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="DA27" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 26 days in 26 days 90% 10%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 25 days in 25 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CAM Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>CAM Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -5874,12 +5874,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ28" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="DA28" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 26 days in 26 days 25% 75%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 25 days in 25 days 24% 76%</t>
         </is>
       </c>
     </row>
@@ -6105,12 +6105,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 18 days Expiry in 18 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 17 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY29" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 18 days Expiry in 18 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 17 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ29" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="DA29" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 18 days in 18 days 92% 8%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 17 days in 17 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -19190,12 +19190,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CAM Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>CAM Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Excluded Position CAM Details Submit by in 26 days Expiry in 26 days Coins Cost Free Points Cost Free</t>
+          <t>Excluded Position CAM Details Submit by in 25 days Expiry in 25 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -19560,12 +19560,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Regista Realm NEW</t>
+          <t>Regista Realm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Regista Realm NEW Control the tempo from central areas by shaping a midfielder to suit your team's tactical framework. Bellingham 77 CM PAC 70 SHO 69 PAS 73 DRI 76 DEF 80 PHY 83 CDM R 3 ★ 3 CDM 78.5 Bellingham 81 CM PAC 75 SHO 69 PAS 77 DRI 77 DEF 80 PHY 83 CDM R 3 ★ 3 CDM 81.4 REQUIREMENTS Overall Max. 80 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES A +5 OVR 81 +2 WF 3 +5 Crossing 80 +5 Short Pass 82 +5 Curve 81 +5 Stamina 75 +5 Vision 81 +5 Fk Accuracy 80 +5 Long Pass 82 +5 Composure 76 +5 Acceleration 75 +5 Sprint Speed 75 +5 Interceptions 79 +5 Defensive Awareness 78 +5 Standing Tackle 78 3 in 10 days in 17 days 42% 58%</t>
+          <t>Regista Realm Control the tempo from central areas by shaping a midfielder to suit your team's tactical framework. Bellingham 77 CM PAC 70 SHO 69 PAS 73 DRI 76 DEF 80 PHY 83 CDM R 3 ★ 3 CDM 78.5 Bellingham 81 CM PAC 75 SHO 69 PAS 77 DRI 77 DEF 80 PHY 83 CDM R 3 ★ 3 CDM 81.4 REQUIREMENTS Overall Max. 80 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES A +5 OVR 81 +2 WF 3 +5 Crossing 80 +5 Short Pass 82 +5 Curve 81 +5 Stamina 75 +5 Vision 81 +5 Fk Accuracy 80 +5 Long Pass 82 +5 Composure 76 +5 Acceleration 75 +5 Sprint Speed 75 +5 Interceptions 79 +5 Defensive Awareness 78 +5 Standing Tackle 78 3 in 9 days in 16 days 41% 59%</t>
         </is>
       </c>
     </row>
@@ -19592,7 +19592,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wing Specialization Boost your winger's attributes and specialize your Level 3 rewards to gain clinical finishing, rapid speed, or precise Tiki Taka play. Müller 77 LB PAC 78 SHO 69 PAS 77 DRI 79 DEF 76 PHY 69 RB RM R 3 ★ 3 RB 77.7 Müller 83 LB PAC 86 SHO 69 PAS 77 DRI 80 DEF 76 PHY 70 RB RM R 3 ★ 3 RB 82.1 REQUIREMENTS Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 UPGRADES A +7 OVR 83 +1 SM 3 +8 Sprint Speed 82 +5 Balance 76 +5 Composure 78 +8 Acceleration 82 +5 Agility 78 +5 Reactions 76 +10 Stamina 75 +5 Positioning 81 +5 Finishing 80 +5 Shot Power 80 3 in 9 days in 16 days 33% 67%</t>
+          <t>Wing Specialization Boost your winger's attributes and specialize your Level 3 rewards to gain clinical finishing, rapid speed, or precise Tiki Taka play. Müller 77 LB PAC 78 SHO 69 PAS 77 DRI 79 DEF 76 PHY 69 RB RM R 3 ★ 3 RB 77.7 Müller 83 LB PAC 86 SHO 69 PAS 77 DRI 80 DEF 76 PHY 70 RB RM R 3 ★ 3 RB 82.1 REQUIREMENTS Overall Max. 79 Position RM, RW Excluded Position ST, CDM Max PS 7 UPGRADES A +7 OVR 83 +1 SM 3 +8 Sprint Speed 82 +5 Balance 76 +5 Composure 78 +8 Acceleration 82 +5 Agility 78 +5 Reactions 76 +10 Stamina 75 +5 Positioning 81 +5 Finishing 80 +5 Shot Power 80 3 in 8 days in 15 days 32% 68%</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trust the Keeper Trust the keeper and give them time to work their magic. Sharpen their skills between the sticks and turn your last line of defence into a wall attackers cannot break. Berisha 71 GK DIV 67 HAN 71 KIC 67 REF 70 SPD 24 POS 71 L 1 ★ 2 GK 70.5 Berisha 79 GK DIV 80 HAN 77 KIC 74 REF 80 SPD 34 POS 77 L 1 ★ 2 GK 80.4 REQUIREMENTS Overall Max. 74 Position GK Max PS 7 UPGRADES +10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 TRAINING TIME 1 day in 7 days in 14 days 74% 26%</t>
+          <t>Trust the Keeper Trust the keeper and give them time to work their magic. Sharpen their skills between the sticks and turn your last line of defence into a wall attackers cannot break. Berisha 71 GK DIV 67 HAN 71 KIC 67 REF 70 SPD 24 POS 71 L 1 ★ 2 GK 70.5 Berisha 79 GK DIV 80 HAN 77 KIC 74 REF 80 SPD 34 POS 77 L 1 ★ 2 GK 80.4 REQUIREMENTS Overall Max. 74 Position GK Max PS 7 UPGRADES +10 OVR 79 +9 POS 77 +10 Acceleration 50 +9 Reactions 76 +8 Kicking 74 +10 Reflexes 80 +10 Sprint Speed 50 +15 Diving 80 +8 Handling 77 3 TRAINING TIME 1 day in 6 days in 13 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 5 days in 12 days 25% 75%</t>
+          <t>Flank Identity Sharpen your wide player's impact on the match, leading to a pivotal choice that permanently steers their tactical development on the wing. Alvarado 78 RM PAC 81 SHO 70 PAS 78 DRI 75 DEF 65 PHY 68 CM LM CAM RW LW L 4 ★ 4 CAM 76.5 Alvarado 80 RM PAC 83 SHO 71 PAS 78 DRI 79 DEF 65 PHY 72 CM LM CAM RW LW L 4 ★ 4 RM 80.2 REQUIREMENTS Overall Max. 79 Position LM, LW Excluded Position ST, CDM, LB Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 80 +5 Sprint Speed 83 +5 Agility 82 +5 Reactions 78 +5 Dribbling 80 +5 Stamina 77 +5 Acceleration 83 +5 Positioning 79 +5 Balance 80 +5 Ball Control 79 +5 Composure 76 +4 Finishing 79 +4 Shot Power 78 +5 Vision 77 +5 Crossing 79 +5 Curve 78 3 in 4 days in 11 days 25% 75%</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 3 days in 10 days 26% 74%</t>
+          <t>Pivot Shift Sharpen your midfielder's ability to control the tempo, concluding with a decision that steers them toward forward progression or defensive coverage. Burger 78 CM PAC 71 SHO 68 PAS 77 DRI 75 DEF 76 PHY 83 CDM L 3 ★ 4 CM 77.0 Burger 80 CM PAC 73 SHO 68 PAS 78 DRI 75 DEF 77 PHY 83 CDM L 3 ★ 4 CM 79.7 REQUIREMENTS Overall Max. 79 Position CDM, CM Excluded Position ST, CAM, CB Max PS 7 Pace Max. 83 UPGRADES B +5 OVR 80 +3 Sprint Speed 75 +5 Crossing 76 +5 Long Pass 80 +5 Agility 75 +3 Acceleration 75 +5 Vision 80 +5 Short Pass 78 +5 Curve 75 +5 Balance 75 +5 Interceptions 78 +5 Standing Tackle 78 +5 Sliding Tackle 77 +5 Strength 78 +5 Aggression 76 3 in 2 days in 9 days 26% 74%</t>
         </is>
       </c>
     </row>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 2 days in 9 days 74% 26%</t>
+          <t>Frontline Paradox Build out your striker’s core threat in the box, ending in a key decision that sets their role at the apex of your system. Leroux 78 ST PAC 74 SHO 75 PAS 78 DRI 78 DEF 44 PHY 76 R 4 ★ 4 ST 74.0 Leroux 81 ST PAC 79 SHO 80 PAS 78 DRI 79 DEF 44 PHY 76 R 4 ★ 4 ST 78.8 REQUIREMENTS Overall Max. 79 Position ST Excluded Position CM, LM, RM Max PS 7 Pace Max. 85 UPGRADES A +5 OVR 81 +1 WF 3 +5 Sprint Speed 82 +5 Finishing 81 +5 Long Shots 78 +5 Penalties 82 +5 Acceleration 82 +5 Positioning 78 +5 Shot Power 80 +5 Volleys 82 +5 Agility 78 +5 Balance 78 +5 Ball Control 78 +5 Dribbling 77 ST Advanced Forward + 3 in 21 hours in 8 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -19727,7 +19727,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 19 days in 19 days 83% 17%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.1 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 18 days in 18 days 83% 17%</t>
         </is>
       </c>
     </row>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Backline Conductor 2 Fortify your central defender's core defensive instincts and physical stature while sharpening their distribution to build play confidently from the deep. Egan-Riley 75 CB PAC 80 SHO 32 PAS 61 DRI 66 DEF 74 PHY 79 R 2 ★ 3 CB 73.5 Egan-Riley 80 CB PAC 80 SHO 32 PAS 64 DRI 66 DEF 79 PHY 80 R 2 ★ 3 CB 76.8 REQUIREMENTS Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 in 8 days in 15 days 69% 31%</t>
+          <t>Backline Conductor 2 Fortify your central defender's core defensive instincts and physical stature while sharpening their distribution to build play confidently from the deep. Egan-Riley 75 CB PAC 80 SHO 32 PAS 61 DRI 66 DEF 74 PHY 79 R 2 ★ 3 CB 73.5 Egan-Riley 80 CB PAC 80 SHO 32 PAS 64 DRI 66 DEF 79 PHY 80 R 2 ★ 3 CB 76.8 REQUIREMENTS Overall Max. 79 Position CB Excluded Position LB, RB Max PS 7 Pace Max. 80 UPGRADES +5 OVR 80 +5 Short Pass 75 +5 Heading Acc. 81 +5 Sliding Tackle 81 +5 Strength 78 +5 Long Pass 75 +5 Defensive Awareness 80 +5 Jumping 75 +5 Aggression 79 +5 Vision 76 +5 Interceptions 79 +5 Standing Tackle 78 +5 Stamina 75 3 in 7 days in 14 days 69% 31%</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Ueda 80 ST PAC 80 SHO 80 PAS 66 DRI 79 DEF 32 PHY 77 R 3 ★ 4 ST 80.2 Ueda 81 ST PAC 82 SHO 81 PAS 66 DRI 81 DEF 32 PHY 77 R 3 ★ 4 ST 81.7 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 19 days in 26 days 77% 23%</t>
+          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Ueda 80 ST PAC 80 SHO 80 PAS 66 DRI 79 DEF 32 PHY 77 R 3 ★ 4 ST 80.2 Ueda 81 ST PAC 82 SHO 81 PAS 66 DRI 81 DEF 32 PHY 77 R 3 ★ 4 ST 81.7 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 18 days in 25 days 76% 24%</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gallery Excellence Unlocked by completing the Gallery Milestone objective Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 67% 33%</t>
+          <t>Gallery Excellence Unlocked by completing the Gallery Milestone objective Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 1 year in 1 year 65% 35%</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 50% 50%</t>
+          <t>Season Ladder Excellence [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 50% 50%</t>
         </is>
       </c>
     </row>
@@ -19970,7 +19970,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 19% 81%</t>
+          <t>Ones to Watch Retro 20 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 19% 81%</t>
         </is>
       </c>
     </row>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 16% 84%</t>
+          <t>Ones to Watch Retro 19 [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 16% 84%</t>
         </is>
       </c>
     </row>
@@ -20024,7 +20024,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 25 days in 25 days 21% 79%</t>
+          <t>Ones to Watch Retro 18 [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 Dumornay 88 ST PAC 92 SHO 85 PAS 79 DRI 90 DEF 60 PHY 73 CDM CM CAM R 4 ★ 5 ST 92.7 REQUIREMENTS No requirements UPGRADES No upgrades in 24 days in 24 days 21% 79%</t>
         </is>
       </c>
     </row>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 26 days in 26 days 95% 5%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 78.7 Pineda 78 CAM PAC 81 SHO 73 PAS 74 DRI 82 DEF 73 PHY 71 CM R 4 ★ 4 CM 79.8 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 25 days in 25 days 96% 4%</t>
         </is>
       </c>
     </row>
@@ -20078,7 +20078,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 35% 65%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 83.7 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.1 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 1 year in 1 year 34% 66%</t>
         </is>
       </c>
     </row>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 26 days in 26 days 87% 13%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 81.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.8 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 25 days in 25 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -20132,7 +20132,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 26 days in 26 days 81% 19%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 25 days in 25 days 81% 19%</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 26 days in 26 days 91% 9%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LM 70.1 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 80.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 25 days in 25 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 26 days in 26 days 87% 13%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.1 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.4 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 25 days in 25 days 88% 13%</t>
         </is>
       </c>
     </row>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 26 days in 26 days 37% 63%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.4 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 79.0 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 25 days in 25 days 36% 64%</t>
         </is>
       </c>
     </row>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 26 days in 26 days 90% 10%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.9 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.6 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 25 days in 25 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -20267,7 +20267,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 26 days in 26 days 25% 75%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Berg 79 CDM PAC 74 SHO 69 PAS 78 DRI 73 DEF 74 PHY 83 CM R 3 ★ 3 CM 77.8 Berg 80 CDM PAC 74 SHO 69 PAS 79 DRI 73 DEF 75 PHY 83 CM R 3 ★ 3 CM 78.4 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 25 days in 25 days 24% 76%</t>
         </is>
       </c>
     </row>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 18 days in 18 days 92% 8%</t>
+          <t>Repeat Delivery 2 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Meza 73 CM PAC 69 SHO 71 PAS 73 DRI 76 DEF 68 PHY 73 CDM RM RW R 5 ★ 4 CM 71.8 Meza 78 CM PAC 74 SHO 71 PAS 78 DRI 77 DEF 68 PHY 76 CDM RM RW R 5 ★ 4 CM 77.1 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 17 days in 17 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03T19:50:13</t>
+          <t>2026-10-04T20:10:07</t>
         </is>
       </c>
     </row>

--- a/latest/evolutions_raw_latest.xlsx
+++ b/latest/evolutions_raw_latest.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA33"/>
+  <dimension ref="A1:DA32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position GK Max PS 7 Max PS+ 0 Details Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position GK Max PS 7 Max PS+ 0 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position GK Max PS 7 Max PS+ 0 Details Submit by in 10 days Expiry in 17 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position GK Max PS 7 Max PS+ 0 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>Poor Sophia NEW</t>
+          <t>Poor Sophia</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>Poor Sophia NEW Poor Sophia no more! A bit more pace (don’t get excited, still a keeper) and extra skill moves. Enough to nutmeg the striker, then calmly jog back to goal. Barkas 75 GK DIV 75 HAN 73 KIC 71 REF 78 SPD 42 POS 73 L 1 ★ 2 GK 76.9 Barkas 80 GK DIV 80 HAN 79 KIC 77 REF 84 SPD 50 POS 79 L 3 ★ 2 GK 83.1 REQUIREMENTS Overall Max. 81 Position GK Max PS 7 Max PS+ 0 UPGRADES +5 OVR 83 +6 POS 80 +2 SM 3 +30 Acceleration 50 +6 Reactions 82 +6 Kicking 81 +6 Reflexes 84 +30 Sprint Speed 50 +6 Diving 80 +6 Handling 82 3 Show less in 10 days in 17 days 82% 18%</t>
+          <t>Poor Sophia Poor Sophia no more! A bit more pace (don’t get excited, still a keeper) and extra skill moves. Enough to nutmeg the striker, then calmly jog back to goal. Barkas 75 GK DIV 75 HAN 73 KIC 71 REF 78 SPD 42 POS 73 L 1 ★ 2 GK 76.9 Barkas 80 GK DIV 80 HAN 79 KIC 77 REF 84 SPD 50 POS 79 L 3 ★ 2 GK 83.1 REQUIREMENTS Overall Max. 81 Position GK Max PS 7 Max PS+ 0 UPGRADES +5 OVR 83 +6 POS 80 +2 SM 3 +30 Acceleration 50 +6 Reactions 82 +6 Kicking 81 +6 Reflexes 84 +30 Sprint Speed 50 +6 Diving 80 +6 Handling 82 3 Show less in 9 days in 16 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position CAM, CM Skill Moves Max. 4 Max PS 7 Pace Max. 75 Defending Max. 74 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position CAM, CM Skill Moves Max. 4 Max PS 7 Pace Max. 75 Defending Max. 74 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position CAM, CM Skill Moves Max. 4 Max PS 7 Pace Max. 75 Defending Max. 74 Details Submit by in 9 days Expiry in 16 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position CAM, CM Skill Moves Max. 4 Max PS 7 Pace Max. 75 Defending Max. 74 Details Submit by in 8 days Expiry in 15 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>Zoomaestro Your playmaker always had the vision, now they get the legs. Boost pace and dribbling on your CAM or CM and glide past defenders in a blink. Iván Jaime 74 LM PAC 74 SHO 74 PAS 71 DRI 76 DEF 45 PHY 63 CAM ST LW R 3 ★ 4 LM 74.0 Iván Jaime 81 LM PAC 82 SHO 75 PAS 77 DRI 83 DEF 45 PHY 64 CAM ST LW R 4 ★ 4 LM 82.0 REQUIREMENTS Overall Max. 80 Position CAM, CM Skill Moves Max. 4 Max PS 7 Pace Max. 75 Defending Max. 74 UPGRADES +7 OVR 83 +1 SM 4 +5 Positioning 84 +10 Short Pass 85 +7 Balance 82 +10 Dribbling 83 +10 Acceleration 83 +5 Long Shots 83 +5 Curve 81 +7 Reactions 82 +10 Composure 81 +10 Sprint Speed 83 +10 Vision 82 +7 Agility 85 +10 Ball Control 85 +5 Stamina 84 3 in 9 days in 16 days 70% 30%</t>
+          <t>Zoomaestro Your playmaker always had the vision, now they get the legs. Boost pace and dribbling on your CAM or CM and glide past defenders in a blink. Iván Jaime 74 LM PAC 74 SHO 74 PAS 71 DRI 76 DEF 45 PHY 63 CAM ST LW R 3 ★ 4 LM 74.0 Iván Jaime 81 LM PAC 82 SHO 75 PAS 77 DRI 83 DEF 45 PHY 64 CAM ST LW R 4 ★ 4 LM 82.0 REQUIREMENTS Overall Max. 80 Position CAM, CM Skill Moves Max. 4 Max PS 7 Pace Max. 75 Defending Max. 74 UPGRADES +7 OVR 83 +1 SM 4 +5 Positioning 84 +10 Short Pass 85 +7 Balance 82 +10 Dribbling 83 +10 Acceleration 83 +5 Long Shots 83 +5 Curve 81 +7 Reactions 82 +10 Composure 81 +10 Sprint Speed 83 +10 Vision 82 +7 Agility 85 +10 Ball Control 85 +5 Stamina 84 3 in 8 days in 15 days 71% 29%</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM, CM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 83 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM, CM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 83 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM, CM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 83 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM, CM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 83 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>Middle Management Send your junior midfielder to this training to acquire skills necessary for managing the center of the pitch. From passing &amp; shooting, to interceptions &amp; strength, plus many more. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CDM 64.6 Bannan 80 CM PAC 75 SHO 75 PAS 81 DRI 74 DEF 73 PHY 77 CDM L 3 ★ 3 CDM 80.9 REQUIREMENTS Overall Max. 74 Position CDM, CM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 83 UPGRADES +40 OVR 80 +2 WF 3 +40 Finishing 76 +50 Vision 81 +50 Long Pass 81 +40 Standing Tackle 77 +40 Aggression 75 +40 Shot Power 77 +50 Crossing 80 +50 Curve 79 +40 Sliding Tackle 76 +40 Acceleration 75 +40 Long Shots 76 +50 Fk Accuracy 80 +40 Interceptions 77 +40 Jumping 75 +40 Sprint Speed 75 +40 Volleys 75 +50 Short Pass 81 +40 Defensive Awareness 76 +40 Strength 76 3 TRAINING TIME 1 day in 3 days in 10 days 32% 68%</t>
+          <t>Middle Management Send your junior midfielder to this training to acquire skills necessary for managing the center of the pitch. From passing &amp; shooting, to interceptions &amp; strength, plus many more. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CDM 64.6 Bannan 80 CM PAC 75 SHO 75 PAS 81 DRI 74 DEF 73 PHY 77 CDM L 3 ★ 3 CDM 80.9 REQUIREMENTS Overall Max. 74 Position CDM, CM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 83 UPGRADES +40 OVR 80 +2 WF 3 +40 Finishing 76 +50 Vision 81 +50 Long Pass 81 +40 Standing Tackle 77 +40 Aggression 75 +40 Shot Power 77 +50 Crossing 80 +50 Curve 79 +40 Sliding Tackle 76 +40 Acceleration 75 +40 Long Shots 76 +50 Fk Accuracy 80 +40 Interceptions 77 +40 Jumping 75 +40 Sprint Speed 75 +40 Volleys 75 +50 Short Pass 81 +40 Defensive Awareness 76 +40 Strength 76 3 TRAINING TIME 1 day in 7 days in 14 days 32% 68%</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>Rarity Future Stars Academy Overall Min. 83 Overall Max. 83 Max PS 7 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity Future Stars Academy Overall Min. 83 Overall Max. 83 Max PS 7 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>Rarity Future Stars Academy Overall Min. 83 Overall Max. 83 Max PS 7 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity Future Stars Academy Overall Min. 83 Overall Max. 83 Max PS 7 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>Future Stars Academy IV Graduation day has arrived. Complete your Future Star's journey as a clinical finisher or a creative playmaker, ready to shine on the biggest stage. Madjed 70 RM PAC 79 SHO 66 PAS 65 DRI 74 DEF 25 PHY 60 CAM RW ST L 4 ★ 2 RM 69.5 Madjed 85 RM PAC 87 SHO 82 PAS 84 DRI 83 DEF 28 PHY 72 CAM RW ST L 4 ★ 4 RM 86.8 REQUIREMENTS Rarity Future Stars Academy Overall Min. 83 Overall Max. 83 Max PS 7 UPGRADES +2 OVR 85 +5 Long Shots 78 +8 Penalties 75 +6 Composure 80 +5 Jumping 70 +4 Strength 72 +6 Shot Power 80 +8 Volleys 76 +6 Crossing 80 +4 Heading Acc. 72 +3 Stamina 83 +6 Aggression 60 +1 Finishing 84 4 in 7 days in 14 days 84% 16%</t>
+          <t>Future Stars Academy IV Graduation day has arrived. Complete your Future Star's journey as a clinical finisher or a creative playmaker, ready to shine on the biggest stage. Madjed 70 RM PAC 79 SHO 66 PAS 65 DRI 74 DEF 25 PHY 60 CAM RW ST L 4 ★ 2 RM 69.5 Madjed 85 RM PAC 87 SHO 82 PAS 84 DRI 83 DEF 28 PHY 72 CAM RW ST L 4 ★ 4 RM 86.8 REQUIREMENTS Rarity Future Stars Academy Overall Min. 83 Overall Max. 83 Max PS 7 UPGRADES +2 OVR 85 +5 Long Shots 78 +8 Penalties 75 +6 Composure 80 +5 Jumping 70 +4 Strength 72 +6 Shot Power 80 +8 Volleys 76 +6 Crossing 80 +4 Heading Acc. 72 +3 Stamina 83 +6 Aggression 60 +1 Finishing 84 4 in 6 days in 13 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position CB Excluded Position CDM Max PS 7 Pace Max. 75 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position CB Excluded Position CDM Max PS 7 Pace Max. 75 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position CB Excluded Position CDM Max PS 7 Pace Max. 75 Details Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position CB Excluded Position CDM Max PS 7 Pace Max. 75 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>Speed Bump Your centre-back stops attackers. Now they can catch them too. Give a slower CB a pace upgrade and keep the wall standing, even on the counter. Tomiyasu 76 LB PAC 67 SHO 33 PAS 67 DRI 71 DEF 78 PHY 76 RB CB CM R 2 ★ 5 CM 71.0 Tomiyasu 83 LB PAC 77 SHO 33 PAS 70 DRI 73 DEF 82 PHY 80 RB CB CM R 2 ★ 5 CB 80.8 REQUIREMENTS Overall Max. 80 Position CB Excluded Position CDM Max PS 7 Pace Max. 75 UPGRADES +10 OVR 83 +10 Acceleration 77 +4 Long Pass 76 +14 Composure 81 +7 Defensive Awareness 82 +10 Jumping 85 +10 Sprint Speed 77 +7 Reactions 80 +7 Interceptions 82 +12 Standing Tackle 82 +7 Strength 86 +11 Short Pass 80 +5 Ball Control 76 +5 Heading Acc. 80 +7 Sliding Tackle 82 +5 Aggression 84 3 in 7 days in 14 days 60% 40%</t>
+          <t>Speed Bump Your centre-back stops attackers. Now they can catch them too. Give a slower CB a pace upgrade and keep the wall standing, even on the counter. Tomiyasu 76 LB PAC 67 SHO 33 PAS 67 DRI 71 DEF 78 PHY 76 RB CB CM R 2 ★ 5 CM 71.0 Tomiyasu 83 LB PAC 77 SHO 33 PAS 70 DRI 73 DEF 82 PHY 80 RB CB CM R 2 ★ 5 CB 80.8 REQUIREMENTS Overall Max. 80 Position CB Excluded Position CDM Max PS 7 Pace Max. 75 UPGRADES +10 OVR 83 +10 Acceleration 77 +4 Long Pass 76 +14 Composure 81 +7 Defensive Awareness 82 +10 Jumping 85 +10 Sprint Speed 77 +7 Reactions 80 +7 Interceptions 82 +12 Standing Tackle 82 +7 Strength 86 +11 Short Pass 80 +5 Ball Control 76 +5 Heading Acc. 80 +7 Sliding Tackle 82 +5 Aggression 84 3 in 6 days in 13 days 60% 40%</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position CDM, CM Excluded Position CB, ST, CAM Max PS 7 Pace Max. 85 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position CDM, CM Excluded Position CB, ST, CAM Max PS 7 Pace Max. 85 Details Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position CDM, CM Excluded Position CB, ST, CAM Max PS 7 Pace Max. 85 Details Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position CDM, CM Excluded Position CB, ST, CAM Max PS 7 Pace Max. 85 Details Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>Centre Stage Command the centre circle with a resolute midfielder primed to reclaim possession, withstand physical pressure, and pick out key forward runs. Miley 77 CM PAC 68 SHO 66 PAS 76 DRI 75 DEF 76 PHY 69 RB CDM RM R 3 ★ 4 CDM 75.1 Miley 85 CM PAC 75 SHO 66 PAS 82 DRI 75 DEF 81 PHY 84 RB CDM RM R 3 ★ 4 CDM 84.7 REQUIREMENTS Overall Max. 81 Position CDM, CM Excluded Position CB, ST, CAM Max PS 7 Pace Max. 85 UPGRADES +10 OVR 85 +2 SM 3 +2 WF 3 +7 Sprint Speed 77 +10 Short Pass 82 +10 Heading Acc. 81 +30 Jumping 85 +10 Vision 83 +10 Long Pass 83 +10 Defensive Awareness 80 +30 Stamina 84 +10 Crossing 82 +10 Curve 82 +10 Standing Tackle 81 +30 Strength 85 +7 Acceleration 77 +10 Fk Accuracy 82 +10 Interceptions 82 +10 Sliding Tackle 82 +30 Aggression 85 3 in 6 days in 13 days 64% 36%</t>
+          <t>Centre Stage Command the centre circle with a resolute midfielder primed to reclaim possession, withstand physical pressure, and pick out key forward runs. Miley 77 CM PAC 68 SHO 66 PAS 76 DRI 75 DEF 76 PHY 69 RB CDM RM R 3 ★ 4 CDM 75.1 Miley 85 CM PAC 75 SHO 66 PAS 82 DRI 75 DEF 81 PHY 84 RB CDM RM R 3 ★ 4 CDM 84.7 REQUIREMENTS Overall Max. 81 Position CDM, CM Excluded Position CB, ST, CAM Max PS 7 Pace Max. 85 UPGRADES +10 OVR 85 +2 SM 3 +2 WF 3 +7 Sprint Speed 77 +10 Short Pass 82 +10 Heading Acc. 81 +30 Jumping 85 +10 Vision 83 +10 Long Pass 83 +10 Defensive Awareness 80 +30 Stamina 84 +10 Crossing 82 +10 Curve 82 +10 Standing Tackle 81 +30 Strength 85 +7 Acceleration 77 +10 Fk Accuracy 82 +10 Interceptions 82 +10 Sliding Tackle 82 +30 Aggression 85 3 in 5 days in 12 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 85 Details Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 85 Details Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 85 Details Submit by in 5 days Expiry in 12 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 85 Details Submit by in 4 days Expiry in 11 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>Side Step Dominate the touchline by developing a fullback equipped to shut down opposing attackers and lead the charge forward. Neville 75 RB PAC 73 SHO 70 PAS 73 DRI 72 DEF 74 PHY 79 LB R 3 ★ 4 RB 75.5 Neville 81 RB PAC 78 SHO 75 PAS 78 DRI 72 DEF 79 PHY 79 LB R 3 ★ 4 RB 79.7 REQUIREMENTS Overall Max. 80 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 85 UPGRADES +7 OVR 81 +2 WF 3 +5 Sprint Speed 83 +7 Long Shots 78 +7 Crossing 81 +7 Long Pass 76 +7 Defensive Awareness 78 +7 Finishing 78 +7 Volleys 76 +7 Fk Accuracy 78 +7 Curve 77 +7 Standing Tackle 81 +5 Acceleration 83 +7 Shot Power 77 +7 Vision 78 +7 Short Pass 80 +7 Interceptions 78 +7 Sliding Tackle 81 3 in 5 days in 12 days 21% 79%</t>
+          <t>Side Step Dominate the touchline by developing a fullback equipped to shut down opposing attackers and lead the charge forward. Neville 75 RB PAC 73 SHO 70 PAS 73 DRI 72 DEF 74 PHY 79 LB R 3 ★ 4 RB 75.5 Neville 81 RB PAC 78 SHO 75 PAS 78 DRI 72 DEF 79 PHY 79 LB R 3 ★ 4 RB 79.7 REQUIREMENTS Overall Max. 80 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 85 UPGRADES +7 OVR 81 +2 WF 3 +5 Sprint Speed 83 +7 Long Shots 78 +7 Crossing 81 +7 Long Pass 76 +7 Defensive Awareness 78 +7 Finishing 78 +7 Volleys 76 +7 Fk Accuracy 78 +7 Curve 77 +7 Standing Tackle 81 +5 Acceleration 83 +7 Shot Power 77 +7 Vision 78 +7 Short Pass 80 +7 Interceptions 78 +7 Sliding Tackle 81 3 in 4 days in 11 days 22% 78%</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2697,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>Rarity Future Stars Academy Overall Min. 82 Overall Max. 82 Max PS 7 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity Future Stars Academy Overall Min. 82 Overall Max. 82 Max PS 7 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>Rarity Future Stars Academy Overall Min. 82 Overall Max. 82 Max PS 7 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity Future Stars Academy Overall Min. 82 Overall Max. 82 Max PS 7 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>Future Stars Academy III Time to find their signature. Unlock a new PlayStyle and sharpen their pace, shooting or dribbling as your Future Star rises to the next level. Zeitler 68 ST PAC 75 SHO 68 PAS 56 DRI 69 DEF 40 PHY 56 LM CAM LW R 3 ★ 4 ST 65.7 Zeitler 83 ST PAC 84 SHO 78 PAS 84 DRI 86 DEF 41 PHY 69 LM CAM LW R 4 ★ 4 LM 84.7 REQUIREMENTS Rarity Future Stars Academy Overall Min. 82 Overall Max. 82 Max PS 7 UPGRADES +1 OVR 83 +3 Sprint Speed 87 +3 Acceleration 87 3 in 7 days in 14 days 91% 9%</t>
+          <t>Future Stars Academy III Time to find their signature. Unlock a new PlayStyle and sharpen their pace, shooting or dribbling as your Future Star rises to the next level. Zeitler 68 ST PAC 75 SHO 68 PAS 56 DRI 69 DEF 40 PHY 56 LM CAM LW R 3 ★ 4 ST 65.7 Zeitler 83 ST PAC 84 SHO 78 PAS 84 DRI 86 DEF 41 PHY 69 LM CAM LW R 4 ★ 4 LM 84.7 REQUIREMENTS Rarity Future Stars Academy Overall Min. 82 Overall Max. 82 Max PS 7 UPGRADES +1 OVR 83 +3 Sprint Speed 87 +3 Acceleration 87 3 in 6 days in 13 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2932,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position LW, RW Excluded Position ST, CM, CAM Max PS 7 Pace Max. 86 Details Submit by in 3 days Expiry in 10 days Coins Cost 20,000 Points Cost 150</t>
+          <t>Overall Max. 80 Position LW, RW Excluded Position ST, CM, CAM Max PS 7 Pace Max. 86 Details Submit by in 2 days Expiry in 9 days Coins Cost 20,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position LW, RW Excluded Position ST, CM, CAM Max PS 7 Pace Max. 86 Details Submit by in 3 days Expiry in 10 days Coins Cost 20,000 Points Cost 150</t>
+          <t>Overall Max. 80 Position LW, RW Excluded Position ST, CM, CAM Max PS 7 Pace Max. 86 Details Submit by in 2 days Expiry in 9 days Coins Cost 20,000 Points Cost 150</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>Touchline Magic 20,000 150 Unlock defences from out wide with a dynamic winger capable of accelerating past markers, showcasing elite dribbling, and scoring crucial goals. Murphy 79 RW PAC 76 SHO 77 PAS 78 DRI 79 DEF 60 PHY 66 RM R 3 ★ 4 RM 72.0 Murphy 84 RW PAC 85 SHO 80 PAS 79 DRI 84 DEF 60 PHY 68 RM R 4 ★ 4 RM 82.6 REQUIREMENTS Overall Max. 80 Position LW, RW Excluded Position ST, CM, CAM Max PS 7 Pace Max. 86 UPGRADES +10 OVR 84 +1 SM 4 +10 Sprint Speed 85 +7 Long Shots 81 +10 Agility 84 +10 Dribbling 84 +7 Positioning 81 +7 Vision 79 +10 Balance 83 +10 Composure 83 +7 Finishing 82 +7 Short Pass 80 +10 Reactions 83 +7 Stamina 82 +10 Acceleration 85 +7 Shot Power 81 +7 Curve 83 +10 Ball Control 84 3 in 3 days in 10 days 46% 54%</t>
+          <t>Touchline Magic 20,000 150 Unlock defences from out wide with a dynamic winger capable of accelerating past markers, showcasing elite dribbling, and scoring crucial goals. Murphy 79 RW PAC 76 SHO 77 PAS 78 DRI 79 DEF 60 PHY 66 RM R 3 ★ 4 RM 72.0 Murphy 84 RW PAC 85 SHO 80 PAS 79 DRI 84 DEF 60 PHY 68 RM R 4 ★ 4 RM 82.6 REQUIREMENTS Overall Max. 80 Position LW, RW Excluded Position ST, CM, CAM Max PS 7 Pace Max. 86 UPGRADES +10 OVR 84 +1 SM 4 +10 Sprint Speed 85 +7 Long Shots 81 +10 Agility 84 +10 Dribbling 84 +7 Positioning 81 +7 Vision 79 +10 Balance 83 +10 Composure 83 +7 Finishing 82 +7 Short Pass 80 +10 Reactions 83 +7 Stamina 82 +10 Acceleration 85 +7 Shot Power 81 +7 Curve 83 +10 Ball Control 84 3 in 2 days in 9 days 46% 54%</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>Rarity Future Stars Academy Overall Min. 81 Overall Max. 81 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity Future Stars Academy Overall Min. 81 Overall Max. 81 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>Rarity Future Stars Academy Overall Min. 81 Overall Max. 81 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Rarity Future Stars Academy Overall Min. 81 Overall Max. 81 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>Future Stars Academy II The next step in their journey. Help your Future Star grow into a playmaker, a physical powerhouse or a well-rounded all-rounder. Mboup 70 LM PAC 86 SHO 65 PAS 60 DRI 73 DEF 27 PHY 58 ST LW R 3 ★ 3 LM 72.3 Mboup 82 LM PAC 86 SHO 84 PAS 84 DRI 82 DEF 29 PHY 67 ST LW R 3 ★ 4 LM 84.1 REQUIREMENTS Rarity Future Stars Academy Overall Min. 81 Overall Max. 81 UPGRADES +1 OVR 82 +1 Finishing 80 +1 Long Shots 78 +2 Reactions 82 +1 Dribbling 81 +2 Heading Acc. 75 +1 Positioning 81 +1 Shot Power 81 +1 Balance 78 +2 Ball Control 81 +2 Composure 80 +1 Stamina 83 +10 Vision 86 +12 Crossing 82 +15 Fk Accuracy 80 +8 Short Pass 86 +12 Long Pass 82 +12 Curve 84 in 7 days in 14 days 91% 9%</t>
+          <t>Future Stars Academy II The next step in their journey. Help your Future Star grow into a playmaker, a physical powerhouse or a well-rounded all-rounder. Mboup 70 LM PAC 86 SHO 65 PAS 60 DRI 73 DEF 27 PHY 58 ST LW R 3 ★ 3 LM 72.3 Mboup 82 LM PAC 86 SHO 84 PAS 84 DRI 82 DEF 29 PHY 67 ST LW R 3 ★ 4 LM 84.1 REQUIREMENTS Rarity Future Stars Academy Overall Min. 81 Overall Max. 81 UPGRADES +1 OVR 82 +1 Finishing 80 +1 Long Shots 78 +2 Reactions 82 +1 Dribbling 81 +2 Heading Acc. 75 +1 Positioning 81 +1 Shot Power 81 +1 Balance 78 +2 Ball Control 81 +2 Composure 80 +1 Stamina 83 +10 Vision 86 +12 Crossing 82 +15 Fk Accuracy 80 +8 Short Pass 86 +12 Long Pass 82 +12 Curve 84 in 6 days in 13 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CAM, CM Excluded Position CDM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 2 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CAM, CM Excluded Position CDM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 1 day Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CAM, CM Excluded Position CDM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 2 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CAM, CM Excluded Position CDM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 1 day Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ12" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>Playmaker Reborn Reinvent your midfield engine with sharp vision and crisp passes to dictate match tempo from the center. Taylor 67 LM PAC 83 SHO 62 PAS 58 DRI 69 DEF 36 PHY 64 CM CAM LW R 3 ★ 5 LM 70.2 Taylor 80 LM PAC 83 SHO 76 PAS 80 DRI 78 DEF 36 PHY 66 CM CAM LW R 3 ★ 5 LM 78.8 REQUIREMENTS Overall Max. 74 Position CAM, CM Excluded Position CDM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 80 +40 Positioning 77 +40 Volleys 76 +50 Fk Accuracy 79 +40 Agility 78 +40 Dribbling 77 +40 Finishing 76 +40 Penalties 77 +50 Short Pass 80 +40 Balance 76 +40 Composure 77 +40 Acceleration 76 +40 Shot Power 75 +50 Vision 80 +50 Long Pass 81 +40 Reactions 74 +40 Stamina 79 +40 Sprint Speed 75 +40 Long Shots 77 +50 Crossing 79 +50 Curve 79 +40 Ball Control 77 3 TRAINING TIME 1 day in 2 days in 10 days 33% 67%</t>
+          <t>Playmaker Reborn Reinvent your midfield engine with sharp vision and crisp passes to dictate match tempo from the center. Taylor 67 LM PAC 83 SHO 62 PAS 58 DRI 69 DEF 36 PHY 64 CM CAM LW R 3 ★ 5 LM 70.2 Taylor 80 LM PAC 83 SHO 76 PAS 80 DRI 78 DEF 36 PHY 66 CM CAM LW R 3 ★ 5 LM 78.8 REQUIREMENTS Overall Max. 74 Position CAM, CM Excluded Position CDM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 80 +40 Positioning 77 +40 Volleys 76 +50 Fk Accuracy 79 +40 Agility 78 +40 Dribbling 77 +40 Finishing 76 +40 Penalties 77 +50 Short Pass 80 +40 Balance 76 +40 Composure 77 +40 Acceleration 76 +40 Shot Power 75 +50 Vision 80 +50 Long Pass 81 +40 Reactions 74 +40 Stamina 79 +40 Sprint Speed 75 +40 Long Shots 77 +50 Crossing 79 +50 Curve 79 +40 Ball Control 77 3 TRAINING TIME 1 day in 1 day in 9 days 33% 67%</t>
         </is>
       </c>
     </row>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>Overall Max. 83 Max PS 2 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 83 Max PS 2 Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>Overall Max. 83 Max PS 2 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 83 Max PS 2 Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>Quick Step [FC 26 Obj] Unlocked by completing the FC 26 Season 9 Pass Spence 80 LB PAC 89 SHO 54 PAS 71 DRI 79 DEF 76 PHY 75 RB R 3 ★ 4 RB 81.5 Spence 80 LB PAC 89 SHO 54 PAS 71 DRI 79 DEF 76 PHY 75 RB R 3 ★ 4 RB 83.2 REQUIREMENTS Overall Max. 83 Max PS 2 UPGRADES 3 in 1 year in 1 year 75% 25%</t>
+          <t>Quick Step [FC 26 Obj] Unlocked by completing the FC 26 Season 9 Pass Spence 80 LB PAC 89 SHO 54 PAS 71 DRI 79 DEF 76 PHY 75 RB R 3 ★ 4 RB 81.5 Spence 80 LB PAC 89 SHO 54 PAS 71 DRI 79 DEF 76 PHY 75 RB R 3 ★ 4 RB 83.2 REQUIREMENTS Overall Max. 83 Max PS 2 UPGRADES 3 in 11 months in 11 months 75% 25%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position CAM, ST Born After 2003-10-09 Max PS 7 Pace Max. 86 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position CAM, ST Born After 2003-10-09 Max PS 7 Pace Max. 86 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position CAM, ST Born After 2003-10-09 Max PS 7 Pace Max. 86 Details Type Pathway, pick one option per level Submit by in 7 days Expiry in 14 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position CAM, ST Born After 2003-10-09 Max PS 7 Pace Max. 86 Details Type Pathway, pick one option per level Submit by in 6 days Expiry in 13 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ14" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>Future Stars Academy I Every legend starts somewhere. Develop your young forward into a complete player, then choose whether they make their mark with pace, shooting or dribbling. Mboup 70 LM PAC 86 SHO 65 PAS 60 DRI 73 DEF 27 PHY 58 ST LW R 3 ★ 3 LM 72.3 Mboup 81 LM PAC 86 SHO 84 PAS 79 DRI 81 DEF 29 PHY 67 ST LW R 3 ★ 4 LM 83.2 REQUIREMENTS Overall Max. 80 Position CAM, ST Born After 2003-10-09 Max PS 7 Pace Max. 86 UPGRADES C +34 OVR 81 +2 SM 4 +20 Finishing 79 +30 Vision 82 +35 Long Pass 76 +25 Reactions 80 +20 Heading Acc. 73 +20 Acceleration 81 +20 Shot Power 80 +35 Crossing 76 +35 Curve 76 +32 Ball Control 80 +25 Stamina 82 +20 Sprint Speed 81 +20 Long Shots 77 +30 Fk Accuracy 72 +32 Agility 80 +32 Dribbling 80 +15 Strength 73 +25 Positioning 80 +20 Volleys 75 +35 Short Pass 82 +35 Balance 77 +30 Composure 78 Future Stars Academy in 7 days in 14 days 95% 5%</t>
+          <t>Future Stars Academy I Every legend starts somewhere. Develop your young forward into a complete player, then choose whether they make their mark with pace, shooting or dribbling. Mboup 70 LM PAC 86 SHO 65 PAS 60 DRI 73 DEF 27 PHY 58 ST LW R 3 ★ 3 LM 72.3 Mboup 81 LM PAC 86 SHO 84 PAS 79 DRI 81 DEF 29 PHY 67 ST LW R 3 ★ 4 LM 83.2 REQUIREMENTS Overall Max. 80 Position CAM, ST Born After 2003-10-09 Max PS 7 Pace Max. 86 UPGRADES C +34 OVR 81 +2 SM 4 +20 Finishing 79 +30 Vision 82 +35 Long Pass 76 +25 Reactions 80 +20 Heading Acc. 73 +20 Acceleration 81 +20 Shot Power 80 +35 Crossing 76 +35 Curve 76 +32 Ball Control 80 +25 Stamina 82 +20 Sprint Speed 81 +20 Long Shots 77 +30 Fk Accuracy 72 +32 Agility 80 +32 Dribbling 80 +15 Strength 73 +25 Positioning 80 +20 Volleys 75 +35 Short Pass 82 +35 Balance 77 +30 Composure 78 Future Stars Academy in 6 days in 13 days 95% 5%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position ST Excluded Position CB, CM, CAM Max PS 7 Pace Max. 85 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position ST Excluded Position CB, CM, CAM Max PS 7 Pace Max. 85 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position ST Excluded Position CB, CM, CAM Max PS 7 Pace Max. 85 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position ST Excluded Position CB, CM, CAM Max PS 7 Pace Max. 85 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ15" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>Nine Duty Elevate your striker’s attacking impact to help them consistently influence matches when leading the line. Rodney 60 ST PAC 84 SHO 59 PAS 52 DRI 60 DEF 29 PHY 65 RM LM RW LW R 3 ★ 4 ST 65.3 Rodney 79 ST PAC 84 SHO 79 PAS 75 DRI 78 DEF 29 PHY 65 RM LM RW LW R 3 ★ 4 ST 80.0 REQUIREMENTS Overall Max. 74 Position ST Excluded Position CB, CM, CAM Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +2 SM 3 +50 Positioning 80 +50 Volleys 79 +40 Fk Accuracy 77 +40 Agility 78 +40 Dribbling 78 +50 Finishing 79 +50 Penalties 81 +40 Short Pass 75 +40 Balance 78 +40 Composure 76 +40 Acceleration 78 +50 Shot Power 79 +40 Vision 75 +40 Long Pass 75 +40 Reactions 78 +40 Sprint Speed 78 +50 Long Shots 78 +40 Crossing 75 +40 Curve 77 +40 Ball Control 78 3 TRAINING TIME 1 day in 3 days in 10 days 76% 24%</t>
+          <t>Nine Duty Elevate your striker’s attacking impact to help them consistently influence matches when leading the line. Rodney 60 ST PAC 84 SHO 59 PAS 52 DRI 60 DEF 29 PHY 65 RM LM RW LW R 3 ★ 4 ST 65.3 Rodney 79 ST PAC 84 SHO 79 PAS 75 DRI 78 DEF 29 PHY 65 RM LM RW LW R 3 ★ 4 ST 80.0 REQUIREMENTS Overall Max. 74 Position ST Excluded Position CB, CM, CAM Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +2 SM 3 +50 Positioning 80 +50 Volleys 79 +40 Fk Accuracy 77 +40 Agility 78 +40 Dribbling 78 +50 Finishing 79 +50 Penalties 81 +40 Short Pass 75 +40 Balance 78 +40 Composure 76 +40 Acceleration 78 +50 Shot Power 79 +40 Vision 75 +40 Long Pass 75 +40 Reactions 78 +40 Sprint Speed 78 +50 Long Shots 78 +40 Crossing 75 +40 Curve 77 +40 Ball Control 78 3 TRAINING TIME 1 day in 2 days in 9 days 76% 24%</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 3 days Expiry in 3 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 3 days Expiry in 3 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ16" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CDM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.2 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 3 days in 3 days 83% 17%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CDM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.2 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 2 days in 2 days 83% 17%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position ST Pace Max. 81 Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ17" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.7 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.9 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 80% 20%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.7 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.9 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 11 months in 11 months 80% 20%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ18" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Trimmel 75 RB PAC 61 SHO 65 PAS 74 DRI 68 DEF 74 PHY 79 RM R 3 ★ 3 RB 62.1 Trimmel 79 RB PAC 80 SHO 65 PAS 77 DRI 79 DEF 76 PHY 81 RM R 3 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 88% 12%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Trimmel 75 RB PAC 61 SHO 65 PAS 74 DRI 68 DEF 74 PHY 79 RM R 3 ★ 3 RB 62.1 Trimmel 79 RB PAC 80 SHO 65 PAS 77 DRI 79 DEF 76 PHY 81 RM R 3 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 11 months in 11 months 88% 12%</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>RB Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position RB Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Position RB Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ19" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="DA19" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Luis Henrique 77 RB PAC 90 SHO 74 PAS 72 DRI 78 DEF 70 PHY 76 RM R 3 ★ 3 RB 77.3 Luis Henrique 77 RB PAC 90 SHO 74 PAS 72 DRI 78 DEF 70 PHY 76 RM R 3 ★ 3 RB 78.8 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 82% 18%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Luis Henrique 77 RB PAC 90 SHO 74 PAS 72 DRI 78 DEF 70 PHY 76 RM R 3 ★ 3 RB 77.3 Luis Henrique 77 RB PAC 90 SHO 74 PAS 72 DRI 78 DEF 70 PHY 76 RM R 3 ★ 3 RB 78.8 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 11 months in 11 months 82% 18%</t>
         </is>
       </c>
     </row>
@@ -5013,17 +5013,17 @@
       <c r="CV20" t="inlineStr"/>
       <c r="CW20" t="inlineStr">
         <is>
-          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 82% of GG users upvoted this Evolution. Vote Now! 82% 18% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Endemann 80 RW PAC 87 SHO 75 PAS 74 DRI 79 DEF 45 PHY 70 RM R 4 ★ 4 RM 79.8 Ba Loua 80 RW PAC 92 SHO 76 PAS 75 DRI 80 DEF 42 PHY 65 RM LM L 3 ★ 3 RM 81.6 Elanga 79 RW PAC 94 SHO 70 PAS 74 DRI 80 DEF 39 PHY 65 RM R 3 ★ 5 RM 83.9 Mudryk 75 LM PAC 92 SHO 71 PAS 71 DRI 78 DEF 38 PHY 57 LW R 4 ★ 4 LM 82.2 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 85.3 Rosario 80 CDM PAC 73 SHO 66 PAS 72 DRI 77 DEF 80 PHY 84 CB CM R 3 ★ 3 CDM 80.8 Evolution Upgrades A 4 Level 1 Bento 80 GK DIV 80 HAN 71 KIC 78 REF 83 SPD 39 POS 81 R 1 ★ 2 Bento 80 GK DIV 80 HAN 71 KIC 78 REF 83 SPD 39 POS 81 R 1 ★ 2 GK 78.6 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
+          <t>! OVERVIEW ELIGIBLE PLAYERS EVOLVED PLAYERS TRENDING EVOLVED PLAYERS Community Verdict Worth Doing 82% of GG users upvoted this Evolution. Vote Now! 82% 18% Completion Difficulty Easy Number of Games 1 Recommended Position ST Number of Wins 0 Is Your Player Eligible? Want to check eligibility for your already evolved players? Sync them now on GG Club Trending Evolved Players View All Soulé 80 CAM PAC 82 SHO 76 PAS 79 DRI 81 DEF 48 PHY 66 ST L 4 ★ 4 CAM 81.1 Stoica 80 LM PAC 92 SHO 80 PAS 74 DRI 81 DEF 40 PHY 78 CAM ST LW R 3 ★ 3 ST 85.7 Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 85.3 Poku 76 RM PAC 90 SHO 67 PAS 68 DRI 77 DEF 40 PHY 64 LM RW LW R 3 ★ 5 RM 80.6 Elanga 79 RW PAC 94 SHO 70 PAS 74 DRI 80 DEF 39 PHY 65 RM R 3 ★ 5 RM 83.9 Madueke 80 RW PAC 88 SHO 75 PAS 74 DRI 83 DEF 45 PHY 69 RM L 4 ★ 3 RM 82.8 Evolution Upgrades A 4 Level 1 Bento 80 GK DIV 80 HAN 71 KIC 78 REF 83 SPD 39 POS 81 R 1 ★ 2 Bento 80 GK DIV 80 HAN 71 KIC 78 REF 83 SPD 39 POS 81 R 1 ★ 2 GK 78.6 UPGRADE PATHS Pick one Option A Recommended 4 Option B 4</t>
         </is>
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 3 Details Type Pathway, pick one option per level Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ20" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="DA20" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.7 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 83.0 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES A 4 in 1 year in 1 year 82% 18%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.7 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 83.0 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES A 4 in 11 months in 11 months 82% 18%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 2 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 2 Details Submit by in 8 days Expiry in 8 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 80 Max PS 2 Details Submit by in 7 days Expiry in 7 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ21" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="DA21" t="inlineStr">
         <is>
-          <t>Gamechanger Add Gamechanger to any qualified player. Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 79.4 Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 80.9 REQUIREMENTS Overall Max. 80 Max PS 2 UPGRADES 3 in 8 days in 8 days 49% 51%</t>
+          <t>Gamechanger Add Gamechanger to any qualified player. Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 79.4 Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 80.9 REQUIREMENTS Overall Max. 80 Max PS 2 UPGRADES 3 in 7 days in 7 days 50% 50%</t>
         </is>
       </c>
     </row>
@@ -5196,32 +5196,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Technical - EA SPORTS FC 27</t>
+          <t>Frontline Flair - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2543-technical/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LW, RW, ST</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CAM</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -5229,23 +5241,39 @@
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>84</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>84</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>82</v>
+      </c>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
+      <c r="AF22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>84</v>
+      </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
@@ -5315,27 +5343,27 @@
       <c r="CV22" t="inlineStr"/>
       <c r="CW22" t="inlineStr">
         <is>
-          <t>3 Level 1 Di Gregorio 80 GK DIV 81 HAN 80 KIC 78 REF 84 SPD 56 POS 79 R 1 ★ 3 Di Gregorio 80 GK DIV 81 HAN 80 KIC 78 REF 84 SPD 56 POS 79 R 1 ★ 3 GK 76.9 UPGRADES 3</t>
+          <t>+1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 Level 1 Girelli 83 ST PAC 78 SHO 81 PAS 70 DRI 81 DEF 45 PHY 78 R 3 ★ 4 Girelli 84 ST PAC 80 SHO 82 PAS 70 DRI 83 DEF 45 PHY 78 R 3 ★ 4 ST 79.4 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3</t>
         </is>
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 2 Details Submit by in 19 hours Expiry in 19 hours Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>Overall Max. 80 Max PS 2 Details Submit by in 19 hours Expiry in 19 hours Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 2 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Frontline Flair 2</t>
         </is>
       </c>
       <c r="DA22" t="inlineStr">
         <is>
-          <t>Technical Unlocked by completing the Assist 5 task in the Back to Basics Objective objective Gittens 77 LM PAC 92 SHO 72 PAS 66 DRI 82 DEF 27 PHY 55 LW R 4 ★ 3 LM 80.0 Gittens 77 LM PAC 92 SHO 72 PAS 66 DRI 82 DEF 27 PHY 55 LW R 4 ★ 3 LM 80.8 REQUIREMENTS Overall Max. 80 Max PS 2 UPGRADES 3 in 19 hours in 19 hours 89% 11%</t>
+          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Meerdink 80 ST PAC 78 SHO 81 PAS 70 DRI 80 DEF 38 PHY 84 L 4 ★ 3 ST 80.6 Meerdink 81 ST PAC 80 SHO 82 PAS 70 DRI 82 DEF 38 PHY 84 L 4 ★ 3 ST 82.1 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 2 days in 9 days 75% 25%</t>
         </is>
       </c>
     </row>
@@ -5347,44 +5375,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frontline Flair - EA SPORTS FC 27</t>
+          <t>Pinged Pass - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>LW, RW, ST</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>CAM</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -5392,39 +5408,23 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>84</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>84</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>82</v>
-      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>84</v>
-      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
@@ -5494,27 +5494,27 @@
       <c r="CV23" t="inlineStr"/>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>+1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 Level 1 Girelli 83 ST PAC 78 SHO 81 PAS 70 DRI 81 DEF 45 PHY 78 R 3 ★ 4 Girelli 84 ST PAC 80 SHO 82 PAS 70 DRI 83 DEF 45 PHY 78 R 3 ★ 4 ST 79.4 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3</t>
+          <t>3 Level 1 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 ST 75.2 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 Details Submit by in 3 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ23" t="inlineStr">
         <is>
-          <t>Frontline Flair 2</t>
+          <t>Pinged Pass</t>
         </is>
       </c>
       <c r="DA23" t="inlineStr">
         <is>
-          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Meerdink 80 ST PAC 78 SHO 81 PAS 70 DRI 80 DEF 38 PHY 84 L 4 ★ 3 ST 80.6 Meerdink 81 ST PAC 80 SHO 82 PAS 70 DRI 82 DEF 38 PHY 84 L 4 ★ 3 ST 82.1 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 3 days in 10 days 77% 23%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Vite 76 CM PAC 80 SHO 61 PAS 73 DRI 75 DEF 73 PHY 67 CDM CAM L 3 ★ 4 CDM 78.6 Vite 76 CM PAC 80 SHO 61 PAS 73 DRI 75 DEF 73 PHY 67 CDM CAM L 3 ★ 4 CDM 80.1 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 9 days in 9 days 95% 5%</t>
         </is>
       </c>
     </row>
@@ -5531,23 +5531,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pinged Pass - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -5557,17 +5561,17 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>83</v>
+      </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
@@ -5602,8 +5606,12 @@
       <c r="BE24" t="inlineStr"/>
       <c r="BF24" t="inlineStr"/>
       <c r="BG24" t="inlineStr"/>
-      <c r="BH24" t="inlineStr"/>
-      <c r="BI24" t="inlineStr"/>
+      <c r="BH24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>83</v>
+      </c>
       <c r="BJ24" t="inlineStr"/>
       <c r="BK24" t="inlineStr"/>
       <c r="BL24" t="inlineStr"/>
@@ -5618,8 +5626,12 @@
       <c r="BU24" t="inlineStr"/>
       <c r="BV24" t="inlineStr"/>
       <c r="BW24" t="inlineStr"/>
-      <c r="BX24" t="inlineStr"/>
-      <c r="BY24" t="inlineStr"/>
+      <c r="BX24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>84</v>
+      </c>
       <c r="BZ24" t="inlineStr"/>
       <c r="CA24" t="inlineStr"/>
       <c r="CB24" t="inlineStr"/>
@@ -5645,27 +5657,27 @@
       <c r="CV24" t="inlineStr"/>
       <c r="CW24" t="inlineStr">
         <is>
-          <t>3 Level 1 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 Jackson 79 ST PAC 76 SHO 77 PAS 69 DRI 79 DEF 40 PHY 76 R 3 ★ 3 ST 75.2 UPGRADES 3</t>
+          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Schröder 82 ST PAC 83 SHO 84 PAS 68 DRI 83 DEF 29 PHY 73 CAM R 3 ★ 3 Schröder 83 ST PAC 83 SHO 84 PAS 68 DRI 84 DEF 29 PHY 73 CAM R 3 ★ 3 ST 80.8 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
         </is>
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 82 Position ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 82 Position ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
-          <t>Pinged Pass</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="DA24" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Vite 76 CM PAC 80 SHO 61 PAS 73 DRI 75 DEF 73 PHY 67 CDM CAM L 3 ★ 4 CDM 78.6 Vite 76 CM PAC 80 SHO 61 PAS 73 DRI 75 DEF 73 PHY 67 CDM CAM L 3 ★ 4 CDM 80.1 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 10 days in 10 days 95% 5%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.0 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.4 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 11 months in 11 months 35% 65%</t>
         </is>
       </c>
     </row>
@@ -5677,30 +5689,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
+          <t>LW, RW, ST</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -5712,17 +5724,21 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>83</v>
-      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
@@ -5757,12 +5773,8 @@
       <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="inlineStr"/>
       <c r="BG25" t="inlineStr"/>
-      <c r="BH25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>83</v>
-      </c>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
       <c r="BJ25" t="inlineStr"/>
       <c r="BK25" t="inlineStr"/>
       <c r="BL25" t="inlineStr"/>
@@ -5777,12 +5789,8 @@
       <c r="BU25" t="inlineStr"/>
       <c r="BV25" t="inlineStr"/>
       <c r="BW25" t="inlineStr"/>
-      <c r="BX25" t="n">
-        <v>3</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>84</v>
-      </c>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="inlineStr"/>
       <c r="CA25" t="inlineStr"/>
       <c r="CB25" t="inlineStr"/>
@@ -5808,27 +5816,27 @@
       <c r="CV25" t="inlineStr"/>
       <c r="CW25" t="inlineStr">
         <is>
-          <t>+1 OVR 83 +4 Short Pass 83 +3 Composure 84 Level 1 Schröder 82 ST PAC 83 SHO 84 PAS 68 DRI 83 DEF 29 PHY 73 CAM R 3 ★ 3 Schröder 83 ST PAC 83 SHO 84 PAS 68 DRI 84 DEF 29 PHY 73 CAM R 3 ★ 3 ST 80.8 UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84</t>
+          <t>B · A 4 Level 1 Lewis-Potter 81 LB PAC 81 SHO 74 PAS 78 DRI 82 DEF 76 PHY 70 RM LM RW LW R 3 ★ 4 Lewis-Potter 81 LB PAC 81 SHO 74 PAS 78 DRI 82 DEF 76 PHY 70 RM LM RW LW R 3 ★ 4 LM 80.2 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
         </is>
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>Overall Max. 82 Position ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>Overall Max. 82 Position ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Shooting Practice [SP+ 28]</t>
         </is>
       </c>
       <c r="DA25" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.0 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.4 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 11 months in 11 months 35% 65%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 83.6 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 9 days in 9 days 81% 19%</t>
         </is>
       </c>
     </row>
@@ -5840,32 +5848,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
+          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>LW, RW, ST</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -5877,14 +5881,10 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
@@ -5967,27 +5967,27 @@
       <c r="CV26" t="inlineStr"/>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>B · A 4 Level 1 Lewis-Potter 81 LB PAC 81 SHO 74 PAS 78 DRI 82 DEF 76 PHY 70 RM LM RW LW R 3 ★ 4 Lewis-Potter 81 LB PAC 81 SHO 74 PAS 78 DRI 82 DEF 76 PHY 70 RM LM RW LW R 3 ★ 4 LM 80.2 UPGRADE PATHS Pick one Option A 4 Option B Recommended 4</t>
+          <t>A · A 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 ST 72.3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
         <is>
-          <t>Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ26" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28]</t>
+          <t>Creative or Composed? [SP 27]</t>
         </is>
       </c>
       <c r="DA26" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 83.6 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 10 days in 10 days 82% 18%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.2 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 9 days in 9 days 88% 12%</t>
         </is>
       </c>
     </row>
@@ -5999,32 +5999,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LB, ST</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -6032,15 +6044,27 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
+      <c r="X27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>83</v>
+      </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
@@ -6053,46 +6077,122 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="inlineStr"/>
-      <c r="BE27" t="inlineStr"/>
+      <c r="AL27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>78</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>77</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>74</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>81</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>82</v>
+      </c>
       <c r="BF27" t="inlineStr"/>
       <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="inlineStr"/>
-      <c r="BI27" t="inlineStr"/>
-      <c r="BJ27" t="inlineStr"/>
-      <c r="BK27" t="inlineStr"/>
-      <c r="BL27" t="inlineStr"/>
-      <c r="BM27" t="inlineStr"/>
-      <c r="BN27" t="inlineStr"/>
-      <c r="BO27" t="inlineStr"/>
-      <c r="BP27" t="inlineStr"/>
-      <c r="BQ27" t="inlineStr"/>
-      <c r="BR27" t="inlineStr"/>
-      <c r="BS27" t="inlineStr"/>
-      <c r="BT27" t="inlineStr"/>
-      <c r="BU27" t="inlineStr"/>
-      <c r="BV27" t="inlineStr"/>
-      <c r="BW27" t="inlineStr"/>
-      <c r="BX27" t="inlineStr"/>
-      <c r="BY27" t="inlineStr"/>
+      <c r="BH27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>76</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>80</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>78</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>86</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>85</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>78</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>85</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>84</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>80</v>
+      </c>
       <c r="BZ27" t="inlineStr"/>
       <c r="CA27" t="inlineStr"/>
       <c r="CB27" t="inlineStr"/>
@@ -6105,40 +6205,48 @@
       <c r="CI27" t="inlineStr"/>
       <c r="CJ27" t="inlineStr"/>
       <c r="CK27" t="inlineStr"/>
-      <c r="CL27" t="inlineStr"/>
-      <c r="CM27" t="inlineStr"/>
+      <c r="CL27" t="n">
+        <v>10</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>72</v>
+      </c>
       <c r="CN27" t="inlineStr"/>
       <c r="CO27" t="inlineStr"/>
       <c r="CP27" t="inlineStr"/>
       <c r="CQ27" t="inlineStr"/>
-      <c r="CR27" t="inlineStr"/>
-      <c r="CS27" t="inlineStr"/>
+      <c r="CR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>3</v>
+      </c>
       <c r="CT27" t="inlineStr"/>
       <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="inlineStr"/>
       <c r="CW27" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 Ravensbergen 79 ST PAC 75 SHO 80 PAS 65 DRI 75 DEF 33 PHY 73 R 3 ★ 3 ST 72.3 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Sudakov 78 CAM PAC 80 SHO 76 PAS 77 DRI 80 DEF 60 PHY 72 LM LW R 3 ★ 4 Sudakov 83 CAM PAC 80 SHO 76 PAS 77 DRI 82 DEF 60 PHY 72 LM LW R 3 ★ 4 LM 78.2 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
         </is>
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27]</t>
+          <t>Winger Glow Up [SP+ 26]</t>
         </is>
       </c>
       <c r="DA27" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.2 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 10 days in 10 days 88% 13%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LW 71.0 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 81.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 9 days in 9 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -6155,39 +6263,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>LW</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>LB, ST</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -6195,27 +6291,15 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
-      <c r="X28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>83</v>
-      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
@@ -6228,122 +6312,46 @@
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>78</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>77</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>74</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>74</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>81</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>82</v>
-      </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
       <c r="BF28" t="inlineStr"/>
       <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>76</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>80</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>78</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>86</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>85</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>78</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>85</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>84</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>80</v>
-      </c>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+      <c r="BO28" t="inlineStr"/>
+      <c r="BP28" t="inlineStr"/>
+      <c r="BQ28" t="inlineStr"/>
+      <c r="BR28" t="inlineStr"/>
+      <c r="BS28" t="inlineStr"/>
+      <c r="BT28" t="inlineStr"/>
+      <c r="BU28" t="inlineStr"/>
+      <c r="BV28" t="inlineStr"/>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
+      <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="inlineStr"/>
       <c r="CA28" t="inlineStr"/>
       <c r="CB28" t="inlineStr"/>
@@ -6356,48 +6364,40 @@
       <c r="CI28" t="inlineStr"/>
       <c r="CJ28" t="inlineStr"/>
       <c r="CK28" t="inlineStr"/>
-      <c r="CL28" t="n">
-        <v>10</v>
-      </c>
-      <c r="CM28" t="n">
-        <v>72</v>
-      </c>
+      <c r="CL28" t="inlineStr"/>
+      <c r="CM28" t="inlineStr"/>
       <c r="CN28" t="inlineStr"/>
       <c r="CO28" t="inlineStr"/>
       <c r="CP28" t="inlineStr"/>
       <c r="CQ28" t="inlineStr"/>
-      <c r="CR28" t="n">
-        <v>1</v>
-      </c>
-      <c r="CS28" t="n">
-        <v>3</v>
-      </c>
+      <c r="CR28" t="inlineStr"/>
+      <c r="CS28" t="inlineStr"/>
       <c r="CT28" t="inlineStr"/>
       <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="inlineStr"/>
       <c r="CW28" t="inlineStr">
         <is>
-          <t>+10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 Level 1 Sudakov 78 CAM PAC 80 SHO 76 PAS 77 DRI 80 DEF 60 PHY 72 LM LW R 3 ★ 4 Sudakov 83 CAM PAC 80 SHO 76 PAS 77 DRI 82 DEF 60 PHY 72 LM LW R 3 ★ 4 LM 78.2 UPGRADES +10 OVR 83 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84</t>
+          <t>A · A 3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 GK 77.6 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
         </is>
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26]</t>
+          <t>Tactical Ascent [SP+ 14]</t>
         </is>
       </c>
       <c r="DA28" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LW 71.0 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 81.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 10 days in 10 days 90% 10%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.0 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.1 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 9 days in 9 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -6409,17 +6409,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
+          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -6528,27 +6528,27 @@
       <c r="CV29" t="inlineStr"/>
       <c r="CW29" t="inlineStr">
         <is>
-          <t>A · A 3 Level 1 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 Atubolu 79 GK DIV 79 HAN 74 KIC 79 REF 80 SPD 55 POS 76 R 1 ★ 3 GK 77.6 UPGRADE PATHS Pick one Option A Recommended 3 Option B 3</t>
+          <t>3 Level 1 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 CAM 71.8 UPGRADES 3</t>
         </is>
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY29" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Type Pathway, pick one option per level Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Max PS 2 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ29" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14]</t>
+          <t>Relentless [SP 11]</t>
         </is>
       </c>
       <c r="DA29" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.0 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.1 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 10 days in 10 days 90% 10%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.2 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.7 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 9 days in 9 days 38% 63%</t>
         </is>
       </c>
     </row>
@@ -6565,12 +6565,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -6581,11 +6581,23 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CAM, CM</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -6593,15 +6605,23 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
+      <c r="X30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>80</v>
+      </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
@@ -6614,46 +6634,118 @@
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="inlineStr"/>
-      <c r="BC30" t="inlineStr"/>
+      <c r="AL30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>78</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>82</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>83</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>82</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>78</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>78</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>70</v>
+      </c>
       <c r="BD30" t="inlineStr"/>
       <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="inlineStr"/>
       <c r="BG30" t="inlineStr"/>
-      <c r="BH30" t="inlineStr"/>
-      <c r="BI30" t="inlineStr"/>
-      <c r="BJ30" t="inlineStr"/>
-      <c r="BK30" t="inlineStr"/>
-      <c r="BL30" t="inlineStr"/>
-      <c r="BM30" t="inlineStr"/>
-      <c r="BN30" t="inlineStr"/>
-      <c r="BO30" t="inlineStr"/>
-      <c r="BP30" t="inlineStr"/>
-      <c r="BQ30" t="inlineStr"/>
-      <c r="BR30" t="inlineStr"/>
-      <c r="BS30" t="inlineStr"/>
-      <c r="BT30" t="inlineStr"/>
-      <c r="BU30" t="inlineStr"/>
-      <c r="BV30" t="inlineStr"/>
-      <c r="BW30" t="inlineStr"/>
-      <c r="BX30" t="inlineStr"/>
-      <c r="BY30" t="inlineStr"/>
+      <c r="BH30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>72</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>62</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>77</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>77</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>76</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>76</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>76</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>80</v>
+      </c>
       <c r="BZ30" t="inlineStr"/>
       <c r="CA30" t="inlineStr"/>
       <c r="CB30" t="inlineStr"/>
@@ -6664,10 +6756,18 @@
       <c r="CG30" t="inlineStr"/>
       <c r="CH30" t="inlineStr"/>
       <c r="CI30" t="inlineStr"/>
-      <c r="CJ30" t="inlineStr"/>
-      <c r="CK30" t="inlineStr"/>
-      <c r="CL30" t="inlineStr"/>
-      <c r="CM30" t="inlineStr"/>
+      <c r="CJ30" t="n">
+        <v>10</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>78</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>10</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>67</v>
+      </c>
       <c r="CN30" t="inlineStr"/>
       <c r="CO30" t="inlineStr"/>
       <c r="CP30" t="inlineStr"/>
@@ -6679,27 +6779,27 @@
       <c r="CV30" t="inlineStr"/>
       <c r="CW30" t="inlineStr">
         <is>
-          <t>3 Level 1 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 Tanikawa 79 CAM PAC 72 SHO 76 PAS 76 DRI 79 DEF 56 PHY 66 RM CM RW R 3 ★ 5 CAM 71.8 UPGRADES 3</t>
+          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Panichelli 79 ST PAC 69 SHO 81 PAS 63 DRI 73 DEF 28 PHY 82 R 3 ★ 3 Panichelli 80 ST PAC 69 SHO 81 PAS 64 DRI 73 DEF 28 PHY 82 R 3 ★ 3 ST 69.2 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
         </is>
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY30" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Max PS 2 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
-          <t>Relentless [SP 11]</t>
+          <t>Striker Glow Up [SP 7]</t>
         </is>
       </c>
       <c r="DA30" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.2 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.7 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 10 days in 10 days 38% 63%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.5 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 9 days in 9 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -6711,17 +6811,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -6734,41 +6834,29 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>CM, CDM</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>CAM, CM</t>
+          <t>CAM Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
         <v>80</v>
@@ -6777,126 +6865,62 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>79</v>
+      </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>79</v>
+      </c>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>78</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>82</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>83</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>82</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>78</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>78</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>70</v>
-      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="inlineStr"/>
       <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="inlineStr"/>
       <c r="BG31" t="inlineStr"/>
-      <c r="BH31" t="n">
-        <v>8</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>72</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>8</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>62</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>15</v>
-      </c>
-      <c r="BM31" t="n">
-        <v>77</v>
-      </c>
-      <c r="BN31" t="n">
-        <v>15</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>77</v>
-      </c>
-      <c r="BR31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>76</v>
-      </c>
-      <c r="BT31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BU31" t="n">
-        <v>76</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>76</v>
-      </c>
-      <c r="BX31" t="n">
-        <v>8</v>
-      </c>
-      <c r="BY31" t="n">
-        <v>80</v>
-      </c>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+      <c r="BO31" t="inlineStr"/>
+      <c r="BP31" t="inlineStr"/>
+      <c r="BQ31" t="inlineStr"/>
+      <c r="BR31" t="inlineStr"/>
+      <c r="BS31" t="inlineStr"/>
+      <c r="BT31" t="inlineStr"/>
+      <c r="BU31" t="inlineStr"/>
+      <c r="BV31" t="inlineStr"/>
+      <c r="BW31" t="inlineStr"/>
+      <c r="BX31" t="inlineStr"/>
+      <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="inlineStr"/>
       <c r="CA31" t="inlineStr"/>
       <c r="CB31" t="inlineStr"/>
@@ -6907,18 +6931,10 @@
       <c r="CG31" t="inlineStr"/>
       <c r="CH31" t="inlineStr"/>
       <c r="CI31" t="inlineStr"/>
-      <c r="CJ31" t="n">
-        <v>10</v>
-      </c>
-      <c r="CK31" t="n">
-        <v>78</v>
-      </c>
-      <c r="CL31" t="n">
-        <v>10</v>
-      </c>
-      <c r="CM31" t="n">
-        <v>67</v>
-      </c>
+      <c r="CJ31" t="inlineStr"/>
+      <c r="CK31" t="inlineStr"/>
+      <c r="CL31" t="inlineStr"/>
+      <c r="CM31" t="inlineStr"/>
       <c r="CN31" t="inlineStr"/>
       <c r="CO31" t="inlineStr"/>
       <c r="CP31" t="inlineStr"/>
@@ -6930,27 +6946,27 @@
       <c r="CV31" t="inlineStr"/>
       <c r="CW31" t="inlineStr">
         <is>
-          <t>+10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 Level 1 Panichelli 79 ST PAC 69 SHO 81 PAS 63 DRI 73 DEF 28 PHY 82 R 3 ★ 3 Panichelli 80 ST PAC 69 SHO 81 PAS 64 DRI 73 DEF 28 PHY 82 R 3 ★ 3 ST 69.2 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78</t>
+          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Avdullahu 79 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 72 PHY 75 CM R 2 ★ 4 Avdullahu 80 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 73 PHY 75 CM R 2 ★ 4 CDM 77.8 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
         </is>
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY31" t="inlineStr">
         <is>
-          <t>Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7]</t>
+          <t>Midfield Polish [SP+ 1]</t>
         </is>
       </c>
       <c r="DA31" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.5 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 10 days in 10 days 89% 11%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Hato 78 LB PAC 85 SHO 42 PAS 70 DRI 74 DEF 76 PHY 74 CB CDM L 2 ★ 3 CDM 79.2 Hato 79 LB PAC 85 SHO 42 PAS 71 DRI 74 DEF 77 PHY 74 CB CDM L 2 ★ 3 CDM 79.8 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 9 days in 9 days 23% 77%</t>
         </is>
       </c>
     </row>
@@ -6962,80 +6978,88 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CM, CDM</t>
+          <t>LM, RM</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>CAM Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>LB, RB</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y32" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>79</v>
-      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>79</v>
-      </c>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
+      <c r="AL32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>80</v>
+      </c>
       <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="inlineStr"/>
@@ -7048,30 +7072,74 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="inlineStr"/>
-      <c r="BB32" t="inlineStr"/>
-      <c r="BC32" t="inlineStr"/>
-      <c r="BD32" t="inlineStr"/>
-      <c r="BE32" t="inlineStr"/>
+      <c r="BB32" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>84</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>78</v>
+      </c>
       <c r="BF32" t="inlineStr"/>
       <c r="BG32" t="inlineStr"/>
-      <c r="BH32" t="inlineStr"/>
-      <c r="BI32" t="inlineStr"/>
-      <c r="BJ32" t="inlineStr"/>
-      <c r="BK32" t="inlineStr"/>
-      <c r="BL32" t="inlineStr"/>
-      <c r="BM32" t="inlineStr"/>
-      <c r="BN32" t="inlineStr"/>
-      <c r="BO32" t="inlineStr"/>
-      <c r="BP32" t="inlineStr"/>
-      <c r="BQ32" t="inlineStr"/>
-      <c r="BR32" t="inlineStr"/>
-      <c r="BS32" t="inlineStr"/>
-      <c r="BT32" t="inlineStr"/>
-      <c r="BU32" t="inlineStr"/>
-      <c r="BV32" t="inlineStr"/>
-      <c r="BW32" t="inlineStr"/>
-      <c r="BX32" t="inlineStr"/>
-      <c r="BY32" t="inlineStr"/>
+      <c r="BH32" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>76</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>76</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>78</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>75</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>73</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>74</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>10</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>75</v>
+      </c>
       <c r="BZ32" t="inlineStr"/>
       <c r="CA32" t="inlineStr"/>
       <c r="CB32" t="inlineStr"/>
@@ -7084,271 +7152,52 @@
       <c r="CI32" t="inlineStr"/>
       <c r="CJ32" t="inlineStr"/>
       <c r="CK32" t="inlineStr"/>
-      <c r="CL32" t="inlineStr"/>
-      <c r="CM32" t="inlineStr"/>
+      <c r="CL32" t="n">
+        <v>15</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>78</v>
+      </c>
       <c r="CN32" t="inlineStr"/>
       <c r="CO32" t="inlineStr"/>
       <c r="CP32" t="inlineStr"/>
       <c r="CQ32" t="inlineStr"/>
-      <c r="CR32" t="inlineStr"/>
-      <c r="CS32" t="inlineStr"/>
-      <c r="CT32" t="inlineStr"/>
-      <c r="CU32" t="inlineStr"/>
+      <c r="CR32" t="n">
+        <v>2</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>2</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>3</v>
+      </c>
       <c r="CV32" t="inlineStr"/>
       <c r="CW32" t="inlineStr">
         <is>
-          <t>+1 OVR 80 +1 PAS 79 +1 DEF 79 Level 1 Avdullahu 79 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 72 PHY 75 CM R 2 ★ 4 Avdullahu 80 CDM PAC 69 SHO 61 PAS 79 DRI 78 DEF 73 PHY 75 CM R 2 ★ 4 CDM 77.8 UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79</t>
+          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Bouanani 74 RM PAC 71 SHO 68 PAS 73 DRI 77 DEF 33 PHY 58 CAM RW ST L 3 ★ 3 Bouanani 78 RM PAC 74 SHO 68 PAS 74 DRI 78 DEF 33 PHY 58 CAM RW ST L 3 ★ 3 ST 66.7 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
         </is>
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CY32" t="inlineStr">
         <is>
-          <t>Overall Max. 79 Position CM, CDM Excluded Position CAM Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 1 day Expiry in 1 day Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1]</t>
+          <t>Repeat Delivery 4</t>
         </is>
       </c>
       <c r="DA32" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Hato 78 LB PAC 85 SHO 42 PAS 70 DRI 74 DEF 76 PHY 74 CB CDM L 2 ★ 3 CDM 79.2 Hato 79 LB PAC 85 SHO 42 PAS 71 DRI 74 DEF 77 PHY 74 CB CDM L 2 ★ 3 CDM 79.8 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 10 days in 10 days 23% 77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>LM, RM</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>LB, RB</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
-      <c r="BB33" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>84</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>78</v>
-      </c>
-      <c r="BF33" t="inlineStr"/>
-      <c r="BG33" t="inlineStr"/>
-      <c r="BH33" t="n">
-        <v>15</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>76</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>76</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>12</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>78</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>75</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>12</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>73</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>74</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>74</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>10</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ33" t="inlineStr"/>
-      <c r="CA33" t="inlineStr"/>
-      <c r="CB33" t="inlineStr"/>
-      <c r="CC33" t="inlineStr"/>
-      <c r="CD33" t="inlineStr"/>
-      <c r="CE33" t="inlineStr"/>
-      <c r="CF33" t="inlineStr"/>
-      <c r="CG33" t="inlineStr"/>
-      <c r="CH33" t="inlineStr"/>
-      <c r="CI33" t="inlineStr"/>
-      <c r="CJ33" t="inlineStr"/>
-      <c r="CK33" t="inlineStr"/>
-      <c r="CL33" t="n">
-        <v>15</v>
-      </c>
-      <c r="CM33" t="n">
-        <v>78</v>
-      </c>
-      <c r="CN33" t="inlineStr"/>
-      <c r="CO33" t="inlineStr"/>
-      <c r="CP33" t="inlineStr"/>
-      <c r="CQ33" t="inlineStr"/>
-      <c r="CR33" t="n">
-        <v>2</v>
-      </c>
-      <c r="CS33" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT33" t="n">
-        <v>2</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>3</v>
-      </c>
-      <c r="CV33" t="inlineStr"/>
-      <c r="CW33" t="inlineStr">
-        <is>
-          <t>+8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 Level 1 Bouanani 74 RM PAC 71 SHO 68 PAS 73 DRI 77 DEF 33 PHY 58 CAM RW ST L 3 ★ 3 Bouanani 78 RM PAC 74 SHO 68 PAS 74 DRI 78 DEF 33 PHY 58 CAM RW ST L 3 ★ 3 ST 66.7 UPGRADES +8 OVR 78 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75</t>
-        </is>
-      </c>
-      <c r="CX33" t="inlineStr">
-        <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
-      <c r="CY33" t="inlineStr">
-        <is>
-          <t>Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 Details Submit by in 2 days Expiry in 2 days Coins Cost Free Points Cost Free</t>
-        </is>
-      </c>
-      <c r="CZ33" t="inlineStr">
-        <is>
-          <t>Repeat Delivery 4</t>
-        </is>
-      </c>
-      <c r="DA33" t="inlineStr">
-        <is>
-          <t>Repeat Delivery 4 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Salvio 74 RM PAC 72 SHO 72 PAS 70 DRI 78 DEF 54 PHY 66 LM RW LW R 5 ★ 4 LM 72.1 Salvio 78 RM PAC 77 SHO 72 PAS 78 DRI 78 DEF 54 PHY 68 LM RW LW R 5 ★ 4 RM 77.2 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 2 days in 2 days 91% 9%</t>
+          <t>Repeat Delivery 4 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Salvio 74 RM PAC 72 SHO 72 PAS 70 DRI 78 DEF 54 PHY 66 LM RW LW R 5 ★ 4 LM 72.1 Salvio 78 RM PAC 77 SHO 72 PAS 78 DRI 78 DEF 54 PHY 68 LM RW LW R 5 ★ 4 RM 77.2 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 1 day in 1 day 91% 9%</t>
         </is>
       </c>
     </row>
@@ -22521,7 +22370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26208,12 +26057,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>RB Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Position RB Details Submit by in 1 year Expiry in 1 year Coins Cost Free Points Cost Free</t>
+          <t>Position RB Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -26443,17 +26292,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Overall Max. 80</t>
+          <t>Overall Max. 83</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Technical - EA SPORTS FC 27</t>
+          <t>Frontline Flair - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -26463,24 +26312,24 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2543-technical/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -26490,17 +26339,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Max PS 2</t>
+          <t>Pace Max. 84</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Technical - EA SPORTS FC 27</t>
+          <t>Frontline Flair - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -26510,24 +26359,24 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2543-technical/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -26537,12 +26386,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Overall Max. 83</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -26569,27 +26418,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pace Max. 84</t>
+          <t>Excluded Position CAM</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -26616,27 +26465,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>LW, RW, ST</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Position LW, RW, ST</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -26663,32 +26512,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Excluded Position CAM</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Frontline Flair - EA SPORTS FC 27</t>
+          <t>Pinged Pass - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -26698,44 +26547,44 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LW, RW, ST</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Position LW, RW, ST</t>
+          <t>Max PS 2</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Frontline Flair - EA SPORTS FC 27</t>
+          <t>Pinged Pass - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -26745,12 +26594,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
     </row>
@@ -26772,17 +26621,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Overall Max. 82</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pinged Pass - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -26797,39 +26646,39 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Max PS 2</t>
+          <t>Position ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pinged Pass - EA SPORTS FC 27</t>
+          <t>Believe - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -26844,7 +26693,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
     </row>
@@ -26866,17 +26715,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Overall Max. 82</t>
+          <t>Overall Max. 81</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -26886,44 +26735,44 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Max_PS_Plus</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Max_PS_Plus</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Position ST Details Submit by in 11 months Expiry in 11 months Coins Cost Free Points Cost Free</t>
+          <t>Max PS+ 0</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Believe - EA SPORTS FC 27</t>
+          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -26933,24 +26782,24 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -26960,12 +26809,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Overall Max. 81</t>
+          <t>Max PS 3</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -26992,27 +26841,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Max_PS_Plus</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Max_PS_Plus</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>LW, RW, ST</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Max PS+ 0</t>
+          <t>Position LW, RW, ST</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -27039,12 +26888,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -27054,17 +26903,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Max PS 3</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
+          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -27074,44 +26923,44 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LW, RW, ST</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Position LW, RW, ST</t>
+          <t>Max PS 2</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] - EA SPORTS FC 27</t>
+          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -27121,12 +26970,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
     </row>
@@ -27148,17 +26997,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Overall Max. 81</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -27168,24 +27017,24 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -27195,17 +27044,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Max PS 2</t>
+          <t>Pace Max. 85</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] - EA SPORTS FC 27</t>
+          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -27215,24 +27064,24 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS_Plus</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS_Plus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -27242,12 +27091,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Overall Max. 81</t>
+          <t>Max PS+ 0</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -27274,12 +27123,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -27289,12 +27138,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pace Max. 85</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -27321,12 +27170,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Max_PS_Plus</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Max_PS_Plus</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -27336,12 +27185,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Max PS+ 0</t>
+          <t>Max Pos. 3</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -27368,27 +27217,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>LB, ST</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Excluded Position LB, ST</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -27415,27 +27264,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Max Pos. 3</t>
+          <t>Position LW</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -27462,32 +27311,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LB, ST</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Excluded Position LB, ST</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -27502,39 +27351,39 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Position LW</t>
+          <t>Max PS 2</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] - EA SPORTS FC 27</t>
+          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -27549,7 +27398,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27430,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
+          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -27591,12 +27440,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
         </is>
       </c>
     </row>
@@ -27628,7 +27477,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] - EA SPORTS FC 27</t>
+          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -27638,12 +27487,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
         </is>
       </c>
     </row>
@@ -27675,7 +27524,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -27690,19 +27539,19 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -27712,17 +27561,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Max PS 2</t>
+          <t>Pace Max. 84</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] - EA SPORTS FC 27</t>
+          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -27737,19 +27586,19 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -27759,12 +27608,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -27791,12 +27640,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Max_Positions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -27806,12 +27655,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pace Max. 84</t>
+          <t>Max Pos. 3</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -27838,27 +27687,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>CAM, CM</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Excluded Position CAM, CM</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -27885,27 +27734,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Max_Positions</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Max Pos. 3</t>
+          <t>Position ST</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -27932,32 +27781,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CAM, CM</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Excluded Position CAM, CM</t>
+          <t>Overall Max. 79</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -27967,44 +27816,44 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>CAM Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Position ST</t>
+          <t>Excluded Position CAM Details Submit by in 9 days Expiry in 9 days Coins Cost Free Points Cost Free</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] - EA SPORTS FC 27</t>
+          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -28014,39 +27863,39 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>CM, CDM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Overall Max. 79</t>
+          <t>Position CM, CDM</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -28073,32 +27922,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Excluded_Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Excluded Position</t>
+          <t>OVR_Max</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Exclude</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CAM Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Excluded Position CAM Details Submit by in 10 days Expiry in 10 days Coins Cost Free Points Cost Free</t>
+          <t>Overall Max. 74</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -28108,44 +27957,44 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>PAC_Max</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Include</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CM, CDM</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Position CM, CDM</t>
+          <t>Pace Max. 83</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] - EA SPORTS FC 27</t>
+          <t>Repeat Delivery - EA SPORTS FC 27</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -28155,24 +28004,24 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OVR_Max</t>
+          <t>Max_PS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -28182,12 +28031,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Overall Max. 74</t>
+          <t>Max PS 7</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -28214,27 +28063,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Excluded_Position</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PAC_Max</t>
+          <t>Excluded Position</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Exclude</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>LB, RB</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pace Max. 83</t>
+          <t>Excluded Position LB, RB</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -28261,27 +28110,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Max_PS</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Include</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>LM, RM</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Max PS 7</t>
+          <t>Position LM, RM</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -28300,100 +28149,6 @@
         </is>
       </c>
       <c r="I123" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Excluded_Position</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Excluded Position</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Exclude</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>LB, RB</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Excluded Position LB, RB</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>LM, RM</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Position LM, RM</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Repeat Delivery - EA SPORTS FC 27</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
         <is>
           <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
@@ -28410,7 +28165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28458,12 +28213,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Poor Sophia NEW</t>
+          <t>Poor Sophia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Poor Sophia NEW Poor Sophia no more! A bit more pace (don’t get excited, still a keeper) and extra skill moves. Enough to nutmeg the striker, then calmly jog back to goal. Barkas 75 GK DIV 75 HAN 73 KIC 71 REF 78 SPD 42 POS 73 L 1 ★ 2 GK 76.9 Barkas 80 GK DIV 80 HAN 79 KIC 77 REF 84 SPD 50 POS 79 L 3 ★ 2 GK 83.1 REQUIREMENTS Overall Max. 81 Position GK Max PS 7 Max PS+ 0 UPGRADES +5 OVR 83 +6 POS 80 +2 SM 3 +30 Acceleration 50 +6 Reactions 82 +6 Kicking 81 +6 Reflexes 84 +30 Sprint Speed 50 +6 Diving 80 +6 Handling 82 3 Show less in 10 days in 17 days 82% 18%</t>
+          <t>Poor Sophia Poor Sophia no more! A bit more pace (don’t get excited, still a keeper) and extra skill moves. Enough to nutmeg the striker, then calmly jog back to goal. Barkas 75 GK DIV 75 HAN 73 KIC 71 REF 78 SPD 42 POS 73 L 1 ★ 2 GK 76.9 Barkas 80 GK DIV 80 HAN 79 KIC 77 REF 84 SPD 50 POS 79 L 3 ★ 2 GK 83.1 REQUIREMENTS Overall Max. 81 Position GK Max PS 7 Max PS+ 0 UPGRADES +5 OVR 83 +6 POS 80 +2 SM 3 +30 Acceleration 50 +6 Reactions 82 +6 Kicking 81 +6 Reflexes 84 +30 Sprint Speed 50 +6 Diving 80 +6 Handling 82 3 Show less in 9 days in 16 days 74% 26%</t>
         </is>
       </c>
     </row>
@@ -28490,7 +28245,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zoomaestro Your playmaker always had the vision, now they get the legs. Boost pace and dribbling on your CAM or CM and glide past defenders in a blink. Iván Jaime 74 LM PAC 74 SHO 74 PAS 71 DRI 76 DEF 45 PHY 63 CAM ST LW R 3 ★ 4 LM 74.0 Iván Jaime 81 LM PAC 82 SHO 75 PAS 77 DRI 83 DEF 45 PHY 64 CAM ST LW R 4 ★ 4 LM 82.0 REQUIREMENTS Overall Max. 80 Position CAM, CM Skill Moves Max. 4 Max PS 7 Pace Max. 75 Defending Max. 74 UPGRADES +7 OVR 83 +1 SM 4 +5 Positioning 84 +10 Short Pass 85 +7 Balance 82 +10 Dribbling 83 +10 Acceleration 83 +5 Long Shots 83 +5 Curve 81 +7 Reactions 82 +10 Composure 81 +10 Sprint Speed 83 +10 Vision 82 +7 Agility 85 +10 Ball Control 85 +5 Stamina 84 3 in 9 days in 16 days 70% 30%</t>
+          <t>Zoomaestro Your playmaker always had the vision, now they get the legs. Boost pace and dribbling on your CAM or CM and glide past defenders in a blink. Iván Jaime 74 LM PAC 74 SHO 74 PAS 71 DRI 76 DEF 45 PHY 63 CAM ST LW R 3 ★ 4 LM 74.0 Iván Jaime 81 LM PAC 82 SHO 75 PAS 77 DRI 83 DEF 45 PHY 64 CAM ST LW R 4 ★ 4 LM 82.0 REQUIREMENTS Overall Max. 80 Position CAM, CM Skill Moves Max. 4 Max PS 7 Pace Max. 75 Defending Max. 74 UPGRADES +7 OVR 83 +1 SM 4 +5 Positioning 84 +10 Short Pass 85 +7 Balance 82 +10 Dribbling 83 +10 Acceleration 83 +5 Long Shots 83 +5 Curve 81 +7 Reactions 82 +10 Composure 81 +10 Sprint Speed 83 +10 Vision 82 +7 Agility 85 +10 Ball Control 85 +5 Stamina 84 3 in 8 days in 15 days 71% 29%</t>
         </is>
       </c>
     </row>
@@ -28517,7 +28272,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Middle Management Send your junior midfielder to this training to acquire skills necessary for managing the center of the pitch. From passing &amp; shooting, to interceptions &amp; strength, plus many more. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CDM 64.6 Bannan 80 CM PAC 75 SHO 75 PAS 81 DRI 74 DEF 73 PHY 77 CDM L 3 ★ 3 CDM 80.9 REQUIREMENTS Overall Max. 74 Position CDM, CM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 83 UPGRADES +40 OVR 80 +2 WF 3 +40 Finishing 76 +50 Vision 81 +50 Long Pass 81 +40 Standing Tackle 77 +40 Aggression 75 +40 Shot Power 77 +50 Crossing 80 +50 Curve 79 +40 Sliding Tackle 76 +40 Acceleration 75 +40 Long Shots 76 +50 Fk Accuracy 80 +40 Interceptions 77 +40 Jumping 75 +40 Sprint Speed 75 +40 Volleys 75 +50 Short Pass 81 +40 Defensive Awareness 76 +40 Strength 76 3 TRAINING TIME 1 day in 3 days in 10 days 32% 68%</t>
+          <t>Middle Management Send your junior midfielder to this training to acquire skills necessary for managing the center of the pitch. From passing &amp; shooting, to interceptions &amp; strength, plus many more. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CDM 64.6 Bannan 80 CM PAC 75 SHO 75 PAS 81 DRI 74 DEF 73 PHY 77 CDM L 3 ★ 3 CDM 80.9 REQUIREMENTS Overall Max. 74 Position CDM, CM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 83 UPGRADES +40 OVR 80 +2 WF 3 +40 Finishing 76 +50 Vision 81 +50 Long Pass 81 +40 Standing Tackle 77 +40 Aggression 75 +40 Shot Power 77 +50 Crossing 80 +50 Curve 79 +40 Sliding Tackle 76 +40 Acceleration 75 +40 Long Shots 76 +50 Fk Accuracy 80 +40 Interceptions 77 +40 Jumping 75 +40 Sprint Speed 75 +40 Volleys 75 +50 Short Pass 81 +40 Defensive Awareness 76 +40 Strength 76 3 TRAINING TIME 1 day in 7 days in 14 days 32% 68%</t>
         </is>
       </c>
     </row>
@@ -28544,7 +28299,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Future Stars Academy IV Graduation day has arrived. Complete your Future Star's journey as a clinical finisher or a creative playmaker, ready to shine on the biggest stage. Madjed 70 RM PAC 79 SHO 66 PAS 65 DRI 74 DEF 25 PHY 60 CAM RW ST L 4 ★ 2 RM 69.5 Madjed 85 RM PAC 87 SHO 82 PAS 84 DRI 83 DEF 28 PHY 72 CAM RW ST L 4 ★ 4 RM 86.8 REQUIREMENTS Rarity Future Stars Academy Overall Min. 83 Overall Max. 83 Max PS 7 UPGRADES +2 OVR 85 +5 Long Shots 78 +8 Penalties 75 +6 Composure 80 +5 Jumping 70 +4 Strength 72 +6 Shot Power 80 +8 Volleys 76 +6 Crossing 80 +4 Heading Acc. 72 +3 Stamina 83 +6 Aggression 60 +1 Finishing 84 4 in 7 days in 14 days 84% 16%</t>
+          <t>Future Stars Academy IV Graduation day has arrived. Complete your Future Star's journey as a clinical finisher or a creative playmaker, ready to shine on the biggest stage. Madjed 70 RM PAC 79 SHO 66 PAS 65 DRI 74 DEF 25 PHY 60 CAM RW ST L 4 ★ 2 RM 69.5 Madjed 85 RM PAC 87 SHO 82 PAS 84 DRI 83 DEF 28 PHY 72 CAM RW ST L 4 ★ 4 RM 86.8 REQUIREMENTS Rarity Future Stars Academy Overall Min. 83 Overall Max. 83 Max PS 7 UPGRADES +2 OVR 85 +5 Long Shots 78 +8 Penalties 75 +6 Composure 80 +5 Jumping 70 +4 Strength 72 +6 Shot Power 80 +8 Volleys 76 +6 Crossing 80 +4 Heading Acc. 72 +3 Stamina 83 +6 Aggression 60 +1 Finishing 84 4 in 6 days in 13 days 84% 16%</t>
         </is>
       </c>
     </row>
@@ -28571,7 +28326,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Speed Bump Your centre-back stops attackers. Now they can catch them too. Give a slower CB a pace upgrade and keep the wall standing, even on the counter. Tomiyasu 76 LB PAC 67 SHO 33 PAS 67 DRI 71 DEF 78 PHY 76 RB CB CM R 2 ★ 5 CM 71.0 Tomiyasu 83 LB PAC 77 SHO 33 PAS 70 DRI 73 DEF 82 PHY 80 RB CB CM R 2 ★ 5 CB 80.8 REQUIREMENTS Overall Max. 80 Position CB Excluded Position CDM Max PS 7 Pace Max. 75 UPGRADES +10 OVR 83 +10 Acceleration 77 +4 Long Pass 76 +14 Composure 81 +7 Defensive Awareness 82 +10 Jumping 85 +10 Sprint Speed 77 +7 Reactions 80 +7 Interceptions 82 +12 Standing Tackle 82 +7 Strength 86 +11 Short Pass 80 +5 Ball Control 76 +5 Heading Acc. 80 +7 Sliding Tackle 82 +5 Aggression 84 3 in 7 days in 14 days 60% 40%</t>
+          <t>Speed Bump Your centre-back stops attackers. Now they can catch them too. Give a slower CB a pace upgrade and keep the wall standing, even on the counter. Tomiyasu 76 LB PAC 67 SHO 33 PAS 67 DRI 71 DEF 78 PHY 76 RB CB CM R 2 ★ 5 CM 71.0 Tomiyasu 83 LB PAC 77 SHO 33 PAS 70 DRI 73 DEF 82 PHY 80 RB CB CM R 2 ★ 5 CB 80.8 REQUIREMENTS Overall Max. 80 Position CB Excluded Position CDM Max PS 7 Pace Max. 75 UPGRADES +10 OVR 83 +10 Acceleration 77 +4 Long Pass 76 +14 Composure 81 +7 Defensive Awareness 82 +10 Jumping 85 +10 Sprint Speed 77 +7 Reactions 80 +7 Interceptions 82 +12 Standing Tackle 82 +7 Strength 86 +11 Short Pass 80 +5 Ball Control 76 +5 Heading Acc. 80 +7 Sliding Tackle 82 +5 Aggression 84 3 in 6 days in 13 days 60% 40%</t>
         </is>
       </c>
     </row>
@@ -28598,7 +28353,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Centre Stage Command the centre circle with a resolute midfielder primed to reclaim possession, withstand physical pressure, and pick out key forward runs. Miley 77 CM PAC 68 SHO 66 PAS 76 DRI 75 DEF 76 PHY 69 RB CDM RM R 3 ★ 4 CDM 75.1 Miley 85 CM PAC 75 SHO 66 PAS 82 DRI 75 DEF 81 PHY 84 RB CDM RM R 3 ★ 4 CDM 84.7 REQUIREMENTS Overall Max. 81 Position CDM, CM Excluded Position CB, ST, CAM Max PS 7 Pace Max. 85 UPGRADES +10 OVR 85 +2 SM 3 +2 WF 3 +7 Sprint Speed 77 +10 Short Pass 82 +10 Heading Acc. 81 +30 Jumping 85 +10 Vision 83 +10 Long Pass 83 +10 Defensive Awareness 80 +30 Stamina 84 +10 Crossing 82 +10 Curve 82 +10 Standing Tackle 81 +30 Strength 85 +7 Acceleration 77 +10 Fk Accuracy 82 +10 Interceptions 82 +10 Sliding Tackle 82 +30 Aggression 85 3 in 6 days in 13 days 64% 36%</t>
+          <t>Centre Stage Command the centre circle with a resolute midfielder primed to reclaim possession, withstand physical pressure, and pick out key forward runs. Miley 77 CM PAC 68 SHO 66 PAS 76 DRI 75 DEF 76 PHY 69 RB CDM RM R 3 ★ 4 CDM 75.1 Miley 85 CM PAC 75 SHO 66 PAS 82 DRI 75 DEF 81 PHY 84 RB CDM RM R 3 ★ 4 CDM 84.7 REQUIREMENTS Overall Max. 81 Position CDM, CM Excluded Position CB, ST, CAM Max PS 7 Pace Max. 85 UPGRADES +10 OVR 85 +2 SM 3 +2 WF 3 +7 Sprint Speed 77 +10 Short Pass 82 +10 Heading Acc. 81 +30 Jumping 85 +10 Vision 83 +10 Long Pass 83 +10 Defensive Awareness 80 +30 Stamina 84 +10 Crossing 82 +10 Curve 82 +10 Standing Tackle 81 +30 Strength 85 +7 Acceleration 77 +10 Fk Accuracy 82 +10 Interceptions 82 +10 Sliding Tackle 82 +30 Aggression 85 3 in 5 days in 12 days 64% 36%</t>
         </is>
       </c>
     </row>
@@ -28625,7 +28380,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Side Step Dominate the touchline by developing a fullback equipped to shut down opposing attackers and lead the charge forward. Neville 75 RB PAC 73 SHO 70 PAS 73 DRI 72 DEF 74 PHY 79 LB R 3 ★ 4 RB 75.5 Neville 81 RB PAC 78 SHO 75 PAS 78 DRI 72 DEF 79 PHY 79 LB R 3 ★ 4 RB 79.7 REQUIREMENTS Overall Max. 80 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 85 UPGRADES +7 OVR 81 +2 WF 3 +5 Sprint Speed 83 +7 Long Shots 78 +7 Crossing 81 +7 Long Pass 76 +7 Defensive Awareness 78 +7 Finishing 78 +7 Volleys 76 +7 Fk Accuracy 78 +7 Curve 77 +7 Standing Tackle 81 +5 Acceleration 83 +7 Shot Power 77 +7 Vision 78 +7 Short Pass 80 +7 Interceptions 78 +7 Sliding Tackle 81 3 in 5 days in 12 days 21% 79%</t>
+          <t>Side Step Dominate the touchline by developing a fullback equipped to shut down opposing attackers and lead the charge forward. Neville 75 RB PAC 73 SHO 70 PAS 73 DRI 72 DEF 74 PHY 79 LB R 3 ★ 4 RB 75.5 Neville 81 RB PAC 78 SHO 75 PAS 78 DRI 72 DEF 79 PHY 79 LB R 3 ★ 4 RB 79.7 REQUIREMENTS Overall Max. 80 Position LB, RB Excluded Position CB, CM Max PS 7 Pace Max. 85 UPGRADES +7 OVR 81 +2 WF 3 +5 Sprint Speed 83 +7 Long Shots 78 +7 Crossing 81 +7 Long Pass 76 +7 Defensive Awareness 78 +7 Finishing 78 +7 Volleys 76 +7 Fk Accuracy 78 +7 Curve 77 +7 Standing Tackle 81 +5 Acceleration 83 +7 Shot Power 77 +7 Vision 78 +7 Short Pass 80 +7 Interceptions 78 +7 Sliding Tackle 81 3 in 4 days in 11 days 22% 78%</t>
         </is>
       </c>
     </row>
@@ -28652,7 +28407,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Future Stars Academy III Time to find their signature. Unlock a new PlayStyle and sharpen their pace, shooting or dribbling as your Future Star rises to the next level. Zeitler 68 ST PAC 75 SHO 68 PAS 56 DRI 69 DEF 40 PHY 56 LM CAM LW R 3 ★ 4 ST 65.7 Zeitler 83 ST PAC 84 SHO 78 PAS 84 DRI 86 DEF 41 PHY 69 LM CAM LW R 4 ★ 4 LM 84.7 REQUIREMENTS Rarity Future Stars Academy Overall Min. 82 Overall Max. 82 Max PS 7 UPGRADES +1 OVR 83 +3 Sprint Speed 87 +3 Acceleration 87 3 in 7 days in 14 days 91% 9%</t>
+          <t>Future Stars Academy III Time to find their signature. Unlock a new PlayStyle and sharpen their pace, shooting or dribbling as your Future Star rises to the next level. Zeitler 68 ST PAC 75 SHO 68 PAS 56 DRI 69 DEF 40 PHY 56 LM CAM LW R 3 ★ 4 ST 65.7 Zeitler 83 ST PAC 84 SHO 78 PAS 84 DRI 86 DEF 41 PHY 69 LM CAM LW R 4 ★ 4 LM 84.7 REQUIREMENTS Rarity Future Stars Academy Overall Min. 82 Overall Max. 82 Max PS 7 UPGRADES +1 OVR 83 +3 Sprint Speed 87 +3 Acceleration 87 3 in 6 days in 13 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28434,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Touchline Magic 20,000 150 Unlock defences from out wide with a dynamic winger capable of accelerating past markers, showcasing elite dribbling, and scoring crucial goals. Murphy 79 RW PAC 76 SHO 77 PAS 78 DRI 79 DEF 60 PHY 66 RM R 3 ★ 4 RM 72.0 Murphy 84 RW PAC 85 SHO 80 PAS 79 DRI 84 DEF 60 PHY 68 RM R 4 ★ 4 RM 82.6 REQUIREMENTS Overall Max. 80 Position LW, RW Excluded Position ST, CM, CAM Max PS 7 Pace Max. 86 UPGRADES +10 OVR 84 +1 SM 4 +10 Sprint Speed 85 +7 Long Shots 81 +10 Agility 84 +10 Dribbling 84 +7 Positioning 81 +7 Vision 79 +10 Balance 83 +10 Composure 83 +7 Finishing 82 +7 Short Pass 80 +10 Reactions 83 +7 Stamina 82 +10 Acceleration 85 +7 Shot Power 81 +7 Curve 83 +10 Ball Control 84 3 in 3 days in 10 days 46% 54%</t>
+          <t>Touchline Magic 20,000 150 Unlock defences from out wide with a dynamic winger capable of accelerating past markers, showcasing elite dribbling, and scoring crucial goals. Murphy 79 RW PAC 76 SHO 77 PAS 78 DRI 79 DEF 60 PHY 66 RM R 3 ★ 4 RM 72.0 Murphy 84 RW PAC 85 SHO 80 PAS 79 DRI 84 DEF 60 PHY 68 RM R 4 ★ 4 RM 82.6 REQUIREMENTS Overall Max. 80 Position LW, RW Excluded Position ST, CM, CAM Max PS 7 Pace Max. 86 UPGRADES +10 OVR 84 +1 SM 4 +10 Sprint Speed 85 +7 Long Shots 81 +10 Agility 84 +10 Dribbling 84 +7 Positioning 81 +7 Vision 79 +10 Balance 83 +10 Composure 83 +7 Finishing 82 +7 Short Pass 80 +10 Reactions 83 +7 Stamina 82 +10 Acceleration 85 +7 Shot Power 81 +7 Curve 83 +10 Ball Control 84 3 in 2 days in 9 days 46% 54%</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28461,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Future Stars Academy II The next step in their journey. Help your Future Star grow into a playmaker, a physical powerhouse or a well-rounded all-rounder. Mboup 70 LM PAC 86 SHO 65 PAS 60 DRI 73 DEF 27 PHY 58 ST LW R 3 ★ 3 LM 72.3 Mboup 82 LM PAC 86 SHO 84 PAS 84 DRI 82 DEF 29 PHY 67 ST LW R 3 ★ 4 LM 84.1 REQUIREMENTS Rarity Future Stars Academy Overall Min. 81 Overall Max. 81 UPGRADES +1 OVR 82 +1 Finishing 80 +1 Long Shots 78 +2 Reactions 82 +1 Dribbling 81 +2 Heading Acc. 75 +1 Positioning 81 +1 Shot Power 81 +1 Balance 78 +2 Ball Control 81 +2 Composure 80 +1 Stamina 83 +10 Vision 86 +12 Crossing 82 +15 Fk Accuracy 80 +8 Short Pass 86 +12 Long Pass 82 +12 Curve 84 in 7 days in 14 days 91% 9%</t>
+          <t>Future Stars Academy II The next step in their journey. Help your Future Star grow into a playmaker, a physical powerhouse or a well-rounded all-rounder. Mboup 70 LM PAC 86 SHO 65 PAS 60 DRI 73 DEF 27 PHY 58 ST LW R 3 ★ 3 LM 72.3 Mboup 82 LM PAC 86 SHO 84 PAS 84 DRI 82 DEF 29 PHY 67 ST LW R 3 ★ 4 LM 84.1 REQUIREMENTS Rarity Future Stars Academy Overall Min. 81 Overall Max. 81 UPGRADES +1 OVR 82 +1 Finishing 80 +1 Long Shots 78 +2 Reactions 82 +1 Dribbling 81 +2 Heading Acc. 75 +1 Positioning 81 +1 Shot Power 81 +1 Balance 78 +2 Ball Control 81 +2 Composure 80 +1 Stamina 83 +10 Vision 86 +12 Crossing 82 +15 Fk Accuracy 80 +8 Short Pass 86 +12 Long Pass 82 +12 Curve 84 in 6 days in 13 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -28733,7 +28488,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Playmaker Reborn Reinvent your midfield engine with sharp vision and crisp passes to dictate match tempo from the center. Taylor 67 LM PAC 83 SHO 62 PAS 58 DRI 69 DEF 36 PHY 64 CM CAM LW R 3 ★ 5 LM 70.2 Taylor 80 LM PAC 83 SHO 76 PAS 80 DRI 78 DEF 36 PHY 66 CM CAM LW R 3 ★ 5 LM 78.8 REQUIREMENTS Overall Max. 74 Position CAM, CM Excluded Position CDM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 80 +40 Positioning 77 +40 Volleys 76 +50 Fk Accuracy 79 +40 Agility 78 +40 Dribbling 77 +40 Finishing 76 +40 Penalties 77 +50 Short Pass 80 +40 Balance 76 +40 Composure 77 +40 Acceleration 76 +40 Shot Power 75 +50 Vision 80 +50 Long Pass 81 +40 Reactions 74 +40 Stamina 79 +40 Sprint Speed 75 +40 Long Shots 77 +50 Crossing 79 +50 Curve 79 +40 Ball Control 77 3 TRAINING TIME 1 day in 2 days in 10 days 33% 67%</t>
+          <t>Playmaker Reborn Reinvent your midfield engine with sharp vision and crisp passes to dictate match tempo from the center. Taylor 67 LM PAC 83 SHO 62 PAS 58 DRI 69 DEF 36 PHY 64 CM CAM LW R 3 ★ 5 LM 70.2 Taylor 80 LM PAC 83 SHO 76 PAS 80 DRI 78 DEF 36 PHY 66 CM CAM LW R 3 ★ 5 LM 78.8 REQUIREMENTS Overall Max. 74 Position CAM, CM Excluded Position CDM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 80 +40 Positioning 77 +40 Volleys 76 +50 Fk Accuracy 79 +40 Agility 78 +40 Dribbling 77 +40 Finishing 76 +40 Penalties 77 +50 Short Pass 80 +40 Balance 76 +40 Composure 77 +40 Acceleration 76 +40 Shot Power 75 +50 Vision 80 +50 Long Pass 81 +40 Reactions 74 +40 Stamina 79 +40 Sprint Speed 75 +40 Long Shots 77 +50 Crossing 79 +50 Curve 79 +40 Ball Control 77 3 TRAINING TIME 1 day in 1 day in 9 days 33% 67%</t>
         </is>
       </c>
     </row>
@@ -28760,7 +28515,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Quick Step [FC 26 Obj] Unlocked by completing the FC 26 Season 9 Pass Spence 80 LB PAC 89 SHO 54 PAS 71 DRI 79 DEF 76 PHY 75 RB R 3 ★ 4 RB 81.5 Spence 80 LB PAC 89 SHO 54 PAS 71 DRI 79 DEF 76 PHY 75 RB R 3 ★ 4 RB 83.2 REQUIREMENTS Overall Max. 83 Max PS 2 UPGRADES 3 in 1 year in 1 year 75% 25%</t>
+          <t>Quick Step [FC 26 Obj] Unlocked by completing the FC 26 Season 9 Pass Spence 80 LB PAC 89 SHO 54 PAS 71 DRI 79 DEF 76 PHY 75 RB R 3 ★ 4 RB 81.5 Spence 80 LB PAC 89 SHO 54 PAS 71 DRI 79 DEF 76 PHY 75 RB R 3 ★ 4 RB 83.2 REQUIREMENTS Overall Max. 83 Max PS 2 UPGRADES 3 in 11 months in 11 months 75% 25%</t>
         </is>
       </c>
     </row>
@@ -28787,7 +28542,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Future Stars Academy I Every legend starts somewhere. Develop your young forward into a complete player, then choose whether they make their mark with pace, shooting or dribbling. Mboup 70 LM PAC 86 SHO 65 PAS 60 DRI 73 DEF 27 PHY 58 ST LW R 3 ★ 3 LM 72.3 Mboup 81 LM PAC 86 SHO 84 PAS 79 DRI 81 DEF 29 PHY 67 ST LW R 3 ★ 4 LM 83.2 REQUIREMENTS Overall Max. 80 Position CAM, ST Born After 2003-10-09 Max PS 7 Pace Max. 86 UPGRADES C +34 OVR 81 +2 SM 4 +20 Finishing 79 +30 Vision 82 +35 Long Pass 76 +25 Reactions 80 +20 Heading Acc. 73 +20 Acceleration 81 +20 Shot Power 80 +35 Crossing 76 +35 Curve 76 +32 Ball Control 80 +25 Stamina 82 +20 Sprint Speed 81 +20 Long Shots 77 +30 Fk Accuracy 72 +32 Agility 80 +32 Dribbling 80 +15 Strength 73 +25 Positioning 80 +20 Volleys 75 +35 Short Pass 82 +35 Balance 77 +30 Composure 78 Future Stars Academy in 7 days in 14 days 95% 5%</t>
+          <t>Future Stars Academy I Every legend starts somewhere. Develop your young forward into a complete player, then choose whether they make their mark with pace, shooting or dribbling. Mboup 70 LM PAC 86 SHO 65 PAS 60 DRI 73 DEF 27 PHY 58 ST LW R 3 ★ 3 LM 72.3 Mboup 81 LM PAC 86 SHO 84 PAS 79 DRI 81 DEF 29 PHY 67 ST LW R 3 ★ 4 LM 83.2 REQUIREMENTS Overall Max. 80 Position CAM, ST Born After 2003-10-09 Max PS 7 Pace Max. 86 UPGRADES C +34 OVR 81 +2 SM 4 +20 Finishing 79 +30 Vision 82 +35 Long Pass 76 +25 Reactions 80 +20 Heading Acc. 73 +20 Acceleration 81 +20 Shot Power 80 +35 Crossing 76 +35 Curve 76 +32 Ball Control 80 +25 Stamina 82 +20 Sprint Speed 81 +20 Long Shots 77 +30 Fk Accuracy 72 +32 Agility 80 +32 Dribbling 80 +15 Strength 73 +25 Positioning 80 +20 Volleys 75 +35 Short Pass 82 +35 Balance 77 +30 Composure 78 Future Stars Academy in 6 days in 13 days 95% 5%</t>
         </is>
       </c>
     </row>
@@ -28814,7 +28569,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nine Duty Elevate your striker’s attacking impact to help them consistently influence matches when leading the line. Rodney 60 ST PAC 84 SHO 59 PAS 52 DRI 60 DEF 29 PHY 65 RM LM RW LW R 3 ★ 4 ST 65.3 Rodney 79 ST PAC 84 SHO 79 PAS 75 DRI 78 DEF 29 PHY 65 RM LM RW LW R 3 ★ 4 ST 80.0 REQUIREMENTS Overall Max. 74 Position ST Excluded Position CB, CM, CAM Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +2 SM 3 +50 Positioning 80 +50 Volleys 79 +40 Fk Accuracy 77 +40 Agility 78 +40 Dribbling 78 +50 Finishing 79 +50 Penalties 81 +40 Short Pass 75 +40 Balance 78 +40 Composure 76 +40 Acceleration 78 +50 Shot Power 79 +40 Vision 75 +40 Long Pass 75 +40 Reactions 78 +40 Sprint Speed 78 +50 Long Shots 78 +40 Crossing 75 +40 Curve 77 +40 Ball Control 78 3 TRAINING TIME 1 day in 3 days in 10 days 76% 24%</t>
+          <t>Nine Duty Elevate your striker’s attacking impact to help them consistently influence matches when leading the line. Rodney 60 ST PAC 84 SHO 59 PAS 52 DRI 60 DEF 29 PHY 65 RM LM RW LW R 3 ★ 4 ST 65.3 Rodney 79 ST PAC 84 SHO 79 PAS 75 DRI 78 DEF 29 PHY 65 RM LM RW LW R 3 ★ 4 ST 80.0 REQUIREMENTS Overall Max. 74 Position ST Excluded Position CB, CM, CAM Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +2 SM 3 +50 Positioning 80 +50 Volleys 79 +40 Fk Accuracy 77 +40 Agility 78 +40 Dribbling 78 +50 Finishing 79 +50 Penalties 81 +40 Short Pass 75 +40 Balance 78 +40 Composure 76 +40 Acceleration 78 +50 Shot Power 79 +40 Vision 75 +40 Long Pass 75 +40 Reactions 78 +40 Sprint Speed 78 +50 Long Shots 78 +40 Crossing 75 +40 Curve 77 +40 Ball Control 78 3 TRAINING TIME 1 day in 2 days in 9 days 76% 24%</t>
         </is>
       </c>
     </row>
@@ -28841,7 +28596,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CDM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.2 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 3 days in 3 days 83% 17%</t>
+          <t>Midfield Glow Up Elevate your engine room with a major tactical upgrade, combining enhanced recovery speed, relentless physical presence, and superior distribution across the pitch. Bannan 72 CM PAC 44 SHO 63 PAS 75 DRI 74 DEF 60 PHY 59 CDM L 3 ★ 3 CDM 64.6 Bannan 79 CM PAC 75 SHO 63 PAS 78 DRI 74 DEF 75 PHY 78 CDM L 3 ★ 3 CDM 81.2 REQUIREMENTS Overall Max. 74 Position CDM Excluded Position CAM, CB, ST Max PS 7 Pace Max. 85 UPGRADES +40 OVR 79 +50 Vision 77 +50 Long Pass 79 +40 Standing Tackle 80 +40 Strength 77 +50 Crossing 75 +50 Curve 75 +40 Sliding Tackle 75 +40 Aggression 75 +40 Acceleration 75 +50 Fk Accuracy 74 +40 Interceptions 75 +40 Jumping 76 +40 Sprint Speed 75 +50 Short Pass 80 +40 Defensive Awareness 80 +40 Stamina 76 CDM Deep Lying Playmaker + CDM Box Crasher + 3 TRAINING TIME 1 day in 2 days in 2 days 83% 17%</t>
         </is>
       </c>
     </row>
@@ -28868,7 +28623,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.7 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.9 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 1 year in 1 year 80% 20%</t>
+          <t>Intro to Repeatable Evolutions 2 Discover Repeatable Evolutions, allowing you to run multiple players through the same upgrade path! Lee Dong Gyeong 75 CAM PAC 77 SHO 74 PAS 73 DRI 75 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 76.7 Lee Dong Gyeong 76 CAM PAC 77 SHO 75 PAS 76 DRI 77 DEF 59 PHY 73 CDM CM ST L 4 ★ 5 CAM 77.9 REQUIREMENTS Overall Max. 79 Position ST Pace Max. 81 UPGRADES +1 OVR 80 +4 Long Shots 77 +3 Vision 79 +3 Short Pass 78 +4 Reactions 80 +3 Shot Power 78 +3 Volleys 78 +4 Fk Accuracy 80 +4 Long Pass 77 +4 Dribbling 80 in 11 months in 11 months 80% 20%</t>
         </is>
       </c>
     </row>
@@ -28895,7 +28650,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Trimmel 75 RB PAC 61 SHO 65 PAS 74 DRI 68 DEF 74 PHY 79 RM R 3 ★ 3 RB 62.1 Trimmel 79 RB PAC 80 SHO 65 PAS 77 DRI 79 DEF 76 PHY 81 RM R 3 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 1 year in 1 year 88% 12%</t>
+          <t>Intro to Evolutions Welcome to Evolutions in FC 27! Upgrade a player of your choice and unlock their first attribute boost. Trimmel 75 RB PAC 61 SHO 65 PAS 74 DRI 68 DEF 74 PHY 79 RM R 3 ★ 3 RB 62.1 Trimmel 79 RB PAC 80 SHO 65 PAS 77 DRI 79 DEF 76 PHY 81 RM R 3 ★ 3 RB 76.0 REQUIREMENTS Max Pos. 2 Overall Max. 75 Position RB Excluded Position CB Max PS 7 Pace Max. 80 UPGRADES +34 OVR 79 +40 Sprint Speed 80 +40 Short Pass 76 +40 Balance 77 +40 Interceptions 76 +40 Sliding Tackle 75 +40 Vision 75 +40 Curve 80 +40 Ball Control 80 +40 Defensive Awareness 77 +40 Stamina 80 +40 Acceleration 80 +40 Crossing 78 +40 Agility 78 +40 Dribbling 80 +40 Standing Tackle 78 RB Wingback + 3 in 11 months in 11 months 88% 12%</t>
         </is>
       </c>
     </row>
@@ -28922,7 +28677,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Luis Henrique 77 RB PAC 90 SHO 74 PAS 72 DRI 78 DEF 70 PHY 76 RM R 3 ★ 3 RB 77.3 Luis Henrique 77 RB PAC 90 SHO 74 PAS 72 DRI 78 DEF 70 PHY 76 RM R 3 ★ 3 RB 78.8 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 1 year in 1 year 82% 18%</t>
+          <t>Intro to Training Camp EVOs Send your players to training camp! Collect their attribute upgrades when the training session concludes. Luis Henrique 77 RB PAC 90 SHO 74 PAS 72 DRI 78 DEF 70 PHY 76 RM R 3 ★ 3 RB 77.3 Luis Henrique 77 RB PAC 90 SHO 74 PAS 72 DRI 78 DEF 70 PHY 76 RM R 3 ★ 3 RB 78.8 REQUIREMENTS Overall Max. 80 Position RB UPGRADES RB Fullback + TRAINING TIME 1 hours in 11 months in 11 months 82% 18%</t>
         </is>
       </c>
     </row>
@@ -28949,7 +28704,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.7 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 83.0 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES A 4 in 1 year in 1 year 82% 18%</t>
+          <t>Intro to Pathway Evolutions Explore Pathway Evolutions, a new type of Evolution that allows you to choose how your player develops and upgrades! Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 81.7 Orban 80 ST PAC 82 SHO 85 PAS 73 DRI 82 DEF 26 PHY 68 R 3 ★ 3 ST 83.0 REQUIREMENTS Overall Max. 80 Max PS 3 UPGRADES A 4 in 11 months in 11 months 82% 18%</t>
         </is>
       </c>
     </row>
@@ -28976,7 +28731,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gamechanger Add Gamechanger to any qualified player. Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 79.4 Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 80.9 REQUIREMENTS Overall Max. 80 Max PS 2 UPGRADES 3 in 8 days in 8 days 49% 51%</t>
+          <t>Gamechanger Add Gamechanger to any qualified player. Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 79.4 Kühn 76 RM PAC 90 SHO 71 PAS 68 DRI 80 DEF 47 PHY 63 RW L 4 ★ 4 RM 80.9 REQUIREMENTS Overall Max. 80 Max PS 2 UPGRADES 3 in 7 days in 7 days 50% 50%</t>
         </is>
       </c>
     </row>
@@ -28988,22 +28743,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2543-technical/</t>
+          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Frontline Flair 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Technical Unlocked by completing the Assist 5 task in the Back to Basics Objective objective Gittens 77 LM PAC 92 SHO 72 PAS 66 DRI 82 DEF 27 PHY 55 LW R 4 ★ 3 LM 80.0 Gittens 77 LM PAC 92 SHO 72 PAS 66 DRI 82 DEF 27 PHY 55 LW R 4 ★ 3 LM 80.8 REQUIREMENTS Overall Max. 80 Max PS 2 UPGRADES 3 in 19 hours in 19 hours 89% 11%</t>
+          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Meerdink 80 ST PAC 78 SHO 81 PAS 70 DRI 80 DEF 38 PHY 84 L 4 ★ 3 ST 80.6 Meerdink 81 ST PAC 80 SHO 82 PAS 70 DRI 82 DEF 38 PHY 84 L 4 ★ 3 ST 82.1 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 2 days in 9 days 75% 25%</t>
         </is>
       </c>
     </row>
@@ -29015,22 +28770,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reward</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2532-frontline-flair/</t>
+          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Frontline Flair 2</t>
+          <t>Pinged Pass</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Frontline Flair 2 Unlocked via the Token Store for 100 tokens Meerdink 80 ST PAC 78 SHO 81 PAS 70 DRI 80 DEF 38 PHY 84 L 4 ★ 3 ST 80.6 Meerdink 81 ST PAC 80 SHO 82 PAS 70 DRI 82 DEF 38 PHY 84 L 4 ★ 3 ST 82.1 REQUIREMENTS Overall Max. 83 Position LW, RW, ST Excluded Position CAM Max PS 7 Pace Max. 84 UPGRADES +1 OVR 84 +2 PAC 84 +1 SHO 82 +2 DRI 84 3 in 3 days in 10 days 77% 23%</t>
+          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Vite 76 CM PAC 80 SHO 61 PAS 73 DRI 75 DEF 73 PHY 67 CDM CAM L 3 ★ 4 CDM 78.6 Vite 76 CM PAC 80 SHO 61 PAS 73 DRI 75 DEF 73 PHY 67 CDM CAM L 3 ★ 4 CDM 80.1 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 9 days in 9 days 95% 5%</t>
         </is>
       </c>
     </row>
@@ -29047,17 +28802,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2501-pinged-pass/</t>
+          <t>https://www.fut.gg/evolutions/2500-believe/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pinged Pass</t>
+          <t>Believe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pinged Pass Unlocked by completing the Pep's Domination task in the Ones We Watched World Class Challenge objective Vite 76 CM PAC 80 SHO 61 PAS 73 DRI 75 DEF 73 PHY 67 CDM CAM L 3 ★ 4 CDM 78.6 Vite 76 CM PAC 80 SHO 61 PAS 73 DRI 75 DEF 73 PHY 67 CDM CAM L 3 ★ 4 CDM 80.1 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 10 days in 10 days 95% 5%</t>
+          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.0 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.4 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 11 months in 11 months 35% 65%</t>
         </is>
       </c>
     </row>
@@ -29069,22 +28824,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Objective</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2500-believe/</t>
+          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Believe</t>
+          <t>Shooting Practice [SP+ 28]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Believe Unlocked by completing the Ted Lasso's Masterclass objective Chiesa 80 RM PAC 87 SHO 79 PAS 75 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.0 Chiesa 81 RM PAC 87 SHO 79 PAS 77 DRI 83 DEF 44 PHY 68 RW ST R 4 ★ 4 RM 84.4 REQUIREMENTS Overall Max. 82 Position ST UPGRADES +1 OVR 83 +4 Short Pass 83 +3 Composure 84 in 11 months in 11 months 35% 65%</t>
+          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 83.6 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 9 days in 9 days 81% 19%</t>
         </is>
       </c>
     </row>
@@ -29096,22 +28851,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2499-shooting-practice-sp-28/</t>
+          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28]</t>
+          <t>Creative or Composed? [SP 27]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shooting Practice [SP+ 28] Unlocked by reaching level 28 in the Premium Season Pass. Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 82.1 Nkoudou 78 LM PAC 92 SHO 79 PAS 71 DRI 81 DEF 34 PHY 63 LW R 5 ★ 3 LM 83.6 REQUIREMENTS Overall Max. 81 Position LW, RW, ST Max PS 3 Max PS+ 0 UPGRADES B · A 4 in 10 days in 10 days 82% 18%</t>
+          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.2 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 9 days in 9 days 88% 12%</t>
         </is>
       </c>
     </row>
@@ -29123,22 +28878,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2498-creative-or-composed-sp-27/</t>
+          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27]</t>
+          <t>Winger Glow Up [SP+ 26]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Creative or Composed? [SP 27] Unlocked by reaching level 27 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.2 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 80.2 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 10 days in 10 days 88% 13%</t>
+          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LW 71.0 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 81.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 9 days in 9 days 91% 9%</t>
         </is>
       </c>
     </row>
@@ -29155,17 +28910,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2497-winger-glow-up-sp-26/</t>
+          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26]</t>
+          <t>Tactical Ascent [SP+ 14]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Winger Glow Up [SP+ 26] Unlocked by reaching level 26 in the Premium Season Pass. Cambiaghi 76 LM PAC 73 SHO 74 PAS 72 DRI 79 DEF 43 PHY 60 LW R 3 ★ 5 LW 71.0 Cambiaghi 83 LM PAC 85 SHO 78 PAS 78 DRI 84 DEF 43 PHY 63 LW R 3 ★ 5 LM 81.9 REQUIREMENTS Max Pos. 3 Overall Max. 81 Position LW Excluded Position LB, ST Max PS 7 Max PS+ 0 Pace Max. 85 UPGRADES +10 OVR 83 +1 SM 3 +10 Positioning 80 +10 Volleys 74 +10 Fk Accuracy 73 +15 Agility 86 +15 Dribbling 84 +10 Finishing 78 +10 Penalties 74 +10 Short Pass 76 +15 Balance 85 +15 Composure 80 +15 Acceleration 85 +10 Shot Power 77 +10 Vision 81 +10 Long Pass 80 +15 Reactions 78 +10 Stamina 72 +15 Sprint Speed 85 +10 Long Shots 80 +10 Crossing 82 +10 Curve 78 +15 Ball Control 85 3 in 10 days in 10 days 90% 10%</t>
+          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.0 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.1 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 9 days in 9 days 90% 10%</t>
         </is>
       </c>
     </row>
@@ -29177,22 +28932,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Standard Season Pass</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2496-tactical-ascent-sp-14/</t>
+          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14]</t>
+          <t>Relentless [SP 11]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tactical Ascent [SP+ 14] Unlocked by reaching level 14 in the Premium Season Pass. Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 77.0 Mika Mármol 75 CB PAC 85 SHO 55 PAS 66 DRI 73 DEF 74 PHY 79 LB L 2 ★ 3 LB 80.1 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES A · A 3 in 10 days in 10 days 90% 10%</t>
+          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.2 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.7 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 9 days in 9 days 38% 63%</t>
         </is>
       </c>
     </row>
@@ -29209,17 +28964,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2495-relentless-sp-11/</t>
+          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Relentless [SP 11]</t>
+          <t>Striker Glow Up [SP 7]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Relentless [SP 11] Unlocked by reaching level 11 in the Standard Season Pass. Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.2 Baku 79 RB PAC 83 SHO 72 PAS 75 DRI 80 DEF 75 PHY 76 RM CM RW R 3 ★ 4 CM 78.7 REQUIREMENTS Overall Max. 79 Max PS 2 UPGRADES 3 in 10 days in 10 days 38% 63%</t>
+          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.5 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 9 days in 9 days 89% 11%</t>
         </is>
       </c>
     </row>
@@ -29231,22 +28986,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Standard Season Pass</t>
+          <t>Premium Season Pass</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2494-striker-glow-up-sp-7/</t>
+          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7]</t>
+          <t>Midfield Polish [SP+ 1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Striker Glow Up [SP 7] Unlocked by reaching level 7 in the Standard Season Pass. Zirkzee 77 ST PAC 67 SHO 76 PAS 73 DRI 80 DEF 42 PHY 75 R 4 ★ 3 ST 70.5 Zirkzee 80 ST PAC 77 SHO 81 PAS 74 DRI 82 DEF 42 PHY 75 R 4 ★ 3 ST 78.9 REQUIREMENTS Max Pos. 3 Overall Max. 79 Position ST Excluded Position CAM, CM Max PS 7 Pace Max. 84 UPGRADES +10 OVR 80 +15 Positioning 82 +15 Volleys 78 +8 Long Pass 62 +10 Reactions 76 +10 Jumping 78 +15 Finishing 83 +10 Penalties 75 +15 Curve 77 +10 Ball Control 76 +10 Stamina 67 +10 Acceleration 80 +15 Shot Power 82 +8 Vision 70 +15 Agility 78 +10 Dribbling 76 +10 Sprint Speed 78 +15 Long Shots 78 +8 Short Pass 72 +15 Balance 77 +8 Composure 80 3 in 10 days in 10 days 89% 11%</t>
+          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Hato 78 LB PAC 85 SHO 42 PAS 70 DRI 74 DEF 76 PHY 74 CB CDM L 2 ★ 3 CDM 79.2 Hato 79 LB PAC 85 SHO 42 PAS 71 DRI 74 DEF 77 PHY 74 CB CDM L 2 ★ 3 CDM 79.8 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 9 days in 9 days 23% 77%</t>
         </is>
       </c>
     </row>
@@ -29258,49 +29013,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Premium Season Pass</t>
+          <t>Reward</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.fut.gg/evolutions/2493-midfield-polish-sp-1/</t>
+          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1]</t>
+          <t>Repeat Delivery 4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Midfield Polish [SP+ 1] Unlocked by reaching level 1 in the Premium Season Pass. Hato 78 LB PAC 85 SHO 42 PAS 70 DRI 74 DEF 76 PHY 74 CB CDM L 2 ★ 3 CDM 79.2 Hato 79 LB PAC 85 SHO 42 PAS 71 DRI 74 DEF 77 PHY 74 CB CDM L 2 ★ 3 CDM 79.8 REQUIREMENTS Overall Max. 79 Position CM, CDM Excluded Position CAM UPGRADES +1 OVR 80 +1 PAS 79 +1 DEF 79 in 10 days in 10 days 23% 77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Reward</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.fut.gg/evolutions/2489-repeat-delivery/</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Repeat Delivery 4</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Repeat Delivery 4 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Salvio 74 RM PAC 72 SHO 72 PAS 70 DRI 78 DEF 54 PHY 66 LM RW LW R 5 ★ 4 LM 72.1 Salvio 78 RM PAC 77 SHO 72 PAS 78 DRI 78 DEF 54 PHY 68 LM RW LW R 5 ★ 4 RM 77.2 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 2 days in 2 days 91% 9%</t>
+          <t>Repeat Delivery 4 Keep the service coming. Upgrade your wide midfielder’s passing and delivery, then run it back for another round and keep feeding your attack from the flanks. Salvio 74 RM PAC 72 SHO 72 PAS 70 DRI 78 DEF 54 PHY 66 LM RW LW R 5 ★ 4 LM 72.1 Salvio 78 RM PAC 77 SHO 72 PAS 78 DRI 78 DEF 54 PHY 68 LM RW LW R 5 ★ 4 RM 77.2 REQUIREMENTS Overall Max. 74 Position LM, RM Excluded Position LB, RB Max PS 7 Pace Max. 83 UPGRADES +8 OVR 78 +2 SM 3 +2 WF 3 +5 Sprint Speed 80 +15 Short Pass 76 +12 Balance 75 +10 Composure 75 +15 Vision 84 +12 Long Pass 76 +12 Reactions 73 +15 Stamina 78 +10 Crossing 78 +12 Curve 78 +8 Ball Control 74 +5 Acceleration 80 +4 Fk Accuracy 80 +8 Agility 78 +8 Dribbling 74 3 TRAINING TIME 1 day in 1 day in 1 day 91% 9%</t>
         </is>
       </c>
     </row>
@@ -29360,7 +29088,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -29371,7 +29099,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T21:31:54</t>
+          <t>2026-10-20T20:34:39</t>
         </is>
       </c>
     </row>
@@ -29394,7 +29122,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
